--- a/TM_all.xlsx
+++ b/TM_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aecf56309e6168f4/Documents/comunio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FFB4874-38AD-4E7B-A75E-20013E824FA2}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D89F5939-5F1D-4E30-B714-F2201BE67D18}"/>
   <bookViews>
     <workbookView xWindow="2110" yWindow="2130" windowWidth="28800" windowHeight="15370" xr2:uid="{607DE709-F91E-4262-9941-1066BBEC319E}"/>
   </bookViews>

--- a/TM_all.xlsx
+++ b/TM_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aecf56309e6168f4/Documents/comunio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{541A4631-6AE1-48C0-AD2B-45DD9F4CF406}"/>
+  <xr:revisionPtr revIDLastSave="186" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0C8F75B-CE58-4C61-8AE0-D853AFCD6BA8}"/>
   <bookViews>
     <workbookView xWindow="2110" yWindow="2130" windowWidth="28800" windowHeight="15370" xr2:uid="{607DE709-F91E-4262-9941-1066BBEC319E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4562" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5355" uniqueCount="220">
   <si>
     <t>Spieler</t>
   </si>
@@ -661,6 +661,45 @@
   <si>
     <t>Gomis</t>
   </si>
+  <si>
+    <t>28.05.2025</t>
+  </si>
+  <si>
+    <t>29.05.2025</t>
+  </si>
+  <si>
+    <t>30.05.2025</t>
+  </si>
+  <si>
+    <t>31.05.2025</t>
+  </si>
+  <si>
+    <t>01.06.2025</t>
+  </si>
+  <si>
+    <t>02.06.2025</t>
+  </si>
+  <si>
+    <t>03.06.2025</t>
+  </si>
+  <si>
+    <t>04.06.2025</t>
+  </si>
+  <si>
+    <t>05.06.2025</t>
+  </si>
+  <si>
+    <t>06.06.2025</t>
+  </si>
+  <si>
+    <t>07.06.2025</t>
+  </si>
+  <si>
+    <t>08.06.2025</t>
+  </si>
+  <si>
+    <t>09.06.2025</t>
+  </si>
 </sst>
 </file>
 
@@ -1078,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93EB6F54-7766-4759-97DF-03549A275A7C}">
-  <dimension ref="A1:N794"/>
+  <dimension ref="A1:M794"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="2"/>
@@ -1089,7 +1128,7 @@
     <col min="13" max="16384" width="10.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:13" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1127,7 +1166,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="2" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>87</v>
       </c>
@@ -1145,12 +1184,11 @@
       <c r="L2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="3">
-        <v>45805</v>
-      </c>
-      <c r="N2" s="3"/>
-    </row>
-    <row r="3" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M2" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>195</v>
       </c>
@@ -1168,12 +1206,11 @@
       <c r="L3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="3">
-        <v>45805</v>
-      </c>
-      <c r="N3" s="3"/>
-    </row>
-    <row r="4" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M3" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>114</v>
       </c>
@@ -1191,12 +1228,11 @@
       <c r="L4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="3">
-        <v>45805</v>
-      </c>
-      <c r="N4" s="3"/>
-    </row>
-    <row r="5" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M4" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>196</v>
       </c>
@@ -1214,12 +1250,11 @@
       <c r="L5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="3">
-        <v>45805</v>
-      </c>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>135</v>
       </c>
@@ -1237,12 +1272,11 @@
       <c r="L6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="3">
-        <v>45805</v>
-      </c>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M6" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>197</v>
       </c>
@@ -1260,12 +1294,11 @@
       <c r="L7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="3">
-        <v>45805</v>
-      </c>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M7" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>97</v>
       </c>
@@ -1283,12 +1316,11 @@
       <c r="L8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M8" s="3">
-        <v>45805</v>
-      </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>198</v>
       </c>
@@ -1306,12 +1338,11 @@
       <c r="L9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M9" s="3">
-        <v>45805</v>
-      </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M9" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>134</v>
       </c>
@@ -1329,12 +1360,11 @@
       <c r="L10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M10" s="3">
-        <v>45805</v>
-      </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M10" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>72</v>
       </c>
@@ -1352,12 +1382,11 @@
       <c r="L11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M11" s="3">
-        <v>45805</v>
-      </c>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M11" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>70</v>
       </c>
@@ -1375,12 +1404,11 @@
       <c r="L12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M12" s="3">
-        <v>45805</v>
-      </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M12" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
@@ -1398,12 +1426,11 @@
       <c r="L13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M13" s="3">
-        <v>45805</v>
-      </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M13" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>199</v>
       </c>
@@ -1421,12 +1448,11 @@
       <c r="L14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M14" s="3">
-        <v>45805</v>
-      </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M14" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>146</v>
       </c>
@@ -1444,12 +1470,11 @@
       <c r="L15" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M15" s="3">
-        <v>45806</v>
-      </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M15" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>200</v>
       </c>
@@ -1467,12 +1492,11 @@
       <c r="L16" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M16" s="3">
-        <v>45806</v>
-      </c>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M16" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>201</v>
       </c>
@@ -1490,12 +1514,11 @@
       <c r="L17" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M17" s="3">
-        <v>45807</v>
-      </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M17" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>182</v>
       </c>
@@ -1513,12 +1536,11 @@
       <c r="L18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M18" s="3">
-        <v>45807</v>
-      </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M18" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>133</v>
       </c>
@@ -1536,12 +1558,11 @@
       <c r="L19" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M19" s="3">
-        <v>45807</v>
-      </c>
-      <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M19" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>46</v>
       </c>
@@ -1559,12 +1580,11 @@
       <c r="L20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M20" s="3">
-        <v>45807</v>
-      </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M20" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>137</v>
       </c>
@@ -1582,12 +1602,11 @@
       <c r="L21" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M21" s="3">
-        <v>45807</v>
-      </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M21" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
         <v>151</v>
       </c>
@@ -1605,12 +1624,11 @@
       <c r="L22" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M22" s="3">
-        <v>45807</v>
-      </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M22" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
         <v>108</v>
       </c>
@@ -1628,12 +1646,11 @@
       <c r="L23" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M23" s="3">
-        <v>45807</v>
-      </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M23" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
         <v>125</v>
       </c>
@@ -1651,12 +1668,11 @@
       <c r="L24" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M24" s="3">
-        <v>45807</v>
-      </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M24" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
         <v>177</v>
       </c>
@@ -1674,12 +1690,11 @@
       <c r="L25" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M25" s="3">
-        <v>45807</v>
-      </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M25" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>132</v>
       </c>
@@ -1697,12 +1712,11 @@
       <c r="L26" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M26" s="3">
-        <v>45808</v>
-      </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M26" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
         <v>178</v>
       </c>
@@ -1720,12 +1734,11 @@
       <c r="L27" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M27" s="3">
-        <v>45808</v>
-      </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M27" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
         <v>87</v>
       </c>
@@ -1743,11 +1756,11 @@
       <c r="L28" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M28" s="3">
-        <v>45806</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M28" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
         <v>195</v>
       </c>
@@ -1765,11 +1778,11 @@
       <c r="L29" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M29" s="3">
-        <v>45806</v>
-      </c>
-    </row>
-    <row r="30" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M29" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
         <v>114</v>
       </c>
@@ -1787,11 +1800,11 @@
       <c r="L30" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M30" s="3">
-        <v>45806</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M30" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
         <v>196</v>
       </c>
@@ -1809,11 +1822,11 @@
       <c r="L31" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M31" s="3">
-        <v>45806</v>
-      </c>
-    </row>
-    <row r="32" spans="2:14" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M31" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
         <v>135</v>
       </c>
@@ -1831,8 +1844,8 @@
       <c r="L32" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M32" s="3">
-        <v>45806</v>
+      <c r="M32" s="3" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="33" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -1853,8 +1866,8 @@
       <c r="L33" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M33" s="3">
-        <v>45806</v>
+      <c r="M33" s="3" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="34" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -1875,8 +1888,8 @@
       <c r="L34" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M34" s="3">
-        <v>45806</v>
+      <c r="M34" s="3" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="35" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -1897,8 +1910,8 @@
       <c r="L35" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M35" s="3">
-        <v>45806</v>
+      <c r="M35" s="3" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="36" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -1919,8 +1932,8 @@
       <c r="L36" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M36" s="3">
-        <v>45806</v>
+      <c r="M36" s="3" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="37" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -1941,8 +1954,8 @@
       <c r="L37" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M37" s="3">
-        <v>45806</v>
+      <c r="M37" s="3" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="38" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -1963,8 +1976,8 @@
       <c r="L38" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M38" s="3">
-        <v>45806</v>
+      <c r="M38" s="3" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="39" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -1985,8 +1998,8 @@
       <c r="L39" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M39" s="3">
-        <v>45806</v>
+      <c r="M39" s="3" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="40" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2007,8 +2020,8 @@
       <c r="L40" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M40" s="3">
-        <v>45806</v>
+      <c r="M40" s="3" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="41" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2029,8 +2042,8 @@
       <c r="L41" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M41" s="3">
-        <v>45807</v>
+      <c r="M41" s="3" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="42" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2051,8 +2064,8 @@
       <c r="L42" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M42" s="3">
-        <v>45807</v>
+      <c r="M42" s="3" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="43" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2073,8 +2086,8 @@
       <c r="L43" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M43" s="3">
-        <v>45808</v>
+      <c r="M43" s="3" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="44" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2095,8 +2108,8 @@
       <c r="L44" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M44" s="3">
-        <v>45808</v>
+      <c r="M44" s="3" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2117,8 +2130,8 @@
       <c r="L45" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M45" s="3">
-        <v>45808</v>
+      <c r="M45" s="3" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2139,8 +2152,8 @@
       <c r="L46" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M46" s="3">
-        <v>45808</v>
+      <c r="M46" s="3" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="47" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2161,8 +2174,8 @@
       <c r="L47" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M47" s="3">
-        <v>45808</v>
+      <c r="M47" s="3" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="48" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2183,8 +2196,8 @@
       <c r="L48" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M48" s="3">
-        <v>45808</v>
+      <c r="M48" s="3" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2205,8 +2218,8 @@
       <c r="L49" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M49" s="3">
-        <v>45808</v>
+      <c r="M49" s="3" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="50" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2227,8 +2240,8 @@
       <c r="L50" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M50" s="3">
-        <v>45808</v>
+      <c r="M50" s="3" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="51" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2249,8 +2262,8 @@
       <c r="L51" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M51" s="3">
-        <v>45808</v>
+      <c r="M51" s="3" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2271,8 +2284,8 @@
       <c r="L52" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M52" s="3">
-        <v>45809</v>
+      <c r="M52" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="53" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2293,8 +2306,8 @@
       <c r="L53" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M53" s="3">
-        <v>45809</v>
+      <c r="M53" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="54" spans="2:13" ht="12.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2331,8 +2344,8 @@
       <c r="L54" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M54" s="3">
-        <v>45809</v>
+      <c r="M54" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="55" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2369,8 +2382,8 @@
       <c r="L55" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M55" s="3">
-        <v>45809</v>
+      <c r="M55" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="56" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2407,8 +2420,8 @@
       <c r="L56" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M56" s="3">
-        <v>45809</v>
+      <c r="M56" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="57" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2445,8 +2458,8 @@
       <c r="L57" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M57" s="3">
-        <v>45809</v>
+      <c r="M57" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="58" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2483,8 +2496,8 @@
       <c r="L58" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M58" s="3">
-        <v>45809</v>
+      <c r="M58" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="59" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2521,8 +2534,8 @@
       <c r="L59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M59" s="3">
-        <v>45809</v>
+      <c r="M59" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="60" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2559,8 +2572,8 @@
       <c r="L60" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M60" s="3">
-        <v>45809</v>
+      <c r="M60" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="61" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2597,8 +2610,8 @@
       <c r="L61" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M61" s="3">
-        <v>45809</v>
+      <c r="M61" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="62" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2635,8 +2648,8 @@
       <c r="L62" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M62" s="3">
-        <v>45809</v>
+      <c r="M62" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="63" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2673,8 +2686,8 @@
       <c r="L63" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M63" s="3">
-        <v>45809</v>
+      <c r="M63" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="64" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2711,8 +2724,8 @@
       <c r="L64" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M64" s="3">
-        <v>45809</v>
+      <c r="M64" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="65" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2749,8 +2762,8 @@
       <c r="L65" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M65" s="3">
-        <v>45809</v>
+      <c r="M65" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="66" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2787,8 +2800,8 @@
       <c r="L66" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M66" s="3">
-        <v>45809</v>
+      <c r="M66" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2825,8 +2838,8 @@
       <c r="L67" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="M67" s="3">
-        <v>45809</v>
+      <c r="M67" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="68" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2863,8 +2876,8 @@
       <c r="L68" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M68" s="3">
-        <v>45809</v>
+      <c r="M68" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="69" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2901,8 +2914,8 @@
       <c r="L69" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M69" s="3">
-        <v>45809</v>
+      <c r="M69" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="70" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2939,8 +2952,8 @@
       <c r="L70" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M70" s="3">
-        <v>45809</v>
+      <c r="M70" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="71" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2977,8 +2990,8 @@
       <c r="L71" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M71" s="3">
-        <v>45809</v>
+      <c r="M71" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="72" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3015,8 +3028,8 @@
       <c r="L72" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M72" s="3">
-        <v>45809</v>
+      <c r="M72" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="73" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3053,8 +3066,8 @@
       <c r="L73" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M73" s="3">
-        <v>45809</v>
+      <c r="M73" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="74" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3091,8 +3104,8 @@
       <c r="L74" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M74" s="3">
-        <v>45809</v>
+      <c r="M74" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="75" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3129,8 +3142,8 @@
       <c r="L75" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M75" s="3">
-        <v>45809</v>
+      <c r="M75" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="76" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3167,8 +3180,8 @@
       <c r="L76" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="M76" s="3">
-        <v>45809</v>
+      <c r="M76" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="77" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3205,8 +3218,8 @@
       <c r="L77" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M77" s="3">
-        <v>45809</v>
+      <c r="M77" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="78" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3243,8 +3256,8 @@
       <c r="L78" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M78" s="3">
-        <v>45809</v>
+      <c r="M78" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="79" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3281,8 +3294,8 @@
       <c r="L79" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="M79" s="3">
-        <v>45809</v>
+      <c r="M79" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="80" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3319,8 +3332,8 @@
       <c r="L80" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M80" s="3">
-        <v>45809</v>
+      <c r="M80" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="81" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3357,8 +3370,8 @@
       <c r="L81" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M81" s="3">
-        <v>45809</v>
+      <c r="M81" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="82" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3395,8 +3408,8 @@
       <c r="L82" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M82" s="3">
-        <v>45809</v>
+      <c r="M82" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="83" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3433,8 +3446,8 @@
       <c r="L83" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M83" s="3">
-        <v>45809</v>
+      <c r="M83" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="84" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3471,8 +3484,8 @@
       <c r="L84" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M84" s="3">
-        <v>45809</v>
+      <c r="M84" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="85" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3509,8 +3522,8 @@
       <c r="L85" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M85" s="3">
-        <v>45809</v>
+      <c r="M85" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="86" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3547,8 +3560,8 @@
       <c r="L86" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M86" s="3">
-        <v>45809</v>
+      <c r="M86" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="87" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3585,8 +3598,8 @@
       <c r="L87" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M87" s="3">
-        <v>45809</v>
+      <c r="M87" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="88" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3623,8 +3636,8 @@
       <c r="L88" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M88" s="3">
-        <v>45809</v>
+      <c r="M88" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="89" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3661,8 +3674,8 @@
       <c r="L89" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M89" s="3">
-        <v>45809</v>
+      <c r="M89" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="90" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3699,8 +3712,8 @@
       <c r="L90" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M90" s="3">
-        <v>45809</v>
+      <c r="M90" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="91" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3737,8 +3750,8 @@
       <c r="L91" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M91" s="3">
-        <v>45809</v>
+      <c r="M91" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="92" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3775,8 +3788,8 @@
       <c r="L92" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M92" s="3">
-        <v>45809</v>
+      <c r="M92" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="93" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3813,8 +3826,8 @@
       <c r="L93" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M93" s="3">
-        <v>45809</v>
+      <c r="M93" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="94" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3851,8 +3864,8 @@
       <c r="L94" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M94" s="3">
-        <v>45809</v>
+      <c r="M94" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="95" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3889,8 +3902,8 @@
       <c r="L95" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="M95" s="3">
-        <v>45809</v>
+      <c r="M95" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="96" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3927,8 +3940,8 @@
       <c r="L96" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M96" s="3">
-        <v>45809</v>
+      <c r="M96" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="97" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -3965,8 +3978,8 @@
       <c r="L97" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M97" s="3">
-        <v>45809</v>
+      <c r="M97" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="98" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4003,8 +4016,8 @@
       <c r="L98" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M98" s="3">
-        <v>45809</v>
+      <c r="M98" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="99" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4041,8 +4054,8 @@
       <c r="L99" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M99" s="3">
-        <v>45809</v>
+      <c r="M99" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="100" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4079,8 +4092,8 @@
       <c r="L100" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M100" s="3">
-        <v>45809</v>
+      <c r="M100" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="101" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4117,8 +4130,8 @@
       <c r="L101" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="M101" s="3">
-        <v>45809</v>
+      <c r="M101" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="102" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4155,8 +4168,8 @@
       <c r="L102" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M102" s="3">
-        <v>45809</v>
+      <c r="M102" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="103" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4193,8 +4206,8 @@
       <c r="L103" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M103" s="3">
-        <v>45809</v>
+      <c r="M103" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="104" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4231,8 +4244,8 @@
       <c r="L104" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M104" s="3">
-        <v>45809</v>
+      <c r="M104" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="105" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4269,8 +4282,8 @@
       <c r="L105" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="M105" s="3">
-        <v>45809</v>
+      <c r="M105" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="106" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4307,8 +4320,8 @@
       <c r="L106" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M106" s="3">
-        <v>45809</v>
+      <c r="M106" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="107" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4345,8 +4358,8 @@
       <c r="L107" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M107" s="3">
-        <v>45809</v>
+      <c r="M107" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="108" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4383,8 +4396,8 @@
       <c r="L108" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M108" s="3">
-        <v>45809</v>
+      <c r="M108" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="109" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4421,8 +4434,8 @@
       <c r="L109" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M109" s="3">
-        <v>45809</v>
+      <c r="M109" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="110" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4459,8 +4472,8 @@
       <c r="L110" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M110" s="3">
-        <v>45809</v>
+      <c r="M110" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="111" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4497,8 +4510,8 @@
       <c r="L111" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M111" s="3">
-        <v>45809</v>
+      <c r="M111" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="112" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4535,8 +4548,8 @@
       <c r="L112" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M112" s="3">
-        <v>45809</v>
+      <c r="M112" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="113" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4573,8 +4586,8 @@
       <c r="L113" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M113" s="3">
-        <v>45809</v>
+      <c r="M113" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="114" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4611,8 +4624,8 @@
       <c r="L114" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M114" s="3">
-        <v>45809</v>
+      <c r="M114" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="115" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4649,8 +4662,8 @@
       <c r="L115" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M115" s="3">
-        <v>45809</v>
+      <c r="M115" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="116" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4687,8 +4700,8 @@
       <c r="L116" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="M116" s="3">
-        <v>45809</v>
+      <c r="M116" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="117" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4725,8 +4738,8 @@
       <c r="L117" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M117" s="3">
-        <v>45809</v>
+      <c r="M117" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="118" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4763,8 +4776,8 @@
       <c r="L118" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M118" s="3">
-        <v>45809</v>
+      <c r="M118" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="119" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4801,8 +4814,8 @@
       <c r="L119" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M119" s="3">
-        <v>45809</v>
+      <c r="M119" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="120" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4839,8 +4852,8 @@
       <c r="L120" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="M120" s="3">
-        <v>45809</v>
+      <c r="M120" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="121" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4877,8 +4890,8 @@
       <c r="L121" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M121" s="3">
-        <v>45809</v>
+      <c r="M121" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="122" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4915,8 +4928,8 @@
       <c r="L122" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M122" s="3">
-        <v>45809</v>
+      <c r="M122" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="123" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4953,8 +4966,8 @@
       <c r="L123" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M123" s="3">
-        <v>45809</v>
+      <c r="M123" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="124" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -4991,8 +5004,8 @@
       <c r="L124" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M124" s="3">
-        <v>45809</v>
+      <c r="M124" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -5029,8 +5042,8 @@
       <c r="L125" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M125" s="3">
-        <v>45809</v>
+      <c r="M125" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="126" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -5067,8 +5080,8 @@
       <c r="L126" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M126" s="3">
-        <v>45809</v>
+      <c r="M126" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="127" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -5105,8 +5118,8 @@
       <c r="L127" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M127" s="3">
-        <v>45809</v>
+      <c r="M127" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="128" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -5143,8 +5156,8 @@
       <c r="L128" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M128" s="3">
-        <v>45809</v>
+      <c r="M128" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="129" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -5181,8 +5194,8 @@
       <c r="L129" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M129" s="3">
-        <v>45809</v>
+      <c r="M129" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="130" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -5219,8 +5232,8 @@
       <c r="L130" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M130" s="3">
-        <v>45809</v>
+      <c r="M130" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="131" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -5257,8 +5270,8 @@
       <c r="L131" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M131" s="3">
-        <v>45809</v>
+      <c r="M131" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="132" spans="2:13" x14ac:dyDescent="0.25">
@@ -5295,8 +5308,8 @@
       <c r="L132" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M132" s="3">
-        <v>45809</v>
+      <c r="M132" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="133" spans="2:13" x14ac:dyDescent="0.25">
@@ -5333,8 +5346,8 @@
       <c r="L133" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M133" s="3">
-        <v>45809</v>
+      <c r="M133" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="134" spans="2:13" x14ac:dyDescent="0.25">
@@ -5371,8 +5384,8 @@
       <c r="L134" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="M134" s="3">
-        <v>45809</v>
+      <c r="M134" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="135" spans="2:13" x14ac:dyDescent="0.25">
@@ -5409,8 +5422,8 @@
       <c r="L135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M135" s="3">
-        <v>45810</v>
+      <c r="M135" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="136" spans="2:13" x14ac:dyDescent="0.25">
@@ -5447,8 +5460,8 @@
       <c r="L136" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M136" s="3">
-        <v>45810</v>
+      <c r="M136" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="137" spans="2:13" x14ac:dyDescent="0.25">
@@ -5485,8 +5498,8 @@
       <c r="L137" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M137" s="3">
-        <v>45810</v>
+      <c r="M137" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="138" spans="2:13" x14ac:dyDescent="0.25">
@@ -5523,8 +5536,8 @@
       <c r="L138" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M138" s="3">
-        <v>45810</v>
+      <c r="M138" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="139" spans="2:13" x14ac:dyDescent="0.25">
@@ -5561,8 +5574,8 @@
       <c r="L139" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M139" s="3">
-        <v>45810</v>
+      <c r="M139" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="140" spans="2:13" x14ac:dyDescent="0.25">
@@ -5599,8 +5612,8 @@
       <c r="L140" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M140" s="3">
-        <v>45810</v>
+      <c r="M140" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="141" spans="2:13" x14ac:dyDescent="0.25">
@@ -5637,8 +5650,8 @@
       <c r="L141" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M141" s="3">
-        <v>45810</v>
+      <c r="M141" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="142" spans="2:13" x14ac:dyDescent="0.25">
@@ -5675,8 +5688,8 @@
       <c r="L142" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M142" s="3">
-        <v>45810</v>
+      <c r="M142" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="143" spans="2:13" x14ac:dyDescent="0.25">
@@ -5713,8 +5726,8 @@
       <c r="L143" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M143" s="3">
-        <v>45810</v>
+      <c r="M143" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="144" spans="2:13" x14ac:dyDescent="0.25">
@@ -5751,8 +5764,8 @@
       <c r="L144" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M144" s="3">
-        <v>45810</v>
+      <c r="M144" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="145" spans="2:13" x14ac:dyDescent="0.25">
@@ -5789,8 +5802,8 @@
       <c r="L145" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M145" s="3">
-        <v>45810</v>
+      <c r="M145" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="146" spans="2:13" x14ac:dyDescent="0.25">
@@ -5827,8 +5840,8 @@
       <c r="L146" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M146" s="3">
-        <v>45810</v>
+      <c r="M146" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="147" spans="2:13" x14ac:dyDescent="0.25">
@@ -5865,8 +5878,8 @@
       <c r="L147" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M147" s="3">
-        <v>45810</v>
+      <c r="M147" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="148" spans="2:13" x14ac:dyDescent="0.25">
@@ -5903,8 +5916,8 @@
       <c r="L148" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="M148" s="3">
-        <v>45810</v>
+      <c r="M148" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="149" spans="2:13" x14ac:dyDescent="0.25">
@@ -5941,8 +5954,8 @@
       <c r="L149" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M149" s="3">
-        <v>45810</v>
+      <c r="M149" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="150" spans="2:13" x14ac:dyDescent="0.25">
@@ -5979,8 +5992,8 @@
       <c r="L150" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M150" s="3">
-        <v>45810</v>
+      <c r="M150" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="151" spans="2:13" x14ac:dyDescent="0.25">
@@ -6017,8 +6030,8 @@
       <c r="L151" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M151" s="3">
-        <v>45810</v>
+      <c r="M151" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="152" spans="2:13" x14ac:dyDescent="0.25">
@@ -6055,8 +6068,8 @@
       <c r="L152" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M152" s="3">
-        <v>45810</v>
+      <c r="M152" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="153" spans="2:13" x14ac:dyDescent="0.25">
@@ -6093,8 +6106,8 @@
       <c r="L153" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M153" s="3">
-        <v>45810</v>
+      <c r="M153" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="154" spans="2:13" x14ac:dyDescent="0.25">
@@ -6131,8 +6144,8 @@
       <c r="L154" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M154" s="3">
-        <v>45810</v>
+      <c r="M154" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="155" spans="2:13" x14ac:dyDescent="0.25">
@@ -6169,8 +6182,8 @@
       <c r="L155" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M155" s="3">
-        <v>45810</v>
+      <c r="M155" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="156" spans="2:13" x14ac:dyDescent="0.25">
@@ -6207,8 +6220,8 @@
       <c r="L156" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M156" s="3">
-        <v>45810</v>
+      <c r="M156" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="157" spans="2:13" x14ac:dyDescent="0.25">
@@ -6245,8 +6258,8 @@
       <c r="L157" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M157" s="3">
-        <v>45810</v>
+      <c r="M157" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="158" spans="2:13" x14ac:dyDescent="0.25">
@@ -6283,8 +6296,8 @@
       <c r="L158" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M158" s="3">
-        <v>45810</v>
+      <c r="M158" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="159" spans="2:13" x14ac:dyDescent="0.25">
@@ -6321,8 +6334,8 @@
       <c r="L159" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M159" s="3">
-        <v>45810</v>
+      <c r="M159" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="160" spans="2:13" x14ac:dyDescent="0.25">
@@ -6359,8 +6372,8 @@
       <c r="L160" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M160" s="3">
-        <v>45810</v>
+      <c r="M160" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="161" spans="2:13" x14ac:dyDescent="0.25">
@@ -6397,8 +6410,8 @@
       <c r="L161" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M161" s="3">
-        <v>45810</v>
+      <c r="M161" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="162" spans="2:13" x14ac:dyDescent="0.25">
@@ -6435,8 +6448,8 @@
       <c r="L162" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M162" s="3">
-        <v>45810</v>
+      <c r="M162" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="163" spans="2:13" x14ac:dyDescent="0.25">
@@ -6473,8 +6486,8 @@
       <c r="L163" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M163" s="3">
-        <v>45810</v>
+      <c r="M163" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="164" spans="2:13" x14ac:dyDescent="0.25">
@@ -6511,8 +6524,8 @@
       <c r="L164" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M164" s="3">
-        <v>45810</v>
+      <c r="M164" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="165" spans="2:13" x14ac:dyDescent="0.25">
@@ -6549,8 +6562,8 @@
       <c r="L165" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M165" s="3">
-        <v>45810</v>
+      <c r="M165" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="166" spans="2:13" x14ac:dyDescent="0.25">
@@ -6587,8 +6600,8 @@
       <c r="L166" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M166" s="3">
-        <v>45810</v>
+      <c r="M166" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="167" spans="2:13" x14ac:dyDescent="0.25">
@@ -6625,8 +6638,8 @@
       <c r="L167" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M167" s="3">
-        <v>45810</v>
+      <c r="M167" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="168" spans="2:13" x14ac:dyDescent="0.25">
@@ -6663,8 +6676,8 @@
       <c r="L168" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M168" s="3">
-        <v>45810</v>
+      <c r="M168" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="169" spans="2:13" x14ac:dyDescent="0.25">
@@ -6701,8 +6714,8 @@
       <c r="L169" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M169" s="3">
-        <v>45810</v>
+      <c r="M169" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="170" spans="2:13" x14ac:dyDescent="0.25">
@@ -6739,8 +6752,8 @@
       <c r="L170" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M170" s="3">
-        <v>45810</v>
+      <c r="M170" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="171" spans="2:13" x14ac:dyDescent="0.25">
@@ -6777,8 +6790,8 @@
       <c r="L171" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M171" s="3">
-        <v>45810</v>
+      <c r="M171" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="172" spans="2:13" x14ac:dyDescent="0.25">
@@ -6815,8 +6828,8 @@
       <c r="L172" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M172" s="3">
-        <v>45810</v>
+      <c r="M172" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="173" spans="2:13" x14ac:dyDescent="0.25">
@@ -6853,8 +6866,8 @@
       <c r="L173" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M173" s="3">
-        <v>45810</v>
+      <c r="M173" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="174" spans="2:13" x14ac:dyDescent="0.25">
@@ -6891,8 +6904,8 @@
       <c r="L174" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M174" s="3">
-        <v>45810</v>
+      <c r="M174" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="175" spans="2:13" x14ac:dyDescent="0.25">
@@ -6929,8 +6942,8 @@
       <c r="L175" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M175" s="3">
-        <v>45810</v>
+      <c r="M175" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="176" spans="2:13" x14ac:dyDescent="0.25">
@@ -6967,8 +6980,8 @@
       <c r="L176" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M176" s="3">
-        <v>45810</v>
+      <c r="M176" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="177" spans="2:13" x14ac:dyDescent="0.25">
@@ -7005,8 +7018,8 @@
       <c r="L177" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M177" s="3">
-        <v>45810</v>
+      <c r="M177" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="178" spans="2:13" x14ac:dyDescent="0.25">
@@ -7043,8 +7056,8 @@
       <c r="L178" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M178" s="3">
-        <v>45810</v>
+      <c r="M178" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="179" spans="2:13" x14ac:dyDescent="0.25">
@@ -7081,8 +7094,8 @@
       <c r="L179" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M179" s="3">
-        <v>45810</v>
+      <c r="M179" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="180" spans="2:13" x14ac:dyDescent="0.25">
@@ -7119,8 +7132,8 @@
       <c r="L180" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M180" s="3">
-        <v>45810</v>
+      <c r="M180" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="181" spans="2:13" x14ac:dyDescent="0.25">
@@ -7157,8 +7170,8 @@
       <c r="L181" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M181" s="3">
-        <v>45810</v>
+      <c r="M181" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="182" spans="2:13" x14ac:dyDescent="0.25">
@@ -7195,8 +7208,8 @@
       <c r="L182" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M182" s="3">
-        <v>45810</v>
+      <c r="M182" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="183" spans="2:13" x14ac:dyDescent="0.25">
@@ -7233,8 +7246,8 @@
       <c r="L183" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M183" s="3">
-        <v>45810</v>
+      <c r="M183" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="184" spans="2:13" x14ac:dyDescent="0.25">
@@ -7271,8 +7284,8 @@
       <c r="L184" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M184" s="3">
-        <v>45810</v>
+      <c r="M184" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="185" spans="2:13" x14ac:dyDescent="0.25">
@@ -7309,8 +7322,8 @@
       <c r="L185" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M185" s="3">
-        <v>45810</v>
+      <c r="M185" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="186" spans="2:13" x14ac:dyDescent="0.25">
@@ -7347,8 +7360,8 @@
       <c r="L186" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M186" s="3">
-        <v>45810</v>
+      <c r="M186" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="187" spans="2:13" x14ac:dyDescent="0.25">
@@ -7385,8 +7398,8 @@
       <c r="L187" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M187" s="3">
-        <v>45810</v>
+      <c r="M187" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="188" spans="2:13" x14ac:dyDescent="0.25">
@@ -7423,8 +7436,8 @@
       <c r="L188" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M188" s="3">
-        <v>45810</v>
+      <c r="M188" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="189" spans="2:13" x14ac:dyDescent="0.25">
@@ -7461,8 +7474,8 @@
       <c r="L189" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M189" s="3">
-        <v>45810</v>
+      <c r="M189" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="190" spans="2:13" x14ac:dyDescent="0.25">
@@ -7499,8 +7512,8 @@
       <c r="L190" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M190" s="3">
-        <v>45810</v>
+      <c r="M190" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="191" spans="2:13" x14ac:dyDescent="0.25">
@@ -7537,8 +7550,8 @@
       <c r="L191" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M191" s="3">
-        <v>45810</v>
+      <c r="M191" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="192" spans="2:13" x14ac:dyDescent="0.25">
@@ -7575,8 +7588,8 @@
       <c r="L192" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M192" s="3">
-        <v>45810</v>
+      <c r="M192" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="193" spans="2:13" x14ac:dyDescent="0.25">
@@ -7613,8 +7626,8 @@
       <c r="L193" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M193" s="3">
-        <v>45810</v>
+      <c r="M193" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="194" spans="2:13" x14ac:dyDescent="0.25">
@@ -7651,8 +7664,8 @@
       <c r="L194" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M194" s="3">
-        <v>45810</v>
+      <c r="M194" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="195" spans="2:13" x14ac:dyDescent="0.25">
@@ -7689,8 +7702,8 @@
       <c r="L195" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M195" s="3">
-        <v>45810</v>
+      <c r="M195" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="196" spans="2:13" x14ac:dyDescent="0.25">
@@ -7727,8 +7740,8 @@
       <c r="L196" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M196" s="3">
-        <v>45810</v>
+      <c r="M196" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="197" spans="2:13" x14ac:dyDescent="0.25">
@@ -7765,8 +7778,8 @@
       <c r="L197" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M197" s="3">
-        <v>45810</v>
+      <c r="M197" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="198" spans="2:13" x14ac:dyDescent="0.25">
@@ -7803,8 +7816,8 @@
       <c r="L198" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M198" s="3">
-        <v>45810</v>
+      <c r="M198" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="199" spans="2:13" x14ac:dyDescent="0.25">
@@ -7841,8 +7854,8 @@
       <c r="L199" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M199" s="3">
-        <v>45810</v>
+      <c r="M199" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="200" spans="2:13" x14ac:dyDescent="0.25">
@@ -7879,8 +7892,8 @@
       <c r="L200" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M200" s="3">
-        <v>45810</v>
+      <c r="M200" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="201" spans="2:13" x14ac:dyDescent="0.25">
@@ -7917,8 +7930,8 @@
       <c r="L201" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M201" s="3">
-        <v>45810</v>
+      <c r="M201" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="202" spans="2:13" x14ac:dyDescent="0.25">
@@ -7955,8 +7968,8 @@
       <c r="L202" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M202" s="3">
-        <v>45810</v>
+      <c r="M202" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="203" spans="2:13" x14ac:dyDescent="0.25">
@@ -7993,8 +8006,8 @@
       <c r="L203" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M203" s="3">
-        <v>45810</v>
+      <c r="M203" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="204" spans="2:13" x14ac:dyDescent="0.25">
@@ -8031,8 +8044,8 @@
       <c r="L204" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M204" s="3">
-        <v>45810</v>
+      <c r="M204" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="205" spans="2:13" x14ac:dyDescent="0.25">
@@ -8069,8 +8082,8 @@
       <c r="L205" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M205" s="3">
-        <v>45810</v>
+      <c r="M205" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="206" spans="2:13" x14ac:dyDescent="0.25">
@@ -8107,8 +8120,8 @@
       <c r="L206" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M206" s="3">
-        <v>45810</v>
+      <c r="M206" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="207" spans="2:13" x14ac:dyDescent="0.25">
@@ -8145,8 +8158,8 @@
       <c r="L207" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M207" s="3">
-        <v>45810</v>
+      <c r="M207" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="208" spans="2:13" x14ac:dyDescent="0.25">
@@ -8183,8 +8196,8 @@
       <c r="L208" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M208" s="3">
-        <v>45810</v>
+      <c r="M208" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="209" spans="2:13" x14ac:dyDescent="0.25">
@@ -8221,8 +8234,8 @@
       <c r="L209" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M209" s="3">
-        <v>45810</v>
+      <c r="M209" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="210" spans="2:13" x14ac:dyDescent="0.25">
@@ -8259,8 +8272,8 @@
       <c r="L210" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M210" s="3">
-        <v>45810</v>
+      <c r="M210" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="211" spans="2:13" x14ac:dyDescent="0.25">
@@ -8297,8 +8310,8 @@
       <c r="L211" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M211" s="3">
-        <v>45810</v>
+      <c r="M211" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="212" spans="2:13" x14ac:dyDescent="0.25">
@@ -8335,8 +8348,8 @@
       <c r="L212" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M212" s="3">
-        <v>45810</v>
+      <c r="M212" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="213" spans="2:13" x14ac:dyDescent="0.25">
@@ -8373,8 +8386,8 @@
       <c r="L213" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M213" s="3">
-        <v>45810</v>
+      <c r="M213" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="214" spans="2:13" x14ac:dyDescent="0.25">
@@ -8411,8 +8424,8 @@
       <c r="L214" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M214" s="3">
-        <v>45810</v>
+      <c r="M214" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="215" spans="2:13" x14ac:dyDescent="0.25">
@@ -8449,8 +8462,8 @@
       <c r="L215" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M215" s="3">
-        <v>45810</v>
+      <c r="M215" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="216" spans="2:13" x14ac:dyDescent="0.25">
@@ -8487,8 +8500,8 @@
       <c r="L216" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M216" s="3">
-        <v>45810</v>
+      <c r="M216" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="217" spans="2:13" x14ac:dyDescent="0.25">
@@ -8525,8 +8538,8 @@
       <c r="L217" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M217" s="3">
-        <v>45810</v>
+      <c r="M217" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="218" spans="2:13" x14ac:dyDescent="0.25">
@@ -8563,8 +8576,8 @@
       <c r="L218" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M218" s="3">
-        <v>45810</v>
+      <c r="M218" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="219" spans="2:13" x14ac:dyDescent="0.25">
@@ -8601,8 +8614,8 @@
       <c r="L219" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="M219" s="3">
-        <v>45810</v>
+      <c r="M219" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="220" spans="2:13" x14ac:dyDescent="0.25">
@@ -8639,8 +8652,8 @@
       <c r="L220" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M220" s="3">
-        <v>45811</v>
+      <c r="M220" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="221" spans="2:13" x14ac:dyDescent="0.25">
@@ -8677,8 +8690,8 @@
       <c r="L221" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M221" s="3">
-        <v>45811</v>
+      <c r="M221" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="222" spans="2:13" x14ac:dyDescent="0.25">
@@ -8715,8 +8728,8 @@
       <c r="L222" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M222" s="3">
-        <v>45811</v>
+      <c r="M222" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="223" spans="2:13" x14ac:dyDescent="0.25">
@@ -8753,8 +8766,8 @@
       <c r="L223" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M223" s="3">
-        <v>45811</v>
+      <c r="M223" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="224" spans="2:13" x14ac:dyDescent="0.25">
@@ -8791,8 +8804,8 @@
       <c r="L224" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M224" s="3">
-        <v>45811</v>
+      <c r="M224" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="225" spans="2:13" x14ac:dyDescent="0.25">
@@ -8829,8 +8842,8 @@
       <c r="L225" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M225" s="3">
-        <v>45811</v>
+      <c r="M225" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="226" spans="2:13" x14ac:dyDescent="0.25">
@@ -8867,8 +8880,8 @@
       <c r="L226" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M226" s="3">
-        <v>45811</v>
+      <c r="M226" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="227" spans="2:13" x14ac:dyDescent="0.25">
@@ -8905,8 +8918,8 @@
       <c r="L227" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M227" s="3">
-        <v>45811</v>
+      <c r="M227" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="228" spans="2:13" x14ac:dyDescent="0.25">
@@ -8943,8 +8956,8 @@
       <c r="L228" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M228" s="3">
-        <v>45811</v>
+      <c r="M228" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="229" spans="2:13" x14ac:dyDescent="0.25">
@@ -8981,8 +8994,8 @@
       <c r="L229" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M229" s="3">
-        <v>45811</v>
+      <c r="M229" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="230" spans="2:13" x14ac:dyDescent="0.25">
@@ -9019,8 +9032,8 @@
       <c r="L230" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M230" s="3">
-        <v>45811</v>
+      <c r="M230" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="231" spans="2:13" x14ac:dyDescent="0.25">
@@ -9057,8 +9070,8 @@
       <c r="L231" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M231" s="3">
-        <v>45811</v>
+      <c r="M231" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="232" spans="2:13" x14ac:dyDescent="0.25">
@@ -9095,8 +9108,8 @@
       <c r="L232" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M232" s="3">
-        <v>45811</v>
+      <c r="M232" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="233" spans="2:13" x14ac:dyDescent="0.25">
@@ -9133,8 +9146,8 @@
       <c r="L233" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M233" s="3">
-        <v>45811</v>
+      <c r="M233" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="234" spans="2:13" x14ac:dyDescent="0.25">
@@ -9171,8 +9184,8 @@
       <c r="L234" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M234" s="3">
-        <v>45811</v>
+      <c r="M234" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="235" spans="2:13" x14ac:dyDescent="0.25">
@@ -9209,8 +9222,8 @@
       <c r="L235" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M235" s="3">
-        <v>45811</v>
+      <c r="M235" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="236" spans="2:13" x14ac:dyDescent="0.25">
@@ -9247,8 +9260,8 @@
       <c r="L236" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M236" s="3">
-        <v>45811</v>
+      <c r="M236" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="237" spans="2:13" x14ac:dyDescent="0.25">
@@ -9285,8 +9298,8 @@
       <c r="L237" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M237" s="3">
-        <v>45811</v>
+      <c r="M237" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="238" spans="2:13" x14ac:dyDescent="0.25">
@@ -9323,8 +9336,8 @@
       <c r="L238" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M238" s="3">
-        <v>45811</v>
+      <c r="M238" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="239" spans="2:13" x14ac:dyDescent="0.25">
@@ -9361,8 +9374,8 @@
       <c r="L239" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M239" s="3">
-        <v>45811</v>
+      <c r="M239" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="240" spans="2:13" x14ac:dyDescent="0.25">
@@ -9399,8 +9412,8 @@
       <c r="L240" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M240" s="3">
-        <v>45811</v>
+      <c r="M240" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="241" spans="2:13" x14ac:dyDescent="0.25">
@@ -9437,8 +9450,8 @@
       <c r="L241" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M241" s="3">
-        <v>45811</v>
+      <c r="M241" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="242" spans="2:13" x14ac:dyDescent="0.25">
@@ -9475,8 +9488,8 @@
       <c r="L242" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M242" s="3">
-        <v>45811</v>
+      <c r="M242" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="243" spans="2:13" x14ac:dyDescent="0.25">
@@ -9513,8 +9526,8 @@
       <c r="L243" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M243" s="3">
-        <v>45811</v>
+      <c r="M243" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="244" spans="2:13" x14ac:dyDescent="0.25">
@@ -9551,8 +9564,8 @@
       <c r="L244" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M244" s="3">
-        <v>45811</v>
+      <c r="M244" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="245" spans="2:13" x14ac:dyDescent="0.25">
@@ -9589,8 +9602,8 @@
       <c r="L245" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M245" s="3">
-        <v>45811</v>
+      <c r="M245" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="246" spans="2:13" x14ac:dyDescent="0.25">
@@ -9627,8 +9640,8 @@
       <c r="L246" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M246" s="3">
-        <v>45811</v>
+      <c r="M246" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="247" spans="2:13" x14ac:dyDescent="0.25">
@@ -9665,8 +9678,8 @@
       <c r="L247" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M247" s="3">
-        <v>45811</v>
+      <c r="M247" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="248" spans="2:13" x14ac:dyDescent="0.25">
@@ -9703,8 +9716,8 @@
       <c r="L248" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M248" s="3">
-        <v>45811</v>
+      <c r="M248" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="249" spans="2:13" x14ac:dyDescent="0.25">
@@ -9741,8 +9754,8 @@
       <c r="L249" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M249" s="3">
-        <v>45811</v>
+      <c r="M249" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="250" spans="2:13" x14ac:dyDescent="0.25">
@@ -9779,8 +9792,8 @@
       <c r="L250" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M250" s="3">
-        <v>45811</v>
+      <c r="M250" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="251" spans="2:13" x14ac:dyDescent="0.25">
@@ -9817,8 +9830,8 @@
       <c r="L251" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M251" s="3">
-        <v>45811</v>
+      <c r="M251" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="252" spans="2:13" x14ac:dyDescent="0.25">
@@ -9855,8 +9868,8 @@
       <c r="L252" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M252" s="3">
-        <v>45811</v>
+      <c r="M252" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="253" spans="2:13" x14ac:dyDescent="0.25">
@@ -9893,8 +9906,8 @@
       <c r="L253" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M253" s="3">
-        <v>45811</v>
+      <c r="M253" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="254" spans="2:13" x14ac:dyDescent="0.25">
@@ -9931,8 +9944,8 @@
       <c r="L254" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M254" s="3">
-        <v>45811</v>
+      <c r="M254" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="255" spans="2:13" x14ac:dyDescent="0.25">
@@ -9969,8 +9982,8 @@
       <c r="L255" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M255" s="3">
-        <v>45811</v>
+      <c r="M255" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="256" spans="2:13" x14ac:dyDescent="0.25">
@@ -10007,8 +10020,8 @@
       <c r="L256" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M256" s="3">
-        <v>45811</v>
+      <c r="M256" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="257" spans="2:13" x14ac:dyDescent="0.25">
@@ -10045,8 +10058,8 @@
       <c r="L257" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M257" s="3">
-        <v>45811</v>
+      <c r="M257" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="258" spans="2:13" x14ac:dyDescent="0.25">
@@ -10083,8 +10096,8 @@
       <c r="L258" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M258" s="3">
-        <v>45811</v>
+      <c r="M258" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="259" spans="2:13" x14ac:dyDescent="0.25">
@@ -10121,8 +10134,8 @@
       <c r="L259" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M259" s="3">
-        <v>45811</v>
+      <c r="M259" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="260" spans="2:13" x14ac:dyDescent="0.25">
@@ -10159,8 +10172,8 @@
       <c r="L260" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M260" s="3">
-        <v>45811</v>
+      <c r="M260" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="261" spans="2:13" x14ac:dyDescent="0.25">
@@ -10197,8 +10210,8 @@
       <c r="L261" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="M261" s="3">
-        <v>45811</v>
+      <c r="M261" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="262" spans="2:13" x14ac:dyDescent="0.25">
@@ -10235,8 +10248,8 @@
       <c r="L262" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M262" s="3">
-        <v>45811</v>
+      <c r="M262" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="263" spans="2:13" x14ac:dyDescent="0.25">
@@ -10273,8 +10286,8 @@
       <c r="L263" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M263" s="3">
-        <v>45811</v>
+      <c r="M263" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="264" spans="2:13" x14ac:dyDescent="0.25">
@@ -10311,8 +10324,8 @@
       <c r="L264" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M264" s="3">
-        <v>45811</v>
+      <c r="M264" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="265" spans="2:13" x14ac:dyDescent="0.25">
@@ -10349,8 +10362,8 @@
       <c r="L265" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M265" s="3">
-        <v>45811</v>
+      <c r="M265" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="266" spans="2:13" x14ac:dyDescent="0.25">
@@ -10387,8 +10400,8 @@
       <c r="L266" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M266" s="3">
-        <v>45811</v>
+      <c r="M266" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="267" spans="2:13" x14ac:dyDescent="0.25">
@@ -10425,8 +10438,8 @@
       <c r="L267" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M267" s="3">
-        <v>45811</v>
+      <c r="M267" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="268" spans="2:13" x14ac:dyDescent="0.25">
@@ -10463,8 +10476,8 @@
       <c r="L268" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M268" s="3">
-        <v>45811</v>
+      <c r="M268" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="269" spans="2:13" x14ac:dyDescent="0.25">
@@ -10501,8 +10514,8 @@
       <c r="L269" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M269" s="3">
-        <v>45811</v>
+      <c r="M269" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="270" spans="2:13" x14ac:dyDescent="0.25">
@@ -10539,8 +10552,8 @@
       <c r="L270" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M270" s="3">
-        <v>45811</v>
+      <c r="M270" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="271" spans="2:13" x14ac:dyDescent="0.25">
@@ -10577,8 +10590,8 @@
       <c r="L271" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M271" s="3">
-        <v>45811</v>
+      <c r="M271" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="272" spans="2:13" x14ac:dyDescent="0.25">
@@ -10615,8 +10628,8 @@
       <c r="L272" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M272" s="3">
-        <v>45811</v>
+      <c r="M272" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="273" spans="2:13" x14ac:dyDescent="0.25">
@@ -10653,8 +10666,8 @@
       <c r="L273" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M273" s="3">
-        <v>45811</v>
+      <c r="M273" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="274" spans="2:13" x14ac:dyDescent="0.25">
@@ -10691,8 +10704,8 @@
       <c r="L274" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M274" s="3">
-        <v>45811</v>
+      <c r="M274" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="275" spans="2:13" x14ac:dyDescent="0.25">
@@ -10729,8 +10742,8 @@
       <c r="L275" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M275" s="3">
-        <v>45811</v>
+      <c r="M275" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="276" spans="2:13" x14ac:dyDescent="0.25">
@@ -10767,8 +10780,8 @@
       <c r="L276" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M276" s="3">
-        <v>45811</v>
+      <c r="M276" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="277" spans="2:13" x14ac:dyDescent="0.25">
@@ -10805,8 +10818,8 @@
       <c r="L277" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M277" s="3">
-        <v>45811</v>
+      <c r="M277" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="278" spans="2:13" x14ac:dyDescent="0.25">
@@ -10843,8 +10856,8 @@
       <c r="L278" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M278" s="3">
-        <v>45811</v>
+      <c r="M278" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="279" spans="2:13" x14ac:dyDescent="0.25">
@@ -10881,8 +10894,8 @@
       <c r="L279" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M279" s="3">
-        <v>45811</v>
+      <c r="M279" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="280" spans="2:13" x14ac:dyDescent="0.25">
@@ -10919,8 +10932,8 @@
       <c r="L280" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M280" s="3">
-        <v>45811</v>
+      <c r="M280" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="281" spans="2:13" x14ac:dyDescent="0.25">
@@ -10957,8 +10970,8 @@
       <c r="L281" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M281" s="3">
-        <v>45811</v>
+      <c r="M281" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="282" spans="2:13" x14ac:dyDescent="0.25">
@@ -10995,8 +11008,8 @@
       <c r="L282" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M282" s="3">
-        <v>45811</v>
+      <c r="M282" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="283" spans="2:13" x14ac:dyDescent="0.25">
@@ -11033,8 +11046,8 @@
       <c r="L283" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M283" s="3">
-        <v>45811</v>
+      <c r="M283" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="284" spans="2:13" x14ac:dyDescent="0.25">
@@ -11071,8 +11084,8 @@
       <c r="L284" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M284" s="3">
-        <v>45811</v>
+      <c r="M284" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="285" spans="2:13" x14ac:dyDescent="0.25">
@@ -11109,8 +11122,8 @@
       <c r="L285" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M285" s="3">
-        <v>45811</v>
+      <c r="M285" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="286" spans="2:13" x14ac:dyDescent="0.25">
@@ -11147,8 +11160,8 @@
       <c r="L286" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M286" s="3">
-        <v>45811</v>
+      <c r="M286" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="287" spans="2:13" x14ac:dyDescent="0.25">
@@ -11185,8 +11198,8 @@
       <c r="L287" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M287" s="3">
-        <v>45811</v>
+      <c r="M287" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="288" spans="2:13" x14ac:dyDescent="0.25">
@@ -11223,8 +11236,8 @@
       <c r="L288" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M288" s="3">
-        <v>45811</v>
+      <c r="M288" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="289" spans="2:13" x14ac:dyDescent="0.25">
@@ -11261,8 +11274,8 @@
       <c r="L289" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M289" s="3">
-        <v>45811</v>
+      <c r="M289" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="290" spans="2:13" x14ac:dyDescent="0.25">
@@ -11299,8 +11312,8 @@
       <c r="L290" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M290" s="3">
-        <v>45811</v>
+      <c r="M290" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="291" spans="2:13" x14ac:dyDescent="0.25">
@@ -11337,8 +11350,8 @@
       <c r="L291" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M291" s="3">
-        <v>45811</v>
+      <c r="M291" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="292" spans="2:13" x14ac:dyDescent="0.25">
@@ -11375,8 +11388,8 @@
       <c r="L292" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M292" s="3">
-        <v>45811</v>
+      <c r="M292" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="293" spans="2:13" x14ac:dyDescent="0.25">
@@ -11413,8 +11426,8 @@
       <c r="L293" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M293" s="3">
-        <v>45811</v>
+      <c r="M293" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="294" spans="2:13" x14ac:dyDescent="0.25">
@@ -11451,8 +11464,8 @@
       <c r="L294" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M294" s="3">
-        <v>45811</v>
+      <c r="M294" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="295" spans="2:13" x14ac:dyDescent="0.25">
@@ -11489,8 +11502,8 @@
       <c r="L295" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M295" s="3">
-        <v>45811</v>
+      <c r="M295" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="296" spans="2:13" x14ac:dyDescent="0.25">
@@ -11527,8 +11540,8 @@
       <c r="L296" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M296" s="3">
-        <v>45811</v>
+      <c r="M296" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="297" spans="2:13" x14ac:dyDescent="0.25">
@@ -11565,8 +11578,8 @@
       <c r="L297" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M297" s="3">
-        <v>45811</v>
+      <c r="M297" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="298" spans="2:13" x14ac:dyDescent="0.25">
@@ -11603,8 +11616,8 @@
       <c r="L298" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M298" s="3">
-        <v>45811</v>
+      <c r="M298" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="299" spans="2:13" x14ac:dyDescent="0.25">
@@ -11641,8 +11654,8 @@
       <c r="L299" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M299" s="3">
-        <v>45811</v>
+      <c r="M299" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="300" spans="2:13" x14ac:dyDescent="0.25">
@@ -11679,8 +11692,8 @@
       <c r="L300" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M300" s="3">
-        <v>45812</v>
+      <c r="M300" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="301" spans="2:13" x14ac:dyDescent="0.25">
@@ -11717,8 +11730,8 @@
       <c r="L301" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M301" s="3">
-        <v>45812</v>
+      <c r="M301" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="302" spans="2:13" x14ac:dyDescent="0.25">
@@ -11755,8 +11768,8 @@
       <c r="L302" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M302" s="3">
-        <v>45812</v>
+      <c r="M302" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="303" spans="2:13" x14ac:dyDescent="0.25">
@@ -11793,8 +11806,8 @@
       <c r="L303" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="M303" s="3">
-        <v>45812</v>
+      <c r="M303" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="304" spans="2:13" x14ac:dyDescent="0.25">
@@ -11831,8 +11844,8 @@
       <c r="L304" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M304" s="3">
-        <v>45812</v>
+      <c r="M304" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="305" spans="2:13" x14ac:dyDescent="0.25">
@@ -11869,8 +11882,8 @@
       <c r="L305" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M305" s="3">
-        <v>45812</v>
+      <c r="M305" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="306" spans="2:13" x14ac:dyDescent="0.25">
@@ -11907,8 +11920,8 @@
       <c r="L306" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M306" s="3">
-        <v>45812</v>
+      <c r="M306" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="307" spans="2:13" x14ac:dyDescent="0.25">
@@ -11945,8 +11958,8 @@
       <c r="L307" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M307" s="3">
-        <v>45812</v>
+      <c r="M307" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="308" spans="2:13" x14ac:dyDescent="0.25">
@@ -11983,8 +11996,8 @@
       <c r="L308" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M308" s="3">
-        <v>45812</v>
+      <c r="M308" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="309" spans="2:13" x14ac:dyDescent="0.25">
@@ -12021,8 +12034,8 @@
       <c r="L309" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M309" s="3">
-        <v>45812</v>
+      <c r="M309" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="310" spans="2:13" x14ac:dyDescent="0.25">
@@ -12059,8 +12072,8 @@
       <c r="L310" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M310" s="3">
-        <v>45812</v>
+      <c r="M310" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="311" spans="2:13" x14ac:dyDescent="0.25">
@@ -12097,8 +12110,8 @@
       <c r="L311" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M311" s="3">
-        <v>45812</v>
+      <c r="M311" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="312" spans="2:13" x14ac:dyDescent="0.25">
@@ -12135,8 +12148,8 @@
       <c r="L312" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="M312" s="3">
-        <v>45812</v>
+      <c r="M312" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="313" spans="2:13" x14ac:dyDescent="0.25">
@@ -12173,8 +12186,8 @@
       <c r="L313" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M313" s="3">
-        <v>45812</v>
+      <c r="M313" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="314" spans="2:13" x14ac:dyDescent="0.25">
@@ -12211,8 +12224,8 @@
       <c r="L314" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M314" s="3">
-        <v>45812</v>
+      <c r="M314" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="315" spans="2:13" x14ac:dyDescent="0.25">
@@ -12249,8 +12262,8 @@
       <c r="L315" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M315" s="3">
-        <v>45812</v>
+      <c r="M315" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="316" spans="2:13" x14ac:dyDescent="0.25">
@@ -12287,8 +12300,8 @@
       <c r="L316" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M316" s="3">
-        <v>45812</v>
+      <c r="M316" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="317" spans="2:13" x14ac:dyDescent="0.25">
@@ -12325,8 +12338,8 @@
       <c r="L317" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M317" s="3">
-        <v>45812</v>
+      <c r="M317" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="318" spans="2:13" x14ac:dyDescent="0.25">
@@ -12363,8 +12376,8 @@
       <c r="L318" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M318" s="3">
-        <v>45812</v>
+      <c r="M318" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="319" spans="2:13" x14ac:dyDescent="0.25">
@@ -12401,8 +12414,8 @@
       <c r="L319" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M319" s="3">
-        <v>45812</v>
+      <c r="M319" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="320" spans="2:13" x14ac:dyDescent="0.25">
@@ -12439,8 +12452,8 @@
       <c r="L320" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M320" s="3">
-        <v>45812</v>
+      <c r="M320" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="321" spans="2:13" x14ac:dyDescent="0.25">
@@ -12477,8 +12490,8 @@
       <c r="L321" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M321" s="3">
-        <v>45812</v>
+      <c r="M321" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="322" spans="2:13" x14ac:dyDescent="0.25">
@@ -12515,8 +12528,8 @@
       <c r="L322" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M322" s="3">
-        <v>45812</v>
+      <c r="M322" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="323" spans="2:13" x14ac:dyDescent="0.25">
@@ -12553,8 +12566,8 @@
       <c r="L323" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M323" s="3">
-        <v>45812</v>
+      <c r="M323" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="324" spans="2:13" x14ac:dyDescent="0.25">
@@ -12591,8 +12604,8 @@
       <c r="L324" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M324" s="3">
-        <v>45812</v>
+      <c r="M324" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="325" spans="2:13" x14ac:dyDescent="0.25">
@@ -12629,8 +12642,8 @@
       <c r="L325" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M325" s="3">
-        <v>45812</v>
+      <c r="M325" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="326" spans="2:13" x14ac:dyDescent="0.25">
@@ -12667,8 +12680,8 @@
       <c r="L326" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M326" s="3">
-        <v>45812</v>
+      <c r="M326" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="327" spans="2:13" x14ac:dyDescent="0.25">
@@ -12705,8 +12718,8 @@
       <c r="L327" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M327" s="3">
-        <v>45812</v>
+      <c r="M327" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="328" spans="2:13" x14ac:dyDescent="0.25">
@@ -12743,8 +12756,8 @@
       <c r="L328" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M328" s="3">
-        <v>45812</v>
+      <c r="M328" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="329" spans="2:13" x14ac:dyDescent="0.25">
@@ -12781,8 +12794,8 @@
       <c r="L329" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M329" s="3">
-        <v>45812</v>
+      <c r="M329" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="330" spans="2:13" x14ac:dyDescent="0.25">
@@ -12819,8 +12832,8 @@
       <c r="L330" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M330" s="3">
-        <v>45812</v>
+      <c r="M330" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="331" spans="2:13" x14ac:dyDescent="0.25">
@@ -12857,8 +12870,8 @@
       <c r="L331" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M331" s="3">
-        <v>45812</v>
+      <c r="M331" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="332" spans="2:13" x14ac:dyDescent="0.25">
@@ -12895,8 +12908,8 @@
       <c r="L332" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M332" s="3">
-        <v>45812</v>
+      <c r="M332" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="333" spans="2:13" x14ac:dyDescent="0.25">
@@ -12933,8 +12946,8 @@
       <c r="L333" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M333" s="3">
-        <v>45812</v>
+      <c r="M333" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="334" spans="2:13" x14ac:dyDescent="0.25">
@@ -12971,8 +12984,8 @@
       <c r="L334" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M334" s="3">
-        <v>45812</v>
+      <c r="M334" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="335" spans="2:13" x14ac:dyDescent="0.25">
@@ -13009,8 +13022,8 @@
       <c r="L335" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M335" s="3">
-        <v>45812</v>
+      <c r="M335" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="336" spans="2:13" x14ac:dyDescent="0.25">
@@ -13047,8 +13060,8 @@
       <c r="L336" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="M336" s="3">
-        <v>45812</v>
+      <c r="M336" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="337" spans="2:13" x14ac:dyDescent="0.25">
@@ -13085,8 +13098,8 @@
       <c r="L337" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M337" s="3">
-        <v>45812</v>
+      <c r="M337" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="338" spans="2:13" x14ac:dyDescent="0.25">
@@ -13123,8 +13136,8 @@
       <c r="L338" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M338" s="3">
-        <v>45812</v>
+      <c r="M338" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="339" spans="2:13" x14ac:dyDescent="0.25">
@@ -13161,8 +13174,8 @@
       <c r="L339" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M339" s="3">
-        <v>45812</v>
+      <c r="M339" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="340" spans="2:13" x14ac:dyDescent="0.25">
@@ -13199,8 +13212,8 @@
       <c r="L340" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M340" s="3">
-        <v>45812</v>
+      <c r="M340" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="341" spans="2:13" x14ac:dyDescent="0.25">
@@ -13237,8 +13250,8 @@
       <c r="L341" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M341" s="3">
-        <v>45812</v>
+      <c r="M341" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="342" spans="2:13" x14ac:dyDescent="0.25">
@@ -13275,8 +13288,8 @@
       <c r="L342" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M342" s="3">
-        <v>45812</v>
+      <c r="M342" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="343" spans="2:13" x14ac:dyDescent="0.25">
@@ -13313,8 +13326,8 @@
       <c r="L343" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M343" s="3">
-        <v>45812</v>
+      <c r="M343" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="344" spans="2:13" x14ac:dyDescent="0.25">
@@ -13351,8 +13364,8 @@
       <c r="L344" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M344" s="3">
-        <v>45812</v>
+      <c r="M344" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="345" spans="2:13" x14ac:dyDescent="0.25">
@@ -13389,8 +13402,8 @@
       <c r="L345" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M345" s="3">
-        <v>45812</v>
+      <c r="M345" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="346" spans="2:13" x14ac:dyDescent="0.25">
@@ -13427,8 +13440,8 @@
       <c r="L346" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M346" s="3">
-        <v>45812</v>
+      <c r="M346" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="347" spans="2:13" x14ac:dyDescent="0.25">
@@ -13465,8 +13478,8 @@
       <c r="L347" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M347" s="3">
-        <v>45812</v>
+      <c r="M347" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="348" spans="2:13" x14ac:dyDescent="0.25">
@@ -13503,8 +13516,8 @@
       <c r="L348" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M348" s="3">
-        <v>45812</v>
+      <c r="M348" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="349" spans="2:13" x14ac:dyDescent="0.25">
@@ -13541,8 +13554,8 @@
       <c r="L349" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M349" s="3">
-        <v>45812</v>
+      <c r="M349" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="350" spans="2:13" x14ac:dyDescent="0.25">
@@ -13579,8 +13592,8 @@
       <c r="L350" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M350" s="3">
-        <v>45812</v>
+      <c r="M350" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="351" spans="2:13" x14ac:dyDescent="0.25">
@@ -13617,8 +13630,8 @@
       <c r="L351" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M351" s="3">
-        <v>45812</v>
+      <c r="M351" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="352" spans="2:13" x14ac:dyDescent="0.25">
@@ -13655,8 +13668,8 @@
       <c r="L352" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M352" s="3">
-        <v>45812</v>
+      <c r="M352" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="353" spans="2:13" x14ac:dyDescent="0.25">
@@ -13693,8 +13706,8 @@
       <c r="L353" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M353" s="3">
-        <v>45812</v>
+      <c r="M353" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="354" spans="2:13" x14ac:dyDescent="0.25">
@@ -13731,8 +13744,8 @@
       <c r="L354" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M354" s="3">
-        <v>45812</v>
+      <c r="M354" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="355" spans="2:13" x14ac:dyDescent="0.25">
@@ -13769,8 +13782,8 @@
       <c r="L355" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M355" s="3">
-        <v>45812</v>
+      <c r="M355" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="356" spans="2:13" x14ac:dyDescent="0.25">
@@ -13807,8 +13820,8 @@
       <c r="L356" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M356" s="3">
-        <v>45812</v>
+      <c r="M356" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="357" spans="2:13" x14ac:dyDescent="0.25">
@@ -13845,8 +13858,8 @@
       <c r="L357" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M357" s="3">
-        <v>45812</v>
+      <c r="M357" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="358" spans="2:13" x14ac:dyDescent="0.25">
@@ -13883,8 +13896,8 @@
       <c r="L358" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M358" s="3">
-        <v>45812</v>
+      <c r="M358" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="359" spans="2:13" x14ac:dyDescent="0.25">
@@ -13921,8 +13934,8 @@
       <c r="L359" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M359" s="3">
-        <v>45812</v>
+      <c r="M359" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="360" spans="2:13" x14ac:dyDescent="0.25">
@@ -13959,8 +13972,8 @@
       <c r="L360" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M360" s="3">
-        <v>45812</v>
+      <c r="M360" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="361" spans="2:13" x14ac:dyDescent="0.25">
@@ -13997,8 +14010,8 @@
       <c r="L361" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M361" s="3">
-        <v>45812</v>
+      <c r="M361" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="362" spans="2:13" x14ac:dyDescent="0.25">
@@ -14035,8 +14048,8 @@
       <c r="L362" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M362" s="3">
-        <v>45812</v>
+      <c r="M362" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="363" spans="2:13" x14ac:dyDescent="0.25">
@@ -14073,8 +14086,8 @@
       <c r="L363" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="M363" s="3">
-        <v>45812</v>
+      <c r="M363" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="364" spans="2:13" x14ac:dyDescent="0.25">
@@ -14111,8 +14124,8 @@
       <c r="L364" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M364" s="3">
-        <v>45812</v>
+      <c r="M364" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="365" spans="2:13" x14ac:dyDescent="0.25">
@@ -14149,8 +14162,8 @@
       <c r="L365" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M365" s="3">
-        <v>45812</v>
+      <c r="M365" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="366" spans="2:13" x14ac:dyDescent="0.25">
@@ -14187,8 +14200,8 @@
       <c r="L366" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M366" s="3">
-        <v>45812</v>
+      <c r="M366" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="367" spans="2:13" x14ac:dyDescent="0.25">
@@ -14225,8 +14238,8 @@
       <c r="L367" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M367" s="3">
-        <v>45812</v>
+      <c r="M367" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="368" spans="2:13" x14ac:dyDescent="0.25">
@@ -14263,8 +14276,8 @@
       <c r="L368" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M368" s="3">
-        <v>45812</v>
+      <c r="M368" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="369" spans="2:13" x14ac:dyDescent="0.25">
@@ -14301,8 +14314,8 @@
       <c r="L369" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M369" s="3">
-        <v>45812</v>
+      <c r="M369" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="370" spans="2:13" x14ac:dyDescent="0.25">
@@ -14339,8 +14352,8 @@
       <c r="L370" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M370" s="3">
-        <v>45812</v>
+      <c r="M370" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="371" spans="2:13" x14ac:dyDescent="0.25">
@@ -14377,8 +14390,8 @@
       <c r="L371" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M371" s="3">
-        <v>45812</v>
+      <c r="M371" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="372" spans="2:13" x14ac:dyDescent="0.25">
@@ -14415,8 +14428,8 @@
       <c r="L372" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M372" s="3">
-        <v>45812</v>
+      <c r="M372" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="373" spans="2:13" x14ac:dyDescent="0.25">
@@ -14453,8 +14466,8 @@
       <c r="L373" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M373" s="3">
-        <v>45812</v>
+      <c r="M373" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="374" spans="2:13" x14ac:dyDescent="0.25">
@@ -14491,8 +14504,8 @@
       <c r="L374" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M374" s="3">
-        <v>45812</v>
+      <c r="M374" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="375" spans="2:13" x14ac:dyDescent="0.25">
@@ -14529,8 +14542,8 @@
       <c r="L375" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M375" s="3">
-        <v>45812</v>
+      <c r="M375" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="376" spans="2:13" x14ac:dyDescent="0.25">
@@ -14567,8 +14580,8 @@
       <c r="L376" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M376" s="3">
-        <v>45812</v>
+      <c r="M376" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="377" spans="2:13" x14ac:dyDescent="0.25">
@@ -14605,8 +14618,8 @@
       <c r="L377" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M377" s="3">
-        <v>45812</v>
+      <c r="M377" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="378" spans="2:13" x14ac:dyDescent="0.25">
@@ -14643,8 +14656,8 @@
       <c r="L378" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M378" s="3">
-        <v>45812</v>
+      <c r="M378" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="379" spans="2:13" x14ac:dyDescent="0.25">
@@ -14681,8 +14694,8 @@
       <c r="L379" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M379" s="3">
-        <v>45812</v>
+      <c r="M379" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="380" spans="2:13" x14ac:dyDescent="0.25">
@@ -14719,8 +14732,8 @@
       <c r="L380" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="M380" s="3">
-        <v>45812</v>
+      <c r="M380" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="381" spans="2:13" x14ac:dyDescent="0.25">
@@ -14757,8 +14770,8 @@
       <c r="L381" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M381" s="3">
-        <v>45813</v>
+      <c r="M381" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="382" spans="2:13" x14ac:dyDescent="0.25">
@@ -14795,8 +14808,8 @@
       <c r="L382" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M382" s="3">
-        <v>45813</v>
+      <c r="M382" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="383" spans="2:13" x14ac:dyDescent="0.25">
@@ -14833,8 +14846,8 @@
       <c r="L383" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M383" s="3">
-        <v>45813</v>
+      <c r="M383" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="384" spans="2:13" x14ac:dyDescent="0.25">
@@ -14871,8 +14884,8 @@
       <c r="L384" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M384" s="3">
-        <v>45813</v>
+      <c r="M384" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="385" spans="2:13" x14ac:dyDescent="0.25">
@@ -14909,8 +14922,8 @@
       <c r="L385" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M385" s="3">
-        <v>45813</v>
+      <c r="M385" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="386" spans="2:13" x14ac:dyDescent="0.25">
@@ -14947,8 +14960,8 @@
       <c r="L386" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M386" s="3">
-        <v>45813</v>
+      <c r="M386" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="387" spans="2:13" x14ac:dyDescent="0.25">
@@ -14985,8 +14998,8 @@
       <c r="L387" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M387" s="3">
-        <v>45813</v>
+      <c r="M387" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="388" spans="2:13" x14ac:dyDescent="0.25">
@@ -15023,8 +15036,8 @@
       <c r="L388" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M388" s="3">
-        <v>45813</v>
+      <c r="M388" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="389" spans="2:13" x14ac:dyDescent="0.25">
@@ -15061,8 +15074,8 @@
       <c r="L389" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M389" s="3">
-        <v>45813</v>
+      <c r="M389" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="390" spans="2:13" x14ac:dyDescent="0.25">
@@ -15099,8 +15112,8 @@
       <c r="L390" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M390" s="3">
-        <v>45813</v>
+      <c r="M390" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="391" spans="2:13" x14ac:dyDescent="0.25">
@@ -15137,8 +15150,8 @@
       <c r="L391" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M391" s="3">
-        <v>45813</v>
+      <c r="M391" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="392" spans="2:13" x14ac:dyDescent="0.25">
@@ -15175,8 +15188,8 @@
       <c r="L392" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M392" s="3">
-        <v>45813</v>
+      <c r="M392" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="393" spans="2:13" x14ac:dyDescent="0.25">
@@ -15213,8 +15226,8 @@
       <c r="L393" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M393" s="3">
-        <v>45813</v>
+      <c r="M393" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="394" spans="2:13" x14ac:dyDescent="0.25">
@@ -15251,8 +15264,8 @@
       <c r="L394" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M394" s="3">
-        <v>45813</v>
+      <c r="M394" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="395" spans="2:13" x14ac:dyDescent="0.25">
@@ -15289,8 +15302,8 @@
       <c r="L395" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M395" s="3">
-        <v>45813</v>
+      <c r="M395" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="396" spans="2:13" x14ac:dyDescent="0.25">
@@ -15327,8 +15340,8 @@
       <c r="L396" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M396" s="3">
-        <v>45813</v>
+      <c r="M396" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="397" spans="2:13" x14ac:dyDescent="0.25">
@@ -15365,8 +15378,8 @@
       <c r="L397" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M397" s="3">
-        <v>45813</v>
+      <c r="M397" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="398" spans="2:13" x14ac:dyDescent="0.25">
@@ -15403,8 +15416,8 @@
       <c r="L398" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M398" s="3">
-        <v>45813</v>
+      <c r="M398" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="399" spans="2:13" x14ac:dyDescent="0.25">
@@ -15441,8 +15454,8 @@
       <c r="L399" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M399" s="3">
-        <v>45813</v>
+      <c r="M399" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="400" spans="2:13" x14ac:dyDescent="0.25">
@@ -15479,8 +15492,8 @@
       <c r="L400" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M400" s="3">
-        <v>45813</v>
+      <c r="M400" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="401" spans="2:13" x14ac:dyDescent="0.25">
@@ -15517,8 +15530,8 @@
       <c r="L401" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M401" s="3">
-        <v>45813</v>
+      <c r="M401" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="402" spans="2:13" x14ac:dyDescent="0.25">
@@ -15555,8 +15568,8 @@
       <c r="L402" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M402" s="3">
-        <v>45813</v>
+      <c r="M402" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="403" spans="2:13" x14ac:dyDescent="0.25">
@@ -15593,8 +15606,8 @@
       <c r="L403" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M403" s="3">
-        <v>45813</v>
+      <c r="M403" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="404" spans="2:13" x14ac:dyDescent="0.25">
@@ -15631,8 +15644,8 @@
       <c r="L404" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M404" s="3">
-        <v>45813</v>
+      <c r="M404" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="405" spans="2:13" x14ac:dyDescent="0.25">
@@ -15669,8 +15682,8 @@
       <c r="L405" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M405" s="3">
-        <v>45813</v>
+      <c r="M405" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="406" spans="2:13" x14ac:dyDescent="0.25">
@@ -15707,8 +15720,8 @@
       <c r="L406" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M406" s="3">
-        <v>45813</v>
+      <c r="M406" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="407" spans="2:13" x14ac:dyDescent="0.25">
@@ -15745,8 +15758,8 @@
       <c r="L407" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M407" s="3">
-        <v>45813</v>
+      <c r="M407" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="408" spans="2:13" x14ac:dyDescent="0.25">
@@ -15783,8 +15796,8 @@
       <c r="L408" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M408" s="3">
-        <v>45813</v>
+      <c r="M408" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="409" spans="2:13" x14ac:dyDescent="0.25">
@@ -15821,8 +15834,8 @@
       <c r="L409" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M409" s="3">
-        <v>45813</v>
+      <c r="M409" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="410" spans="2:13" x14ac:dyDescent="0.25">
@@ -15859,8 +15872,8 @@
       <c r="L410" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M410" s="3">
-        <v>45813</v>
+      <c r="M410" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="411" spans="2:13" x14ac:dyDescent="0.25">
@@ -15897,8 +15910,8 @@
       <c r="L411" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M411" s="3">
-        <v>45813</v>
+      <c r="M411" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="412" spans="2:13" x14ac:dyDescent="0.25">
@@ -15935,8 +15948,8 @@
       <c r="L412" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M412" s="3">
-        <v>45813</v>
+      <c r="M412" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="413" spans="2:13" x14ac:dyDescent="0.25">
@@ -15973,8 +15986,8 @@
       <c r="L413" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M413" s="3">
-        <v>45813</v>
+      <c r="M413" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="414" spans="2:13" x14ac:dyDescent="0.25">
@@ -16011,8 +16024,8 @@
       <c r="L414" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M414" s="3">
-        <v>45813</v>
+      <c r="M414" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="415" spans="2:13" x14ac:dyDescent="0.25">
@@ -16049,8 +16062,8 @@
       <c r="L415" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M415" s="3">
-        <v>45813</v>
+      <c r="M415" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="416" spans="2:13" x14ac:dyDescent="0.25">
@@ -16087,8 +16100,8 @@
       <c r="L416" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M416" s="3">
-        <v>45813</v>
+      <c r="M416" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="417" spans="2:13" x14ac:dyDescent="0.25">
@@ -16125,8 +16138,8 @@
       <c r="L417" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M417" s="3">
-        <v>45813</v>
+      <c r="M417" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="418" spans="2:13" x14ac:dyDescent="0.25">
@@ -16163,8 +16176,8 @@
       <c r="L418" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M418" s="3">
-        <v>45813</v>
+      <c r="M418" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="419" spans="2:13" x14ac:dyDescent="0.25">
@@ -16201,8 +16214,8 @@
       <c r="L419" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M419" s="3">
-        <v>45813</v>
+      <c r="M419" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="420" spans="2:13" x14ac:dyDescent="0.25">
@@ -16239,8 +16252,8 @@
       <c r="L420" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M420" s="3">
-        <v>45813</v>
+      <c r="M420" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="421" spans="2:13" x14ac:dyDescent="0.25">
@@ -16277,8 +16290,8 @@
       <c r="L421" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M421" s="3">
-        <v>45813</v>
+      <c r="M421" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="422" spans="2:13" x14ac:dyDescent="0.25">
@@ -16315,8 +16328,8 @@
       <c r="L422" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M422" s="3">
-        <v>45813</v>
+      <c r="M422" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="423" spans="2:13" x14ac:dyDescent="0.25">
@@ -16353,8 +16366,8 @@
       <c r="L423" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M423" s="3">
-        <v>45813</v>
+      <c r="M423" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="424" spans="2:13" x14ac:dyDescent="0.25">
@@ -16391,8 +16404,8 @@
       <c r="L424" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M424" s="3">
-        <v>45813</v>
+      <c r="M424" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="425" spans="2:13" x14ac:dyDescent="0.25">
@@ -16429,8 +16442,8 @@
       <c r="L425" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M425" s="3">
-        <v>45813</v>
+      <c r="M425" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="426" spans="2:13" x14ac:dyDescent="0.25">
@@ -16467,8 +16480,8 @@
       <c r="L426" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M426" s="3">
-        <v>45813</v>
+      <c r="M426" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="427" spans="2:13" x14ac:dyDescent="0.25">
@@ -16505,8 +16518,8 @@
       <c r="L427" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M427" s="3">
-        <v>45813</v>
+      <c r="M427" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="428" spans="2:13" x14ac:dyDescent="0.25">
@@ -16543,8 +16556,8 @@
       <c r="L428" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M428" s="3">
-        <v>45813</v>
+      <c r="M428" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="429" spans="2:13" x14ac:dyDescent="0.25">
@@ -16581,8 +16594,8 @@
       <c r="L429" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M429" s="3">
-        <v>45813</v>
+      <c r="M429" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="430" spans="2:13" x14ac:dyDescent="0.25">
@@ -16619,8 +16632,8 @@
       <c r="L430" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M430" s="3">
-        <v>45813</v>
+      <c r="M430" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="431" spans="2:13" x14ac:dyDescent="0.25">
@@ -16657,8 +16670,8 @@
       <c r="L431" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M431" s="3">
-        <v>45813</v>
+      <c r="M431" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="432" spans="2:13" x14ac:dyDescent="0.25">
@@ -16695,8 +16708,8 @@
       <c r="L432" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M432" s="3">
-        <v>45813</v>
+      <c r="M432" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="433" spans="2:13" x14ac:dyDescent="0.25">
@@ -16733,8 +16746,8 @@
       <c r="L433" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M433" s="3">
-        <v>45813</v>
+      <c r="M433" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="434" spans="2:13" x14ac:dyDescent="0.25">
@@ -16771,8 +16784,8 @@
       <c r="L434" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M434" s="3">
-        <v>45813</v>
+      <c r="M434" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="435" spans="2:13" x14ac:dyDescent="0.25">
@@ -16809,8 +16822,8 @@
       <c r="L435" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M435" s="3">
-        <v>45813</v>
+      <c r="M435" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="436" spans="2:13" x14ac:dyDescent="0.25">
@@ -16847,8 +16860,8 @@
       <c r="L436" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M436" s="3">
-        <v>45813</v>
+      <c r="M436" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="437" spans="2:13" x14ac:dyDescent="0.25">
@@ -16885,8 +16898,8 @@
       <c r="L437" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M437" s="3">
-        <v>45813</v>
+      <c r="M437" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="438" spans="2:13" x14ac:dyDescent="0.25">
@@ -16923,8 +16936,8 @@
       <c r="L438" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M438" s="3">
-        <v>45813</v>
+      <c r="M438" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="439" spans="2:13" x14ac:dyDescent="0.25">
@@ -16961,8 +16974,8 @@
       <c r="L439" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M439" s="3">
-        <v>45813</v>
+      <c r="M439" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="440" spans="2:13" x14ac:dyDescent="0.25">
@@ -16999,8 +17012,8 @@
       <c r="L440" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M440" s="3">
-        <v>45813</v>
+      <c r="M440" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="441" spans="2:13" x14ac:dyDescent="0.25">
@@ -17037,8 +17050,8 @@
       <c r="L441" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M441" s="3">
-        <v>45813</v>
+      <c r="M441" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="442" spans="2:13" x14ac:dyDescent="0.25">
@@ -17075,8 +17088,8 @@
       <c r="L442" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M442" s="3">
-        <v>45813</v>
+      <c r="M442" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="443" spans="2:13" x14ac:dyDescent="0.25">
@@ -17113,8 +17126,8 @@
       <c r="L443" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M443" s="3">
-        <v>45813</v>
+      <c r="M443" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="444" spans="2:13" x14ac:dyDescent="0.25">
@@ -17151,8 +17164,8 @@
       <c r="L444" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M444" s="3">
-        <v>45813</v>
+      <c r="M444" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="445" spans="2:13" x14ac:dyDescent="0.25">
@@ -17189,8 +17202,8 @@
       <c r="L445" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M445" s="3">
-        <v>45813</v>
+      <c r="M445" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="446" spans="2:13" x14ac:dyDescent="0.25">
@@ -17227,8 +17240,8 @@
       <c r="L446" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M446" s="3">
-        <v>45813</v>
+      <c r="M446" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="447" spans="2:13" x14ac:dyDescent="0.25">
@@ -17265,8 +17278,8 @@
       <c r="L447" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M447" s="3">
-        <v>45813</v>
+      <c r="M447" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="448" spans="2:13" x14ac:dyDescent="0.25">
@@ -17303,8 +17316,8 @@
       <c r="L448" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M448" s="3">
-        <v>45813</v>
+      <c r="M448" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="449" spans="2:13" x14ac:dyDescent="0.25">
@@ -17341,8 +17354,8 @@
       <c r="L449" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M449" s="3">
-        <v>45813</v>
+      <c r="M449" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="450" spans="2:13" x14ac:dyDescent="0.25">
@@ -17379,8 +17392,8 @@
       <c r="L450" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M450" s="3">
-        <v>45813</v>
+      <c r="M450" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="451" spans="2:13" x14ac:dyDescent="0.25">
@@ -17417,8 +17430,8 @@
       <c r="L451" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M451" s="3">
-        <v>45813</v>
+      <c r="M451" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="452" spans="2:13" x14ac:dyDescent="0.25">
@@ -17455,8 +17468,8 @@
       <c r="L452" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M452" s="3">
-        <v>45813</v>
+      <c r="M452" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="453" spans="2:13" x14ac:dyDescent="0.25">
@@ -17493,8 +17506,8 @@
       <c r="L453" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M453" s="3">
-        <v>45813</v>
+      <c r="M453" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="454" spans="2:13" x14ac:dyDescent="0.25">
@@ -17531,8 +17544,8 @@
       <c r="L454" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M454" s="3">
-        <v>45813</v>
+      <c r="M454" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="455" spans="2:13" x14ac:dyDescent="0.25">
@@ -17569,8 +17582,8 @@
       <c r="L455" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M455" s="3">
-        <v>45813</v>
+      <c r="M455" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="456" spans="2:13" x14ac:dyDescent="0.25">
@@ -17607,8 +17620,8 @@
       <c r="L456" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M456" s="3">
-        <v>45813</v>
+      <c r="M456" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="457" spans="2:13" x14ac:dyDescent="0.25">
@@ -17645,8 +17658,8 @@
       <c r="L457" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M457" s="3">
-        <v>45813</v>
+      <c r="M457" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="458" spans="2:13" x14ac:dyDescent="0.25">
@@ -17683,8 +17696,8 @@
       <c r="L458" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M458" s="3">
-        <v>45813</v>
+      <c r="M458" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="459" spans="2:13" x14ac:dyDescent="0.25">
@@ -17721,8 +17734,8 @@
       <c r="L459" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M459" s="3">
-        <v>45814</v>
+      <c r="M459" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="460" spans="2:13" x14ac:dyDescent="0.25">
@@ -17759,8 +17772,8 @@
       <c r="L460" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M460" s="3">
-        <v>45814</v>
+      <c r="M460" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="461" spans="2:13" x14ac:dyDescent="0.25">
@@ -17797,8 +17810,8 @@
       <c r="L461" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M461" s="3">
-        <v>45814</v>
+      <c r="M461" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="462" spans="2:13" x14ac:dyDescent="0.25">
@@ -17835,8 +17848,8 @@
       <c r="L462" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M462" s="3">
-        <v>45814</v>
+      <c r="M462" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="463" spans="2:13" x14ac:dyDescent="0.25">
@@ -17873,8 +17886,8 @@
       <c r="L463" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M463" s="3">
-        <v>45814</v>
+      <c r="M463" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="464" spans="2:13" x14ac:dyDescent="0.25">
@@ -17911,8 +17924,8 @@
       <c r="L464" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M464" s="3">
-        <v>45814</v>
+      <c r="M464" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="465" spans="2:13" x14ac:dyDescent="0.25">
@@ -17949,8 +17962,8 @@
       <c r="L465" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M465" s="3">
-        <v>45814</v>
+      <c r="M465" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="466" spans="2:13" x14ac:dyDescent="0.25">
@@ -17987,8 +18000,8 @@
       <c r="L466" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M466" s="3">
-        <v>45814</v>
+      <c r="M466" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="467" spans="2:13" x14ac:dyDescent="0.25">
@@ -18025,8 +18038,8 @@
       <c r="L467" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M467" s="3">
-        <v>45814</v>
+      <c r="M467" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="468" spans="2:13" x14ac:dyDescent="0.25">
@@ -18063,8 +18076,8 @@
       <c r="L468" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M468" s="3">
-        <v>45814</v>
+      <c r="M468" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="469" spans="2:13" x14ac:dyDescent="0.25">
@@ -18101,8 +18114,8 @@
       <c r="L469" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M469" s="3">
-        <v>45814</v>
+      <c r="M469" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="470" spans="2:13" x14ac:dyDescent="0.25">
@@ -18139,8 +18152,8 @@
       <c r="L470" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M470" s="3">
-        <v>45814</v>
+      <c r="M470" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="471" spans="2:13" x14ac:dyDescent="0.25">
@@ -18177,8 +18190,8 @@
       <c r="L471" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M471" s="3">
-        <v>45814</v>
+      <c r="M471" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="472" spans="2:13" x14ac:dyDescent="0.25">
@@ -18215,8 +18228,8 @@
       <c r="L472" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M472" s="3">
-        <v>45814</v>
+      <c r="M472" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="473" spans="2:13" x14ac:dyDescent="0.25">
@@ -18253,8 +18266,8 @@
       <c r="L473" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M473" s="3">
-        <v>45814</v>
+      <c r="M473" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="474" spans="2:13" x14ac:dyDescent="0.25">
@@ -18291,8 +18304,8 @@
       <c r="L474" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M474" s="3">
-        <v>45814</v>
+      <c r="M474" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="475" spans="2:13" x14ac:dyDescent="0.25">
@@ -18329,8 +18342,8 @@
       <c r="L475" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M475" s="3">
-        <v>45814</v>
+      <c r="M475" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="476" spans="2:13" x14ac:dyDescent="0.25">
@@ -18367,8 +18380,8 @@
       <c r="L476" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M476" s="3">
-        <v>45814</v>
+      <c r="M476" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="477" spans="2:13" x14ac:dyDescent="0.25">
@@ -18405,8 +18418,8 @@
       <c r="L477" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M477" s="3">
-        <v>45814</v>
+      <c r="M477" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="478" spans="2:13" x14ac:dyDescent="0.25">
@@ -18443,8 +18456,8 @@
       <c r="L478" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M478" s="3">
-        <v>45814</v>
+      <c r="M478" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="479" spans="2:13" x14ac:dyDescent="0.25">
@@ -18481,8 +18494,8 @@
       <c r="L479" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M479" s="3">
-        <v>45814</v>
+      <c r="M479" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="480" spans="2:13" x14ac:dyDescent="0.25">
@@ -18519,8 +18532,8 @@
       <c r="L480" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M480" s="3">
-        <v>45814</v>
+      <c r="M480" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="481" spans="2:13" x14ac:dyDescent="0.25">
@@ -18557,8 +18570,8 @@
       <c r="L481" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M481" s="3">
-        <v>45814</v>
+      <c r="M481" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="482" spans="2:13" x14ac:dyDescent="0.25">
@@ -18595,8 +18608,8 @@
       <c r="L482" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M482" s="3">
-        <v>45814</v>
+      <c r="M482" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="483" spans="2:13" x14ac:dyDescent="0.25">
@@ -18633,8 +18646,8 @@
       <c r="L483" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M483" s="3">
-        <v>45814</v>
+      <c r="M483" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="484" spans="2:13" x14ac:dyDescent="0.25">
@@ -18671,8 +18684,8 @@
       <c r="L484" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M484" s="3">
-        <v>45814</v>
+      <c r="M484" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="485" spans="2:13" x14ac:dyDescent="0.25">
@@ -18709,8 +18722,8 @@
       <c r="L485" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M485" s="3">
-        <v>45814</v>
+      <c r="M485" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="486" spans="2:13" x14ac:dyDescent="0.25">
@@ -18747,8 +18760,8 @@
       <c r="L486" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M486" s="3">
-        <v>45814</v>
+      <c r="M486" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="487" spans="2:13" x14ac:dyDescent="0.25">
@@ -18785,8 +18798,8 @@
       <c r="L487" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M487" s="3">
-        <v>45814</v>
+      <c r="M487" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="488" spans="2:13" x14ac:dyDescent="0.25">
@@ -18823,8 +18836,8 @@
       <c r="L488" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M488" s="3">
-        <v>45814</v>
+      <c r="M488" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="489" spans="2:13" x14ac:dyDescent="0.25">
@@ -18861,8 +18874,8 @@
       <c r="L489" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M489" s="3">
-        <v>45814</v>
+      <c r="M489" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="490" spans="2:13" x14ac:dyDescent="0.25">
@@ -18899,8 +18912,8 @@
       <c r="L490" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M490" s="3">
-        <v>45814</v>
+      <c r="M490" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="491" spans="2:13" x14ac:dyDescent="0.25">
@@ -18937,8 +18950,8 @@
       <c r="L491" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M491" s="3">
-        <v>45814</v>
+      <c r="M491" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="492" spans="2:13" x14ac:dyDescent="0.25">
@@ -18975,8 +18988,8 @@
       <c r="L492" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M492" s="3">
-        <v>45814</v>
+      <c r="M492" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="493" spans="2:13" x14ac:dyDescent="0.25">
@@ -19013,8 +19026,8 @@
       <c r="L493" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M493" s="3">
-        <v>45814</v>
+      <c r="M493" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="494" spans="2:13" x14ac:dyDescent="0.25">
@@ -19051,8 +19064,8 @@
       <c r="L494" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M494" s="3">
-        <v>45814</v>
+      <c r="M494" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="495" spans="2:13" x14ac:dyDescent="0.25">
@@ -19089,8 +19102,8 @@
       <c r="L495" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M495" s="3">
-        <v>45814</v>
+      <c r="M495" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="496" spans="2:13" x14ac:dyDescent="0.25">
@@ -19127,8 +19140,8 @@
       <c r="L496" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M496" s="3">
-        <v>45814</v>
+      <c r="M496" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="497" spans="2:13" x14ac:dyDescent="0.25">
@@ -19165,8 +19178,8 @@
       <c r="L497" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M497" s="3">
-        <v>45814</v>
+      <c r="M497" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="498" spans="2:13" x14ac:dyDescent="0.25">
@@ -19203,8 +19216,8 @@
       <c r="L498" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M498" s="3">
-        <v>45814</v>
+      <c r="M498" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="499" spans="2:13" x14ac:dyDescent="0.25">
@@ -19241,8 +19254,8 @@
       <c r="L499" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M499" s="3">
-        <v>45814</v>
+      <c r="M499" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="500" spans="2:13" x14ac:dyDescent="0.25">
@@ -19279,8 +19292,8 @@
       <c r="L500" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M500" s="3">
-        <v>45814</v>
+      <c r="M500" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="501" spans="2:13" x14ac:dyDescent="0.25">
@@ -19317,8 +19330,8 @@
       <c r="L501" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M501" s="3">
-        <v>45814</v>
+      <c r="M501" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="502" spans="2:13" x14ac:dyDescent="0.25">
@@ -19355,8 +19368,8 @@
       <c r="L502" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M502" s="3">
-        <v>45814</v>
+      <c r="M502" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="503" spans="2:13" x14ac:dyDescent="0.25">
@@ -19393,8 +19406,8 @@
       <c r="L503" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M503" s="3">
-        <v>45814</v>
+      <c r="M503" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="504" spans="2:13" x14ac:dyDescent="0.25">
@@ -19431,8 +19444,8 @@
       <c r="L504" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M504" s="3">
-        <v>45814</v>
+      <c r="M504" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="505" spans="2:13" x14ac:dyDescent="0.25">
@@ -19469,8 +19482,8 @@
       <c r="L505" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M505" s="3">
-        <v>45814</v>
+      <c r="M505" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="506" spans="2:13" x14ac:dyDescent="0.25">
@@ -19507,8 +19520,8 @@
       <c r="L506" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M506" s="3">
-        <v>45814</v>
+      <c r="M506" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="507" spans="2:13" x14ac:dyDescent="0.25">
@@ -19545,8 +19558,8 @@
       <c r="L507" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M507" s="3">
-        <v>45814</v>
+      <c r="M507" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="508" spans="2:13" x14ac:dyDescent="0.25">
@@ -19583,8 +19596,8 @@
       <c r="L508" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M508" s="3">
-        <v>45814</v>
+      <c r="M508" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="509" spans="2:13" x14ac:dyDescent="0.25">
@@ -19621,8 +19634,8 @@
       <c r="L509" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M509" s="3">
-        <v>45814</v>
+      <c r="M509" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="510" spans="2:13" x14ac:dyDescent="0.25">
@@ -19659,8 +19672,8 @@
       <c r="L510" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M510" s="3">
-        <v>45814</v>
+      <c r="M510" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="511" spans="2:13" x14ac:dyDescent="0.25">
@@ -19697,8 +19710,8 @@
       <c r="L511" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M511" s="3">
-        <v>45814</v>
+      <c r="M511" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="512" spans="2:13" x14ac:dyDescent="0.25">
@@ -19735,8 +19748,8 @@
       <c r="L512" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M512" s="3">
-        <v>45814</v>
+      <c r="M512" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="513" spans="2:13" x14ac:dyDescent="0.25">
@@ -19773,8 +19786,8 @@
       <c r="L513" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M513" s="3">
-        <v>45814</v>
+      <c r="M513" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="514" spans="2:13" x14ac:dyDescent="0.25">
@@ -19811,8 +19824,8 @@
       <c r="L514" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M514" s="3">
-        <v>45814</v>
+      <c r="M514" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="515" spans="2:13" x14ac:dyDescent="0.25">
@@ -19849,8 +19862,8 @@
       <c r="L515" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M515" s="3">
-        <v>45814</v>
+      <c r="M515" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="516" spans="2:13" x14ac:dyDescent="0.25">
@@ -19887,8 +19900,8 @@
       <c r="L516" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M516" s="3">
-        <v>45814</v>
+      <c r="M516" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="517" spans="2:13" x14ac:dyDescent="0.25">
@@ -19925,8 +19938,8 @@
       <c r="L517" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M517" s="3">
-        <v>45814</v>
+      <c r="M517" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="518" spans="2:13" x14ac:dyDescent="0.25">
@@ -19963,8 +19976,8 @@
       <c r="L518" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M518" s="3">
-        <v>45814</v>
+      <c r="M518" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="519" spans="2:13" x14ac:dyDescent="0.25">
@@ -20001,8 +20014,8 @@
       <c r="L519" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M519" s="3">
-        <v>45814</v>
+      <c r="M519" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="520" spans="2:13" x14ac:dyDescent="0.25">
@@ -20039,8 +20052,8 @@
       <c r="L520" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M520" s="3">
-        <v>45814</v>
+      <c r="M520" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="521" spans="2:13" x14ac:dyDescent="0.25">
@@ -20077,8 +20090,8 @@
       <c r="L521" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M521" s="3">
-        <v>45814</v>
+      <c r="M521" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="522" spans="2:13" x14ac:dyDescent="0.25">
@@ -20115,8 +20128,8 @@
       <c r="L522" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M522" s="3">
-        <v>45814</v>
+      <c r="M522" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="523" spans="2:13" x14ac:dyDescent="0.25">
@@ -20153,8 +20166,8 @@
       <c r="L523" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M523" s="3">
-        <v>45814</v>
+      <c r="M523" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="524" spans="2:13" x14ac:dyDescent="0.25">
@@ -20191,8 +20204,8 @@
       <c r="L524" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M524" s="3">
-        <v>45814</v>
+      <c r="M524" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="525" spans="2:13" x14ac:dyDescent="0.25">
@@ -20229,8 +20242,8 @@
       <c r="L525" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M525" s="3">
-        <v>45814</v>
+      <c r="M525" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="526" spans="2:13" x14ac:dyDescent="0.25">
@@ -20267,8 +20280,8 @@
       <c r="L526" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M526" s="3">
-        <v>45814</v>
+      <c r="M526" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="527" spans="2:13" x14ac:dyDescent="0.25">
@@ -20305,8 +20318,8 @@
       <c r="L527" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M527" s="3">
-        <v>45814</v>
+      <c r="M527" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="528" spans="2:13" x14ac:dyDescent="0.25">
@@ -20343,8 +20356,8 @@
       <c r="L528" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M528" s="3">
-        <v>45814</v>
+      <c r="M528" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="529" spans="2:13" x14ac:dyDescent="0.25">
@@ -20381,8 +20394,8 @@
       <c r="L529" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M529" s="3">
-        <v>45814</v>
+      <c r="M529" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="530" spans="2:13" x14ac:dyDescent="0.25">
@@ -20419,8 +20432,8 @@
       <c r="L530" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M530" s="3">
-        <v>45814</v>
+      <c r="M530" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="531" spans="2:13" x14ac:dyDescent="0.25">
@@ -20457,8 +20470,8 @@
       <c r="L531" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M531" s="3">
-        <v>45814</v>
+      <c r="M531" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="532" spans="2:13" x14ac:dyDescent="0.25">
@@ -20495,8 +20508,8 @@
       <c r="L532" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M532" s="3">
-        <v>45814</v>
+      <c r="M532" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="533" spans="2:13" x14ac:dyDescent="0.25">
@@ -20533,8 +20546,8 @@
       <c r="L533" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M533" s="3">
-        <v>45814</v>
+      <c r="M533" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="534" spans="2:13" x14ac:dyDescent="0.25">
@@ -20571,8 +20584,8 @@
       <c r="L534" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M534" s="3">
-        <v>45814</v>
+      <c r="M534" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="535" spans="2:13" x14ac:dyDescent="0.25">
@@ -20609,8 +20622,8 @@
       <c r="L535" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M535" s="3">
-        <v>45814</v>
+      <c r="M535" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="536" spans="2:13" x14ac:dyDescent="0.25">
@@ -20647,8 +20660,8 @@
       <c r="L536" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M536" s="3">
-        <v>45814</v>
+      <c r="M536" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="537" spans="2:13" x14ac:dyDescent="0.25">
@@ -20685,8 +20698,8 @@
       <c r="L537" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M537" s="3">
-        <v>45814</v>
+      <c r="M537" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="538" spans="2:13" x14ac:dyDescent="0.25">
@@ -20723,8 +20736,8 @@
       <c r="L538" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M538" s="3">
-        <v>45815</v>
+      <c r="M538" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="539" spans="2:13" x14ac:dyDescent="0.25">
@@ -20761,8 +20774,8 @@
       <c r="L539" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M539" s="3">
-        <v>45815</v>
+      <c r="M539" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="540" spans="2:13" x14ac:dyDescent="0.25">
@@ -20799,8 +20812,8 @@
       <c r="L540" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M540" s="3">
-        <v>45815</v>
+      <c r="M540" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="541" spans="2:13" x14ac:dyDescent="0.25">
@@ -20837,8 +20850,8 @@
       <c r="L541" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M541" s="3">
-        <v>45815</v>
+      <c r="M541" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="542" spans="2:13" x14ac:dyDescent="0.25">
@@ -20875,8 +20888,8 @@
       <c r="L542" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M542" s="3">
-        <v>45815</v>
+      <c r="M542" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="543" spans="2:13" x14ac:dyDescent="0.25">
@@ -20913,8 +20926,8 @@
       <c r="L543" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M543" s="3">
-        <v>45815</v>
+      <c r="M543" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="544" spans="2:13" x14ac:dyDescent="0.25">
@@ -20951,8 +20964,8 @@
       <c r="L544" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M544" s="3">
-        <v>45815</v>
+      <c r="M544" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="545" spans="2:13" x14ac:dyDescent="0.25">
@@ -20989,8 +21002,8 @@
       <c r="L545" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M545" s="3">
-        <v>45815</v>
+      <c r="M545" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="546" spans="2:13" x14ac:dyDescent="0.25">
@@ -21027,8 +21040,8 @@
       <c r="L546" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M546" s="3">
-        <v>45815</v>
+      <c r="M546" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="547" spans="2:13" x14ac:dyDescent="0.25">
@@ -21065,8 +21078,8 @@
       <c r="L547" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M547" s="3">
-        <v>45815</v>
+      <c r="M547" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="548" spans="2:13" x14ac:dyDescent="0.25">
@@ -21103,8 +21116,8 @@
       <c r="L548" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M548" s="3">
-        <v>45815</v>
+      <c r="M548" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="549" spans="2:13" x14ac:dyDescent="0.25">
@@ -21141,8 +21154,8 @@
       <c r="L549" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M549" s="3">
-        <v>45815</v>
+      <c r="M549" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="550" spans="2:13" x14ac:dyDescent="0.25">
@@ -21179,8 +21192,8 @@
       <c r="L550" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M550" s="3">
-        <v>45815</v>
+      <c r="M550" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="551" spans="2:13" x14ac:dyDescent="0.25">
@@ -21217,8 +21230,8 @@
       <c r="L551" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M551" s="3">
-        <v>45815</v>
+      <c r="M551" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="552" spans="2:13" x14ac:dyDescent="0.25">
@@ -21255,8 +21268,8 @@
       <c r="L552" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M552" s="3">
-        <v>45815</v>
+      <c r="M552" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="553" spans="2:13" x14ac:dyDescent="0.25">
@@ -21293,8 +21306,8 @@
       <c r="L553" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M553" s="3">
-        <v>45815</v>
+      <c r="M553" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="554" spans="2:13" x14ac:dyDescent="0.25">
@@ -21331,8 +21344,8 @@
       <c r="L554" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M554" s="3">
-        <v>45815</v>
+      <c r="M554" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="555" spans="2:13" x14ac:dyDescent="0.25">
@@ -21369,8 +21382,8 @@
       <c r="L555" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M555" s="3">
-        <v>45815</v>
+      <c r="M555" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="556" spans="2:13" x14ac:dyDescent="0.25">
@@ -21407,8 +21420,8 @@
       <c r="L556" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M556" s="3">
-        <v>45815</v>
+      <c r="M556" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="557" spans="2:13" x14ac:dyDescent="0.25">
@@ -21445,8 +21458,8 @@
       <c r="L557" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M557" s="3">
-        <v>45815</v>
+      <c r="M557" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="558" spans="2:13" x14ac:dyDescent="0.25">
@@ -21483,8 +21496,8 @@
       <c r="L558" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M558" s="3">
-        <v>45815</v>
+      <c r="M558" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="559" spans="2:13" x14ac:dyDescent="0.25">
@@ -21521,8 +21534,8 @@
       <c r="L559" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M559" s="3">
-        <v>45815</v>
+      <c r="M559" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="560" spans="2:13" x14ac:dyDescent="0.25">
@@ -21559,8 +21572,8 @@
       <c r="L560" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M560" s="3">
-        <v>45815</v>
+      <c r="M560" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="561" spans="2:13" x14ac:dyDescent="0.25">
@@ -21597,8 +21610,8 @@
       <c r="L561" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M561" s="3">
-        <v>45815</v>
+      <c r="M561" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="562" spans="2:13" x14ac:dyDescent="0.25">
@@ -21635,8 +21648,8 @@
       <c r="L562" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M562" s="3">
-        <v>45815</v>
+      <c r="M562" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="563" spans="2:13" x14ac:dyDescent="0.25">
@@ -21673,8 +21686,8 @@
       <c r="L563" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M563" s="3">
-        <v>45815</v>
+      <c r="M563" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="564" spans="2:13" x14ac:dyDescent="0.25">
@@ -21711,8 +21724,8 @@
       <c r="L564" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M564" s="3">
-        <v>45815</v>
+      <c r="M564" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="565" spans="2:13" x14ac:dyDescent="0.25">
@@ -21749,8 +21762,8 @@
       <c r="L565" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M565" s="3">
-        <v>45815</v>
+      <c r="M565" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="566" spans="2:13" x14ac:dyDescent="0.25">
@@ -21787,8 +21800,8 @@
       <c r="L566" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M566" s="3">
-        <v>45815</v>
+      <c r="M566" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="567" spans="2:13" x14ac:dyDescent="0.25">
@@ -21825,8 +21838,8 @@
       <c r="L567" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M567" s="3">
-        <v>45815</v>
+      <c r="M567" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="568" spans="2:13" x14ac:dyDescent="0.25">
@@ -21863,8 +21876,8 @@
       <c r="L568" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M568" s="3">
-        <v>45815</v>
+      <c r="M568" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="569" spans="2:13" x14ac:dyDescent="0.25">
@@ -21901,8 +21914,8 @@
       <c r="L569" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M569" s="3">
-        <v>45815</v>
+      <c r="M569" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="570" spans="2:13" x14ac:dyDescent="0.25">
@@ -21939,8 +21952,8 @@
       <c r="L570" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M570" s="3">
-        <v>45815</v>
+      <c r="M570" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="571" spans="2:13" x14ac:dyDescent="0.25">
@@ -21977,8 +21990,8 @@
       <c r="L571" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M571" s="3">
-        <v>45815</v>
+      <c r="M571" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="572" spans="2:13" x14ac:dyDescent="0.25">
@@ -22015,8 +22028,8 @@
       <c r="L572" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M572" s="3">
-        <v>45815</v>
+      <c r="M572" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="573" spans="2:13" x14ac:dyDescent="0.25">
@@ -22053,8 +22066,8 @@
       <c r="L573" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M573" s="3">
-        <v>45815</v>
+      <c r="M573" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="574" spans="2:13" x14ac:dyDescent="0.25">
@@ -22091,8 +22104,8 @@
       <c r="L574" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M574" s="3">
-        <v>45815</v>
+      <c r="M574" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="575" spans="2:13" x14ac:dyDescent="0.25">
@@ -22129,8 +22142,8 @@
       <c r="L575" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M575" s="3">
-        <v>45815</v>
+      <c r="M575" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="576" spans="2:13" x14ac:dyDescent="0.25">
@@ -22167,8 +22180,8 @@
       <c r="L576" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M576" s="3">
-        <v>45815</v>
+      <c r="M576" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="577" spans="2:13" x14ac:dyDescent="0.25">
@@ -22205,8 +22218,8 @@
       <c r="L577" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M577" s="3">
-        <v>45815</v>
+      <c r="M577" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="578" spans="2:13" x14ac:dyDescent="0.25">
@@ -22243,8 +22256,8 @@
       <c r="L578" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M578" s="3">
-        <v>45815</v>
+      <c r="M578" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="579" spans="2:13" x14ac:dyDescent="0.25">
@@ -22281,8 +22294,8 @@
       <c r="L579" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M579" s="3">
-        <v>45815</v>
+      <c r="M579" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="580" spans="2:13" x14ac:dyDescent="0.25">
@@ -22319,8 +22332,8 @@
       <c r="L580" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M580" s="3">
-        <v>45815</v>
+      <c r="M580" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="581" spans="2:13" x14ac:dyDescent="0.25">
@@ -22357,8 +22370,8 @@
       <c r="L581" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M581" s="3">
-        <v>45815</v>
+      <c r="M581" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="582" spans="2:13" x14ac:dyDescent="0.25">
@@ -22395,8 +22408,8 @@
       <c r="L582" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M582" s="3">
-        <v>45815</v>
+      <c r="M582" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="583" spans="2:13" x14ac:dyDescent="0.25">
@@ -22433,8 +22446,8 @@
       <c r="L583" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M583" s="3">
-        <v>45815</v>
+      <c r="M583" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="584" spans="2:13" x14ac:dyDescent="0.25">
@@ -22471,8 +22484,8 @@
       <c r="L584" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M584" s="3">
-        <v>45815</v>
+      <c r="M584" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="585" spans="2:13" x14ac:dyDescent="0.25">
@@ -22509,8 +22522,8 @@
       <c r="L585" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M585" s="3">
-        <v>45815</v>
+      <c r="M585" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="586" spans="2:13" x14ac:dyDescent="0.25">
@@ -22547,8 +22560,8 @@
       <c r="L586" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M586" s="3">
-        <v>45815</v>
+      <c r="M586" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="587" spans="2:13" x14ac:dyDescent="0.25">
@@ -22585,8 +22598,8 @@
       <c r="L587" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M587" s="3">
-        <v>45815</v>
+      <c r="M587" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="588" spans="2:13" x14ac:dyDescent="0.25">
@@ -22623,8 +22636,8 @@
       <c r="L588" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M588" s="3">
-        <v>45815</v>
+      <c r="M588" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="589" spans="2:13" x14ac:dyDescent="0.25">
@@ -22661,8 +22674,8 @@
       <c r="L589" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M589" s="3">
-        <v>45815</v>
+      <c r="M589" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="590" spans="2:13" x14ac:dyDescent="0.25">
@@ -22699,8 +22712,8 @@
       <c r="L590" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M590" s="3">
-        <v>45815</v>
+      <c r="M590" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="591" spans="2:13" x14ac:dyDescent="0.25">
@@ -22737,8 +22750,8 @@
       <c r="L591" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M591" s="3">
-        <v>45815</v>
+      <c r="M591" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="592" spans="2:13" x14ac:dyDescent="0.25">
@@ -22775,8 +22788,8 @@
       <c r="L592" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M592" s="3">
-        <v>45815</v>
+      <c r="M592" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="593" spans="2:13" x14ac:dyDescent="0.25">
@@ -22813,8 +22826,8 @@
       <c r="L593" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M593" s="3">
-        <v>45815</v>
+      <c r="M593" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="594" spans="2:13" x14ac:dyDescent="0.25">
@@ -22851,8 +22864,8 @@
       <c r="L594" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M594" s="3">
-        <v>45815</v>
+      <c r="M594" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="595" spans="2:13" x14ac:dyDescent="0.25">
@@ -22889,8 +22902,8 @@
       <c r="L595" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M595" s="3">
-        <v>45815</v>
+      <c r="M595" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="596" spans="2:13" x14ac:dyDescent="0.25">
@@ -22927,8 +22940,8 @@
       <c r="L596" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M596" s="3">
-        <v>45815</v>
+      <c r="M596" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="597" spans="2:13" x14ac:dyDescent="0.25">
@@ -22965,8 +22978,8 @@
       <c r="L597" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M597" s="3">
-        <v>45815</v>
+      <c r="M597" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="598" spans="2:13" x14ac:dyDescent="0.25">
@@ -23003,8 +23016,8 @@
       <c r="L598" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M598" s="3">
-        <v>45815</v>
+      <c r="M598" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="599" spans="2:13" x14ac:dyDescent="0.25">
@@ -23041,8 +23054,8 @@
       <c r="L599" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M599" s="3">
-        <v>45815</v>
+      <c r="M599" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="600" spans="2:13" x14ac:dyDescent="0.25">
@@ -23079,8 +23092,8 @@
       <c r="L600" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M600" s="3">
-        <v>45815</v>
+      <c r="M600" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="601" spans="2:13" x14ac:dyDescent="0.25">
@@ -23117,8 +23130,8 @@
       <c r="L601" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M601" s="3">
-        <v>45815</v>
+      <c r="M601" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="602" spans="2:13" x14ac:dyDescent="0.25">
@@ -23155,8 +23168,8 @@
       <c r="L602" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M602" s="3">
-        <v>45815</v>
+      <c r="M602" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="603" spans="2:13" x14ac:dyDescent="0.25">
@@ -23193,8 +23206,8 @@
       <c r="L603" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M603" s="3">
-        <v>45815</v>
+      <c r="M603" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="604" spans="2:13" x14ac:dyDescent="0.25">
@@ -23231,8 +23244,8 @@
       <c r="L604" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M604" s="3">
-        <v>45815</v>
+      <c r="M604" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="605" spans="2:13" x14ac:dyDescent="0.25">
@@ -23269,8 +23282,8 @@
       <c r="L605" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M605" s="3">
-        <v>45815</v>
+      <c r="M605" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="606" spans="2:13" x14ac:dyDescent="0.25">
@@ -23307,8 +23320,8 @@
       <c r="L606" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M606" s="3">
-        <v>45815</v>
+      <c r="M606" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="607" spans="2:13" x14ac:dyDescent="0.25">
@@ -23345,8 +23358,8 @@
       <c r="L607" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M607" s="3">
-        <v>45815</v>
+      <c r="M607" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="608" spans="2:13" x14ac:dyDescent="0.25">
@@ -23383,8 +23396,8 @@
       <c r="L608" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M608" s="3">
-        <v>45815</v>
+      <c r="M608" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="609" spans="2:13" x14ac:dyDescent="0.25">
@@ -23421,8 +23434,8 @@
       <c r="L609" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M609" s="3">
-        <v>45815</v>
+      <c r="M609" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="610" spans="2:13" x14ac:dyDescent="0.25">
@@ -23459,8 +23472,8 @@
       <c r="L610" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M610" s="3">
-        <v>45815</v>
+      <c r="M610" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="611" spans="2:13" x14ac:dyDescent="0.25">
@@ -23497,8 +23510,8 @@
       <c r="L611" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M611" s="3">
-        <v>45815</v>
+      <c r="M611" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="612" spans="2:13" x14ac:dyDescent="0.25">
@@ -23535,8 +23548,8 @@
       <c r="L612" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M612" s="3">
-        <v>45815</v>
+      <c r="M612" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="613" spans="2:13" x14ac:dyDescent="0.25">
@@ -23573,8 +23586,8 @@
       <c r="L613" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M613" s="3">
-        <v>45815</v>
+      <c r="M613" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="614" spans="2:13" x14ac:dyDescent="0.25">
@@ -23611,8 +23624,8 @@
       <c r="L614" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M614" s="3">
-        <v>45815</v>
+      <c r="M614" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="615" spans="2:13" x14ac:dyDescent="0.25">
@@ -23649,8 +23662,8 @@
       <c r="L615" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M615" s="3">
-        <v>45815</v>
+      <c r="M615" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="616" spans="2:13" x14ac:dyDescent="0.25">
@@ -23687,8 +23700,8 @@
       <c r="L616" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M616" s="3">
-        <v>45815</v>
+      <c r="M616" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="617" spans="2:13" x14ac:dyDescent="0.25">
@@ -23725,8 +23738,8 @@
       <c r="L617" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M617" s="3">
-        <v>45815</v>
+      <c r="M617" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="618" spans="2:13" x14ac:dyDescent="0.25">
@@ -23763,8 +23776,8 @@
       <c r="L618" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M618" s="3">
-        <v>45815</v>
+      <c r="M618" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="619" spans="2:13" x14ac:dyDescent="0.25">
@@ -23801,8 +23814,8 @@
       <c r="L619" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M619" s="3">
-        <v>45815</v>
+      <c r="M619" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="620" spans="2:13" x14ac:dyDescent="0.25">
@@ -23839,8 +23852,8 @@
       <c r="L620" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M620" s="3">
-        <v>45815</v>
+      <c r="M620" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="621" spans="2:13" x14ac:dyDescent="0.25">
@@ -23877,8 +23890,8 @@
       <c r="L621" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M621" s="3">
-        <v>45815</v>
+      <c r="M621" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="622" spans="2:13" x14ac:dyDescent="0.25">
@@ -23915,8 +23928,8 @@
       <c r="L622" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M622" s="3">
-        <v>45815</v>
+      <c r="M622" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="623" spans="2:13" x14ac:dyDescent="0.25">
@@ -23953,8 +23966,8 @@
       <c r="L623" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M623" s="3">
-        <v>45815</v>
+      <c r="M623" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="624" spans="2:13" x14ac:dyDescent="0.25">
@@ -23991,8 +24004,8 @@
       <c r="L624" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M624" s="3">
-        <v>45815</v>
+      <c r="M624" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="625" spans="1:13" x14ac:dyDescent="0.25">
@@ -24029,8 +24042,8 @@
       <c r="L625" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M625" s="3">
-        <v>45815</v>
+      <c r="M625" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="626" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24067,8 +24080,8 @@
       <c r="L626" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M626" s="2">
-        <v>45815</v>
+      <c r="M626" s="2" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="627" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24106,8 +24119,8 @@
       <c r="L627" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M627" s="2">
-        <v>45816</v>
+      <c r="M627" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="628" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24145,8 +24158,8 @@
       <c r="L628" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M628" s="2">
-        <v>45816</v>
+      <c r="M628" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="629" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24184,8 +24197,8 @@
       <c r="L629" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M629" s="2">
-        <v>45816</v>
+      <c r="M629" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="630" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24223,8 +24236,8 @@
       <c r="L630" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M630" s="2">
-        <v>45816</v>
+      <c r="M630" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="631" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24262,8 +24275,8 @@
       <c r="L631" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M631" s="2">
-        <v>45816</v>
+      <c r="M631" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="632" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24301,8 +24314,8 @@
       <c r="L632" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M632" s="2">
-        <v>45816</v>
+      <c r="M632" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="633" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24340,8 +24353,8 @@
       <c r="L633" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M633" s="2">
-        <v>45816</v>
+      <c r="M633" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="634" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24379,8 +24392,8 @@
       <c r="L634" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M634" s="2">
-        <v>45816</v>
+      <c r="M634" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="635" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24418,8 +24431,8 @@
       <c r="L635" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M635" s="2">
-        <v>45816</v>
+      <c r="M635" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="636" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24457,8 +24470,8 @@
       <c r="L636" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M636" s="2">
-        <v>45816</v>
+      <c r="M636" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="637" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24496,8 +24509,8 @@
       <c r="L637" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M637" s="2">
-        <v>45816</v>
+      <c r="M637" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="638" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24535,8 +24548,8 @@
       <c r="L638" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M638" s="2">
-        <v>45816</v>
+      <c r="M638" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="639" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24574,8 +24587,8 @@
       <c r="L639" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M639" s="2">
-        <v>45816</v>
+      <c r="M639" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="640" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24613,8 +24626,8 @@
       <c r="L640" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M640" s="2">
-        <v>45816</v>
+      <c r="M640" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="641" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24652,8 +24665,8 @@
       <c r="L641" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M641" s="2">
-        <v>45816</v>
+      <c r="M641" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="642" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24691,8 +24704,8 @@
       <c r="L642" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M642" s="2">
-        <v>45816</v>
+      <c r="M642" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="643" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24730,8 +24743,8 @@
       <c r="L643" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M643" s="2">
-        <v>45816</v>
+      <c r="M643" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="644" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24769,8 +24782,8 @@
       <c r="L644" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M644" s="2">
-        <v>45816</v>
+      <c r="M644" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="645" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24808,8 +24821,8 @@
       <c r="L645" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M645" s="2">
-        <v>45816</v>
+      <c r="M645" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="646" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24847,8 +24860,8 @@
       <c r="L646" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M646" s="2">
-        <v>45816</v>
+      <c r="M646" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="647" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24886,8 +24899,8 @@
       <c r="L647" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M647" s="2">
-        <v>45816</v>
+      <c r="M647" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="648" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24925,8 +24938,8 @@
       <c r="L648" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M648" s="2">
-        <v>45816</v>
+      <c r="M648" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="649" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -24964,8 +24977,8 @@
       <c r="L649" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M649" s="2">
-        <v>45816</v>
+      <c r="M649" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="650" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25003,8 +25016,8 @@
       <c r="L650" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M650" s="2">
-        <v>45816</v>
+      <c r="M650" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="651" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25042,8 +25055,8 @@
       <c r="L651" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M651" s="2">
-        <v>45816</v>
+      <c r="M651" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="652" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25081,8 +25094,8 @@
       <c r="L652" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M652" s="2">
-        <v>45816</v>
+      <c r="M652" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="653" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25120,8 +25133,8 @@
       <c r="L653" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M653" s="2">
-        <v>45816</v>
+      <c r="M653" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="654" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25159,8 +25172,8 @@
       <c r="L654" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M654" s="2">
-        <v>45816</v>
+      <c r="M654" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="655" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25198,8 +25211,8 @@
       <c r="L655" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M655" s="2">
-        <v>45816</v>
+      <c r="M655" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="656" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25237,8 +25250,8 @@
       <c r="L656" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M656" s="2">
-        <v>45816</v>
+      <c r="M656" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="657" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25276,8 +25289,8 @@
       <c r="L657" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M657" s="2">
-        <v>45816</v>
+      <c r="M657" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="658" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25315,8 +25328,8 @@
       <c r="L658" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M658" s="2">
-        <v>45816</v>
+      <c r="M658" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="659" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25354,8 +25367,8 @@
       <c r="L659" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M659" s="2">
-        <v>45816</v>
+      <c r="M659" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="660" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25393,8 +25406,8 @@
       <c r="L660" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M660" s="2">
-        <v>45816</v>
+      <c r="M660" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="661" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25432,8 +25445,8 @@
       <c r="L661" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M661" s="2">
-        <v>45816</v>
+      <c r="M661" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="662" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25471,8 +25484,8 @@
       <c r="L662" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M662" s="2">
-        <v>45816</v>
+      <c r="M662" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="663" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25510,8 +25523,8 @@
       <c r="L663" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M663" s="2">
-        <v>45816</v>
+      <c r="M663" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="664" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25549,8 +25562,8 @@
       <c r="L664" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M664" s="2">
-        <v>45816</v>
+      <c r="M664" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="665" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25588,8 +25601,8 @@
       <c r="L665" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M665" s="2">
-        <v>45816</v>
+      <c r="M665" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="666" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25627,8 +25640,8 @@
       <c r="L666" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M666" s="2">
-        <v>45816</v>
+      <c r="M666" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="667" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25666,8 +25679,8 @@
       <c r="L667" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M667" s="2">
-        <v>45816</v>
+      <c r="M667" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="668" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25705,8 +25718,8 @@
       <c r="L668" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M668" s="2">
-        <v>45816</v>
+      <c r="M668" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="669" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25744,8 +25757,8 @@
       <c r="L669" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M669" s="2">
-        <v>45816</v>
+      <c r="M669" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="670" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25783,8 +25796,8 @@
       <c r="L670" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M670" s="2">
-        <v>45816</v>
+      <c r="M670" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="671" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25822,8 +25835,8 @@
       <c r="L671" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M671" s="2">
-        <v>45816</v>
+      <c r="M671" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="672" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25861,8 +25874,8 @@
       <c r="L672" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M672" s="2">
-        <v>45816</v>
+      <c r="M672" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="673" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25900,8 +25913,8 @@
       <c r="L673" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M673" s="2">
-        <v>45816</v>
+      <c r="M673" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="674" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25939,8 +25952,8 @@
       <c r="L674" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M674" s="2">
-        <v>45816</v>
+      <c r="M674" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="675" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -25978,8 +25991,8 @@
       <c r="L675" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M675" s="2">
-        <v>45816</v>
+      <c r="M675" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="676" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26017,8 +26030,8 @@
       <c r="L676" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M676" s="2">
-        <v>45816</v>
+      <c r="M676" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="677" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26056,8 +26069,8 @@
       <c r="L677" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M677" s="2">
-        <v>45816</v>
+      <c r="M677" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="678" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26095,8 +26108,8 @@
       <c r="L678" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M678" s="2">
-        <v>45816</v>
+      <c r="M678" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="679" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26134,8 +26147,8 @@
       <c r="L679" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M679" s="2">
-        <v>45816</v>
+      <c r="M679" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="680" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26173,8 +26186,8 @@
       <c r="L680" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M680" s="2">
-        <v>45816</v>
+      <c r="M680" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="681" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26212,8 +26225,8 @@
       <c r="L681" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M681" s="2">
-        <v>45816</v>
+      <c r="M681" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="682" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26251,8 +26264,8 @@
       <c r="L682" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M682" s="2">
-        <v>45816</v>
+      <c r="M682" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="683" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26290,8 +26303,8 @@
       <c r="L683" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M683" s="2">
-        <v>45816</v>
+      <c r="M683" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="684" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26329,8 +26342,8 @@
       <c r="L684" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M684" s="2">
-        <v>45816</v>
+      <c r="M684" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="685" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26368,8 +26381,8 @@
       <c r="L685" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M685" s="2">
-        <v>45816</v>
+      <c r="M685" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="686" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26407,8 +26420,8 @@
       <c r="L686" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M686" s="2">
-        <v>45816</v>
+      <c r="M686" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="687" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26446,8 +26459,8 @@
       <c r="L687" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M687" s="2">
-        <v>45816</v>
+      <c r="M687" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="688" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26485,8 +26498,8 @@
       <c r="L688" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M688" s="2">
-        <v>45816</v>
+      <c r="M688" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="689" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26524,8 +26537,8 @@
       <c r="L689" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M689" s="2">
-        <v>45816</v>
+      <c r="M689" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="690" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26563,8 +26576,8 @@
       <c r="L690" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M690" s="2">
-        <v>45816</v>
+      <c r="M690" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="691" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26602,8 +26615,8 @@
       <c r="L691" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M691" s="2">
-        <v>45816</v>
+      <c r="M691" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="692" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26641,8 +26654,8 @@
       <c r="L692" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M692" s="2">
-        <v>45816</v>
+      <c r="M692" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="693" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26680,8 +26693,8 @@
       <c r="L693" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M693" s="2">
-        <v>45816</v>
+      <c r="M693" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="694" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26719,8 +26732,8 @@
       <c r="L694" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M694" s="2">
-        <v>45816</v>
+      <c r="M694" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="695" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26758,8 +26771,8 @@
       <c r="L695" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M695" s="2">
-        <v>45816</v>
+      <c r="M695" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="696" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26797,8 +26810,8 @@
       <c r="L696" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M696" s="2">
-        <v>45816</v>
+      <c r="M696" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="697" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26836,8 +26849,8 @@
       <c r="L697" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M697" s="2">
-        <v>45816</v>
+      <c r="M697" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="698" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26875,8 +26888,8 @@
       <c r="L698" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M698" s="2">
-        <v>45816</v>
+      <c r="M698" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="699" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26914,8 +26927,8 @@
       <c r="L699" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M699" s="2">
-        <v>45816</v>
+      <c r="M699" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="700" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26953,8 +26966,8 @@
       <c r="L700" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M700" s="2">
-        <v>45816</v>
+      <c r="M700" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="701" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -26992,8 +27005,8 @@
       <c r="L701" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M701" s="2">
-        <v>45816</v>
+      <c r="M701" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="702" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27031,8 +27044,8 @@
       <c r="L702" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M702" s="2">
-        <v>45816</v>
+      <c r="M702" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="703" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27070,8 +27083,8 @@
       <c r="L703" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M703" s="2">
-        <v>45816</v>
+      <c r="M703" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="704" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27109,8 +27122,8 @@
       <c r="L704" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M704" s="2">
-        <v>45816</v>
+      <c r="M704" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="705" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27148,8 +27161,8 @@
       <c r="L705" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M705" s="2">
-        <v>45816</v>
+      <c r="M705" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="706" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27187,8 +27200,8 @@
       <c r="L706" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M706" s="2">
-        <v>45816</v>
+      <c r="M706" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="707" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27226,8 +27239,8 @@
       <c r="L707" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M707" s="2">
-        <v>45816</v>
+      <c r="M707" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="708" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27265,8 +27278,8 @@
       <c r="L708" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M708" s="2">
-        <v>45816</v>
+      <c r="M708" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="709" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27304,8 +27317,8 @@
       <c r="L709" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M709" s="2">
-        <v>45816</v>
+      <c r="M709" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="710" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27343,8 +27356,8 @@
       <c r="L710" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M710" s="2">
-        <v>45816</v>
+      <c r="M710" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="711" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27382,8 +27395,8 @@
       <c r="L711" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M711" s="2">
-        <v>45816</v>
+      <c r="M711" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="712" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27421,8 +27434,8 @@
       <c r="L712" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M712" s="2">
-        <v>45816</v>
+      <c r="M712" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="713" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27460,8 +27473,8 @@
       <c r="L713" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M713" s="2">
-        <v>45817</v>
+      <c r="M713" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="714" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27499,8 +27512,8 @@
       <c r="L714" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M714" s="2">
-        <v>45817</v>
+      <c r="M714" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="715" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27538,8 +27551,8 @@
       <c r="L715" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M715" s="2">
-        <v>45817</v>
+      <c r="M715" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="716" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27577,8 +27590,8 @@
       <c r="L716" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M716" s="2">
-        <v>45817</v>
+      <c r="M716" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="717" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27616,8 +27629,8 @@
       <c r="L717" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M717" s="2">
-        <v>45817</v>
+      <c r="M717" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="718" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27655,8 +27668,8 @@
       <c r="L718" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M718" s="2">
-        <v>45817</v>
+      <c r="M718" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="719" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27694,8 +27707,8 @@
       <c r="L719" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M719" s="2">
-        <v>45817</v>
+      <c r="M719" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="720" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27733,8 +27746,8 @@
       <c r="L720" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M720" s="2">
-        <v>45817</v>
+      <c r="M720" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="721" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27772,8 +27785,8 @@
       <c r="L721" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M721" s="2">
-        <v>45817</v>
+      <c r="M721" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="722" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27811,8 +27824,8 @@
       <c r="L722" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M722" s="2">
-        <v>45817</v>
+      <c r="M722" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="723" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27850,8 +27863,8 @@
       <c r="L723" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M723" s="2">
-        <v>45817</v>
+      <c r="M723" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="724" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27889,8 +27902,8 @@
       <c r="L724" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M724" s="2">
-        <v>45817</v>
+      <c r="M724" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="725" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27928,8 +27941,8 @@
       <c r="L725" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M725" s="2">
-        <v>45817</v>
+      <c r="M725" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="726" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -27967,8 +27980,8 @@
       <c r="L726" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M726" s="2">
-        <v>45817</v>
+      <c r="M726" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="727" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28006,8 +28019,8 @@
       <c r="L727" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M727" s="2">
-        <v>45817</v>
+      <c r="M727" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="728" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28045,8 +28058,8 @@
       <c r="L728" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M728" s="2">
-        <v>45817</v>
+      <c r="M728" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="729" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28084,8 +28097,8 @@
       <c r="L729" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M729" s="2">
-        <v>45817</v>
+      <c r="M729" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="730" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28123,8 +28136,8 @@
       <c r="L730" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M730" s="2">
-        <v>45817</v>
+      <c r="M730" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="731" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28162,8 +28175,8 @@
       <c r="L731" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M731" s="2">
-        <v>45817</v>
+      <c r="M731" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="732" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28201,8 +28214,8 @@
       <c r="L732" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M732" s="2">
-        <v>45817</v>
+      <c r="M732" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="733" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28240,8 +28253,8 @@
       <c r="L733" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M733" s="2">
-        <v>45817</v>
+      <c r="M733" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="734" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28279,8 +28292,8 @@
       <c r="L734" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M734" s="2">
-        <v>45817</v>
+      <c r="M734" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="735" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28318,8 +28331,8 @@
       <c r="L735" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M735" s="2">
-        <v>45817</v>
+      <c r="M735" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="736" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28357,8 +28370,8 @@
       <c r="L736" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M736" s="2">
-        <v>45817</v>
+      <c r="M736" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="737" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28396,8 +28409,8 @@
       <c r="L737" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M737" s="2">
-        <v>45817</v>
+      <c r="M737" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="738" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28435,8 +28448,8 @@
       <c r="L738" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M738" s="2">
-        <v>45817</v>
+      <c r="M738" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="739" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28474,8 +28487,8 @@
       <c r="L739" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M739" s="2">
-        <v>45817</v>
+      <c r="M739" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="740" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28513,8 +28526,8 @@
       <c r="L740" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M740" s="2">
-        <v>45817</v>
+      <c r="M740" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="741" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28552,8 +28565,8 @@
       <c r="L741" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M741" s="2">
-        <v>45817</v>
+      <c r="M741" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="742" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28591,8 +28604,8 @@
       <c r="L742" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M742" s="2">
-        <v>45817</v>
+      <c r="M742" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="743" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28630,8 +28643,8 @@
       <c r="L743" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M743" s="2">
-        <v>45817</v>
+      <c r="M743" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="744" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28669,8 +28682,8 @@
       <c r="L744" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M744" s="2">
-        <v>45817</v>
+      <c r="M744" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="745" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28708,8 +28721,8 @@
       <c r="L745" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M745" s="2">
-        <v>45817</v>
+      <c r="M745" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="746" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28747,8 +28760,8 @@
       <c r="L746" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M746" s="2">
-        <v>45817</v>
+      <c r="M746" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="747" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28786,8 +28799,8 @@
       <c r="L747" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M747" s="2">
-        <v>45817</v>
+      <c r="M747" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="748" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28825,8 +28838,8 @@
       <c r="L748" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M748" s="2">
-        <v>45817</v>
+      <c r="M748" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="749" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28864,8 +28877,8 @@
       <c r="L749" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M749" s="2">
-        <v>45817</v>
+      <c r="M749" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="750" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28903,8 +28916,8 @@
       <c r="L750" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M750" s="2">
-        <v>45817</v>
+      <c r="M750" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="751" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28942,8 +28955,8 @@
       <c r="L751" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M751" s="2">
-        <v>45817</v>
+      <c r="M751" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="752" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -28981,8 +28994,8 @@
       <c r="L752" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M752" s="2">
-        <v>45817</v>
+      <c r="M752" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="753" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29020,8 +29033,8 @@
       <c r="L753" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M753" s="2">
-        <v>45817</v>
+      <c r="M753" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="754" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29059,8 +29072,8 @@
       <c r="L754" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M754" s="2">
-        <v>45817</v>
+      <c r="M754" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="755" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29098,8 +29111,8 @@
       <c r="L755" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M755" s="2">
-        <v>45817</v>
+      <c r="M755" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="756" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29137,8 +29150,8 @@
       <c r="L756" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M756" s="2">
-        <v>45817</v>
+      <c r="M756" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="757" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29176,8 +29189,8 @@
       <c r="L757" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M757" s="2">
-        <v>45817</v>
+      <c r="M757" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="758" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29215,8 +29228,8 @@
       <c r="L758" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M758" s="2">
-        <v>45817</v>
+      <c r="M758" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="759" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29254,8 +29267,8 @@
       <c r="L759" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M759" s="2">
-        <v>45817</v>
+      <c r="M759" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="760" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29293,8 +29306,8 @@
       <c r="L760" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M760" s="2">
-        <v>45817</v>
+      <c r="M760" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="761" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29332,8 +29345,8 @@
       <c r="L761" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M761" s="2">
-        <v>45817</v>
+      <c r="M761" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="762" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29371,8 +29384,8 @@
       <c r="L762" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M762" s="2">
-        <v>45817</v>
+      <c r="M762" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="763" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29410,8 +29423,8 @@
       <c r="L763" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M763" s="2">
-        <v>45817</v>
+      <c r="M763" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="764" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29449,8 +29462,8 @@
       <c r="L764" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M764" s="2">
-        <v>45817</v>
+      <c r="M764" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="765" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29488,8 +29501,8 @@
       <c r="L765" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M765" s="2">
-        <v>45817</v>
+      <c r="M765" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="766" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29527,8 +29540,8 @@
       <c r="L766" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M766" s="2">
-        <v>45817</v>
+      <c r="M766" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="767" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29566,8 +29579,8 @@
       <c r="L767" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M767" s="2">
-        <v>45817</v>
+      <c r="M767" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="768" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29605,8 +29618,8 @@
       <c r="L768" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M768" s="2">
-        <v>45817</v>
+      <c r="M768" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="769" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29644,8 +29657,8 @@
       <c r="L769" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M769" s="2">
-        <v>45817</v>
+      <c r="M769" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="770" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29683,8 +29696,8 @@
       <c r="L770" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M770" s="2">
-        <v>45817</v>
+      <c r="M770" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="771" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29722,8 +29735,8 @@
       <c r="L771" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M771" s="2">
-        <v>45817</v>
+      <c r="M771" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="772" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29761,8 +29774,8 @@
       <c r="L772" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M772" s="2">
-        <v>45817</v>
+      <c r="M772" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="773" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29800,8 +29813,8 @@
       <c r="L773" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M773" s="2">
-        <v>45817</v>
+      <c r="M773" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="774" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29839,8 +29852,8 @@
       <c r="L774" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M774" s="2">
-        <v>45817</v>
+      <c r="M774" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="775" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29878,8 +29891,8 @@
       <c r="L775" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M775" s="2">
-        <v>45817</v>
+      <c r="M775" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="776" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29917,8 +29930,8 @@
       <c r="L776" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M776" s="2">
-        <v>45817</v>
+      <c r="M776" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="777" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29956,8 +29969,8 @@
       <c r="L777" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M777" s="2">
-        <v>45817</v>
+      <c r="M777" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="778" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -29995,8 +30008,8 @@
       <c r="L778" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M778" s="2">
-        <v>45817</v>
+      <c r="M778" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="779" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -30034,8 +30047,8 @@
       <c r="L779" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M779" s="2">
-        <v>45817</v>
+      <c r="M779" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="780" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -30073,8 +30086,8 @@
       <c r="L780" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M780" s="2">
-        <v>45817</v>
+      <c r="M780" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="781" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -30112,8 +30125,8 @@
       <c r="L781" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M781" s="2">
-        <v>45817</v>
+      <c r="M781" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="782" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -30151,8 +30164,8 @@
       <c r="L782" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M782" s="2">
-        <v>45817</v>
+      <c r="M782" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="783" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -30190,8 +30203,8 @@
       <c r="L783" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M783" s="2">
-        <v>45817</v>
+      <c r="M783" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="784" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -30229,8 +30242,8 @@
       <c r="L784" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M784" s="2">
-        <v>45817</v>
+      <c r="M784" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="785" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -30268,8 +30281,8 @@
       <c r="L785" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M785" s="2">
-        <v>45817</v>
+      <c r="M785" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="786" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -30307,8 +30320,8 @@
       <c r="L786" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M786" s="2">
-        <v>45817</v>
+      <c r="M786" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="787" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -30346,8 +30359,8 @@
       <c r="L787" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M787" s="2">
-        <v>45817</v>
+      <c r="M787" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="788" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -30385,8 +30398,8 @@
       <c r="L788" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M788" s="2">
-        <v>45817</v>
+      <c r="M788" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="789" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -30424,8 +30437,8 @@
       <c r="L789" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M789" s="2">
-        <v>45817</v>
+      <c r="M789" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="790" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -30463,8 +30476,8 @@
       <c r="L790" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M790" s="2">
-        <v>45817</v>
+      <c r="M790" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="791" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -30502,8 +30515,8 @@
       <c r="L791" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M791" s="2">
-        <v>45817</v>
+      <c r="M791" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="792" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -30541,8 +30554,8 @@
       <c r="L792" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M792" s="2">
-        <v>45817</v>
+      <c r="M792" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="793" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -30580,8 +30593,8 @@
       <c r="L793" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M793" s="2">
-        <v>45817</v>
+      <c r="M793" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="794" spans="1:13" x14ac:dyDescent="0.25">
@@ -30619,8 +30632,8 @@
       <c r="L794" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M794" s="2">
-        <v>45817</v>
+      <c r="M794" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/TM_all.xlsx
+++ b/TM_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aecf56309e6168f4/Documents/comunio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C13399CE-4562-480F-9F20-1F4A912D9517}"/>
+  <xr:revisionPtr revIDLastSave="214" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45D9059B-905C-4C1F-88CF-0CDFBF289F64}"/>
   <bookViews>
     <workbookView xWindow="2110" yWindow="2130" windowWidth="28800" windowHeight="15370" xr2:uid="{607DE709-F91E-4262-9941-1066BBEC319E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5971" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6643" uniqueCount="274">
   <si>
     <t>Spieler</t>
   </si>
@@ -718,6 +718,150 @@
   <si>
     <t>10.06.2025</t>
   </si>
+  <si>
+    <t>3,2</t>
+  </si>
+  <si>
+    <t>4,1</t>
+  </si>
+  <si>
+    <t>2,5</t>
+  </si>
+  <si>
+    <t>Ginter</t>
+  </si>
+  <si>
+    <t>4,0</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>3,8</t>
+  </si>
+  <si>
+    <t>2,9</t>
+  </si>
+  <si>
+    <t>2,1</t>
+  </si>
+  <si>
+    <t>3,9</t>
+  </si>
+  <si>
+    <t>5,9</t>
+  </si>
+  <si>
+    <t>3,4</t>
+  </si>
+  <si>
+    <t>2,8</t>
+  </si>
+  <si>
+    <t>4,2</t>
+  </si>
+  <si>
+    <t>A. Jung</t>
+  </si>
+  <si>
+    <t>2,6</t>
+  </si>
+  <si>
+    <t>3,1</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>1,0</t>
+  </si>
+  <si>
+    <t>3,5</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>1,8</t>
+  </si>
+  <si>
+    <t>3,6</t>
+  </si>
+  <si>
+    <t>Kilian</t>
+  </si>
+  <si>
+    <t>0,9</t>
+  </si>
+  <si>
+    <t>1,5</t>
+  </si>
+  <si>
+    <t>2,7</t>
+  </si>
+  <si>
+    <t>8,0</t>
+  </si>
+  <si>
+    <t>5,8</t>
+  </si>
+  <si>
+    <t>5,4</t>
+  </si>
+  <si>
+    <t>0,0</t>
+  </si>
+  <si>
+    <t>Schäfer</t>
+  </si>
+  <si>
+    <t>Nsoki</t>
+  </si>
+  <si>
+    <t>2,4</t>
+  </si>
+  <si>
+    <t>Milošević</t>
+  </si>
+  <si>
+    <t>1,3</t>
+  </si>
+  <si>
+    <t>4,9</t>
+  </si>
+  <si>
+    <t>4,8</t>
+  </si>
+  <si>
+    <t>4,3</t>
+  </si>
+  <si>
+    <t>1,6</t>
+  </si>
+  <si>
+    <t>1,4</t>
+  </si>
+  <si>
+    <t>Ogbus</t>
+  </si>
+  <si>
+    <t>2,0</t>
+  </si>
+  <si>
+    <t>5,2</t>
+  </si>
+  <si>
+    <t>Al-Dakhil</t>
+  </si>
+  <si>
+    <t>1,9</t>
+  </si>
+  <si>
+    <t>Diks</t>
+  </si>
+  <si>
+    <t>11.06.2026</t>
+  </si>
 </sst>
 </file>
 
@@ -1157,7 +1301,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93EB6F54-7766-4759-97DF-03549A275A7C}">
-  <dimension ref="A1:M882"/>
+  <dimension ref="A1:M966"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="2"/>
@@ -34069,7 +34213,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="882" spans="1:13" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A882" s="6"/>
       <c r="B882" s="7" t="s">
         <v>121</v>
@@ -34106,6 +34250,3282 @@
       </c>
       <c r="M882" s="9" t="s">
         <v>225</v>
+      </c>
+    </row>
+    <row r="883" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A883" s="6"/>
+      <c r="B883" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C883" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D883" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E883" s="6">
+        <v>70</v>
+      </c>
+      <c r="F883" s="8">
+        <v>2050000</v>
+      </c>
+      <c r="G883" s="8">
+        <v>2020000</v>
+      </c>
+      <c r="H883" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="I883" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J883" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K883" s="6">
+        <v>0</v>
+      </c>
+      <c r="L883" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M883" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="884" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A884" s="6"/>
+      <c r="B884" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C884" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D884" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E884" s="6">
+        <v>124</v>
+      </c>
+      <c r="F884" s="8">
+        <v>5980000</v>
+      </c>
+      <c r="G884" s="8">
+        <v>5870000</v>
+      </c>
+      <c r="H884" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="I884" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J884" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K884" s="6">
+        <v>0</v>
+      </c>
+      <c r="L884" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M884" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="885" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A885" s="6"/>
+      <c r="B885" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C885" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D885" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E885" s="6">
+        <v>42</v>
+      </c>
+      <c r="F885" s="8">
+        <v>540000</v>
+      </c>
+      <c r="G885" s="8">
+        <v>540000</v>
+      </c>
+      <c r="H885" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="I885" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J885" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K885" s="6">
+        <v>0</v>
+      </c>
+      <c r="L885" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M885" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="886" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A886" s="6"/>
+      <c r="B886" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C886" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D886" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E886" s="6">
+        <v>128</v>
+      </c>
+      <c r="F886" s="8">
+        <v>4970000</v>
+      </c>
+      <c r="G886" s="8">
+        <v>5000000</v>
+      </c>
+      <c r="H886" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="I886" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J886" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K886" s="6">
+        <v>1</v>
+      </c>
+      <c r="L886" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M886" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="887" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A887" s="6"/>
+      <c r="B887" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C887" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D887" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E887" s="6">
+        <v>43</v>
+      </c>
+      <c r="F887" s="8">
+        <v>2720000</v>
+      </c>
+      <c r="G887" s="8">
+        <v>2700000</v>
+      </c>
+      <c r="H887" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I887" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J887" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K887" s="6">
+        <v>0</v>
+      </c>
+      <c r="L887" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M887" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="888" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A888" s="6"/>
+      <c r="B888" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C888" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D888" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E888" s="6">
+        <v>42</v>
+      </c>
+      <c r="F888" s="8">
+        <v>4880000</v>
+      </c>
+      <c r="G888" s="8">
+        <v>4900000</v>
+      </c>
+      <c r="H888" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="I888" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J888" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K888" s="6">
+        <v>0</v>
+      </c>
+      <c r="L888" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M888" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="889" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A889" s="6"/>
+      <c r="B889" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C889" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D889" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E889" s="6">
+        <v>43</v>
+      </c>
+      <c r="F889" s="8">
+        <v>4610000</v>
+      </c>
+      <c r="G889" s="8">
+        <v>4610000</v>
+      </c>
+      <c r="H889" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="I889" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J889" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K889" s="6">
+        <v>0</v>
+      </c>
+      <c r="L889" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M889" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="890" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A890" s="6"/>
+      <c r="B890" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C890" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D890" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E890" s="6">
+        <v>60</v>
+      </c>
+      <c r="F890" s="8">
+        <v>1460000</v>
+      </c>
+      <c r="G890" s="8">
+        <v>1490000</v>
+      </c>
+      <c r="H890" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="I890" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J890" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K890" s="6">
+        <v>0</v>
+      </c>
+      <c r="L890" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M890" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="891" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A891" s="6"/>
+      <c r="B891" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C891" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D891" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E891" s="6">
+        <v>124</v>
+      </c>
+      <c r="F891" s="8">
+        <v>3330000</v>
+      </c>
+      <c r="G891" s="8">
+        <v>3250000</v>
+      </c>
+      <c r="H891" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="I891" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J891" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K891" s="6">
+        <v>0</v>
+      </c>
+      <c r="L891" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M891" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="892" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A892" s="6"/>
+      <c r="B892" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="C892" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D892" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E892" s="6">
+        <v>178</v>
+      </c>
+      <c r="F892" s="8">
+        <v>12830000</v>
+      </c>
+      <c r="G892" s="8">
+        <v>12760000</v>
+      </c>
+      <c r="H892" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="I892" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J892" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K892" s="6">
+        <v>0</v>
+      </c>
+      <c r="L892" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M892" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="893" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A893" s="6"/>
+      <c r="B893" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C893" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D893" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E893" s="6">
+        <v>112</v>
+      </c>
+      <c r="F893" s="8">
+        <v>4550000</v>
+      </c>
+      <c r="G893" s="8">
+        <v>4510000</v>
+      </c>
+      <c r="H893" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="I893" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J893" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K893" s="6">
+        <v>0</v>
+      </c>
+      <c r="L893" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M893" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="894" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A894" s="6"/>
+      <c r="B894" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C894" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D894" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E894" s="6">
+        <v>95</v>
+      </c>
+      <c r="F894" s="8">
+        <v>2540000</v>
+      </c>
+      <c r="G894" s="8">
+        <v>2660000</v>
+      </c>
+      <c r="H894" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I894" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J894" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K894" s="6">
+        <v>0</v>
+      </c>
+      <c r="L894" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M894" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="895" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A895" s="6"/>
+      <c r="B895" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C895" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D895" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E895" s="6">
+        <v>183</v>
+      </c>
+      <c r="F895" s="8">
+        <v>9900000</v>
+      </c>
+      <c r="G895" s="8">
+        <v>9790000</v>
+      </c>
+      <c r="H895" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="I895" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J895" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K895" s="6">
+        <v>0</v>
+      </c>
+      <c r="L895" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M895" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="896" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A896" s="6"/>
+      <c r="B896" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C896" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D896" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E896" s="6">
+        <v>127</v>
+      </c>
+      <c r="F896" s="8">
+        <v>3250000</v>
+      </c>
+      <c r="G896" s="8">
+        <v>3270000</v>
+      </c>
+      <c r="H896" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I896" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J896" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K896" s="6">
+        <v>0</v>
+      </c>
+      <c r="L896" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M896" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="897" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A897" s="6"/>
+      <c r="B897" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C897" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D897" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E897" s="6">
+        <v>69</v>
+      </c>
+      <c r="F897" s="8">
+        <v>1470000</v>
+      </c>
+      <c r="G897" s="8">
+        <v>1470000</v>
+      </c>
+      <c r="H897" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="I897" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J897" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K897" s="6">
+        <v>0</v>
+      </c>
+      <c r="L897" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M897" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="898" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A898" s="6"/>
+      <c r="B898" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C898" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D898" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E898" s="6">
+        <v>72</v>
+      </c>
+      <c r="F898" s="8">
+        <v>1890000</v>
+      </c>
+      <c r="G898" s="8">
+        <v>1900000</v>
+      </c>
+      <c r="H898" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="I898" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J898" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K898" s="6">
+        <v>0</v>
+      </c>
+      <c r="L898" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M898" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="899" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A899" s="6"/>
+      <c r="B899" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C899" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D899" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E899" s="6">
+        <v>0</v>
+      </c>
+      <c r="F899" s="8">
+        <v>2270000</v>
+      </c>
+      <c r="G899" s="8">
+        <v>2310000</v>
+      </c>
+      <c r="H899" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="I899" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J899" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K899" s="6">
+        <v>0</v>
+      </c>
+      <c r="L899" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M899" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="900" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A900" s="6"/>
+      <c r="B900" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C900" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D900" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E900" s="6">
+        <v>0</v>
+      </c>
+      <c r="F900" s="8">
+        <v>2350000</v>
+      </c>
+      <c r="G900" s="8">
+        <v>2310000</v>
+      </c>
+      <c r="H900" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="I900" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J900" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K900" s="6">
+        <v>0</v>
+      </c>
+      <c r="L900" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M900" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="901" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A901" s="6"/>
+      <c r="B901" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C901" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D901" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E901" s="6">
+        <v>110</v>
+      </c>
+      <c r="F901" s="8">
+        <v>3500000</v>
+      </c>
+      <c r="G901" s="8">
+        <v>3450000</v>
+      </c>
+      <c r="H901" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="I901" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J901" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K901" s="6">
+        <v>0</v>
+      </c>
+      <c r="L901" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M901" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="902" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A902" s="6"/>
+      <c r="B902" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C902" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D902" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E902" s="6">
+        <v>117</v>
+      </c>
+      <c r="F902" s="8">
+        <v>3090000</v>
+      </c>
+      <c r="G902" s="8">
+        <v>3110000</v>
+      </c>
+      <c r="H902" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="I902" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J902" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K902" s="6">
+        <v>0</v>
+      </c>
+      <c r="L902" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M902" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="903" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A903" s="6"/>
+      <c r="B903" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C903" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D903" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E903" s="6">
+        <v>0</v>
+      </c>
+      <c r="F903" s="8">
+        <v>3140000</v>
+      </c>
+      <c r="G903" s="8">
+        <v>3090000</v>
+      </c>
+      <c r="H903" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="I903" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J903" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K903" s="6">
+        <v>0</v>
+      </c>
+      <c r="L903" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M903" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="904" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A904" s="6"/>
+      <c r="B904" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C904" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D904" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E904" s="6">
+        <v>71</v>
+      </c>
+      <c r="F904" s="8">
+        <v>1560000</v>
+      </c>
+      <c r="G904" s="8">
+        <v>1550000</v>
+      </c>
+      <c r="H904" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I904" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J904" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K904" s="6">
+        <v>0</v>
+      </c>
+      <c r="L904" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M904" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="905" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A905" s="6"/>
+      <c r="B905" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C905" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D905" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E905" s="6">
+        <v>127</v>
+      </c>
+      <c r="F905" s="8">
+        <v>5550000</v>
+      </c>
+      <c r="G905" s="8">
+        <v>5480000</v>
+      </c>
+      <c r="H905" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="I905" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J905" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K905" s="6">
+        <v>0</v>
+      </c>
+      <c r="L905" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M905" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="906" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A906" s="6"/>
+      <c r="B906" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C906" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D906" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E906" s="6">
+        <v>8</v>
+      </c>
+      <c r="F906" s="8">
+        <v>240000</v>
+      </c>
+      <c r="G906" s="8">
+        <v>240000</v>
+      </c>
+      <c r="H906" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="I906" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J906" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K906" s="6">
+        <v>0</v>
+      </c>
+      <c r="L906" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M906" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="907" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A907" s="6"/>
+      <c r="B907" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C907" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D907" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E907" s="6">
+        <v>72</v>
+      </c>
+      <c r="F907" s="8">
+        <v>3140000</v>
+      </c>
+      <c r="G907" s="8">
+        <v>2990000</v>
+      </c>
+      <c r="H907" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="I907" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J907" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K907" s="6">
+        <v>0</v>
+      </c>
+      <c r="L907" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M907" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="908" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A908" s="6"/>
+      <c r="B908" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C908" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D908" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E908" s="6">
+        <v>57</v>
+      </c>
+      <c r="F908" s="8">
+        <v>2180000</v>
+      </c>
+      <c r="G908" s="8">
+        <v>2220000</v>
+      </c>
+      <c r="H908" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="I908" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J908" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K908" s="6">
+        <v>0</v>
+      </c>
+      <c r="L908" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M908" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="909" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A909" s="6"/>
+      <c r="B909" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C909" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D909" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E909" s="6">
+        <v>22</v>
+      </c>
+      <c r="F909" s="8">
+        <v>3650000</v>
+      </c>
+      <c r="G909" s="8">
+        <v>3640000</v>
+      </c>
+      <c r="H909" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="I909" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J909" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K909" s="6">
+        <v>0</v>
+      </c>
+      <c r="L909" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M909" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="910" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A910" s="6"/>
+      <c r="B910" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C910" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D910" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E910" s="6">
+        <v>87</v>
+      </c>
+      <c r="F910" s="8">
+        <v>2560000</v>
+      </c>
+      <c r="G910" s="8">
+        <v>2570000</v>
+      </c>
+      <c r="H910" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I910" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J910" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K910" s="6">
+        <v>0</v>
+      </c>
+      <c r="L910" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M910" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="911" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A911" s="6"/>
+      <c r="B911" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C911" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D911" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E911" s="6">
+        <v>123</v>
+      </c>
+      <c r="F911" s="8">
+        <v>3880000</v>
+      </c>
+      <c r="G911" s="8">
+        <v>3890000</v>
+      </c>
+      <c r="H911" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="I911" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J911" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K911" s="6">
+        <v>0</v>
+      </c>
+      <c r="L911" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M911" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="912" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A912" s="6"/>
+      <c r="B912" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C912" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D912" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E912" s="6">
+        <v>0</v>
+      </c>
+      <c r="F912" s="8">
+        <v>320000</v>
+      </c>
+      <c r="G912" s="8">
+        <v>320000</v>
+      </c>
+      <c r="H912" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="I912" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J912" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K912" s="6">
+        <v>0</v>
+      </c>
+      <c r="L912" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M912" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="913" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A913" s="6"/>
+      <c r="B913" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C913" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D913" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E913" s="6">
+        <v>6</v>
+      </c>
+      <c r="F913" s="8">
+        <v>3610000</v>
+      </c>
+      <c r="G913" s="8">
+        <v>3700000</v>
+      </c>
+      <c r="H913" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="I913" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J913" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K913" s="6">
+        <v>0</v>
+      </c>
+      <c r="L913" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M913" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="914" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A914" s="6"/>
+      <c r="B914" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C914" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D914" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E914" s="6">
+        <v>77</v>
+      </c>
+      <c r="F914" s="8">
+        <v>2440000</v>
+      </c>
+      <c r="G914" s="8">
+        <v>2390000</v>
+      </c>
+      <c r="H914" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="I914" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J914" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K914" s="6">
+        <v>0</v>
+      </c>
+      <c r="L914" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M914" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="915" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A915" s="6"/>
+      <c r="B915" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C915" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D915" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E915" s="6">
+        <v>199</v>
+      </c>
+      <c r="F915" s="8">
+        <v>18400000</v>
+      </c>
+      <c r="G915" s="8">
+        <v>18570000</v>
+      </c>
+      <c r="H915" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="I915" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J915" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K915" s="6">
+        <v>0</v>
+      </c>
+      <c r="L915" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M915" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="916" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A916" s="6"/>
+      <c r="B916" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C916" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D916" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E916" s="6">
+        <v>179</v>
+      </c>
+      <c r="F916" s="8">
+        <v>11390000</v>
+      </c>
+      <c r="G916" s="8">
+        <v>11420000</v>
+      </c>
+      <c r="H916" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="I916" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J916" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K916" s="6">
+        <v>0</v>
+      </c>
+      <c r="L916" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M916" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="917" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A917" s="6"/>
+      <c r="B917" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C917" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D917" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E917" s="6">
+        <v>185</v>
+      </c>
+      <c r="F917" s="8">
+        <v>12150000</v>
+      </c>
+      <c r="G917" s="8">
+        <v>12270000</v>
+      </c>
+      <c r="H917" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="I917" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J917" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K917" s="6">
+        <v>0</v>
+      </c>
+      <c r="L917" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M917" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="918" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A918" s="6"/>
+      <c r="B918" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C918" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D918" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E918" s="6">
+        <v>0</v>
+      </c>
+      <c r="F918" s="8">
+        <v>4490000</v>
+      </c>
+      <c r="G918" s="8">
+        <v>4520000</v>
+      </c>
+      <c r="H918" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="I918" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J918" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K918" s="6">
+        <v>0</v>
+      </c>
+      <c r="L918" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M918" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="919" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A919" s="6"/>
+      <c r="B919" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C919" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D919" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E919" s="6">
+        <v>51</v>
+      </c>
+      <c r="F919" s="8">
+        <v>2370000</v>
+      </c>
+      <c r="G919" s="8">
+        <v>2510000</v>
+      </c>
+      <c r="H919" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="I919" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J919" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K919" s="6">
+        <v>0</v>
+      </c>
+      <c r="L919" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M919" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="920" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A920" s="6"/>
+      <c r="B920" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C920" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D920" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E920" s="6">
+        <v>119</v>
+      </c>
+      <c r="F920" s="8">
+        <v>6180000</v>
+      </c>
+      <c r="G920" s="8">
+        <v>6170000</v>
+      </c>
+      <c r="H920" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="I920" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J920" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K920" s="6">
+        <v>0</v>
+      </c>
+      <c r="L920" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M920" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="921" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A921" s="6"/>
+      <c r="B921" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C921" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D921" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E921" s="6">
+        <v>0</v>
+      </c>
+      <c r="F921" s="8">
+        <v>170000</v>
+      </c>
+      <c r="G921" s="8">
+        <v>170000</v>
+      </c>
+      <c r="H921" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I921" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J921" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K921" s="6">
+        <v>0</v>
+      </c>
+      <c r="L921" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M921" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="922" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A922" s="6"/>
+      <c r="B922" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C922" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D922" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E922" s="6">
+        <v>127</v>
+      </c>
+      <c r="F922" s="8">
+        <v>6100000</v>
+      </c>
+      <c r="G922" s="8">
+        <v>6030000</v>
+      </c>
+      <c r="H922" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I922" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J922" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K922" s="6">
+        <v>0</v>
+      </c>
+      <c r="L922" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M922" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="923" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A923" s="6"/>
+      <c r="B923" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C923" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D923" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E923" s="6">
+        <v>112</v>
+      </c>
+      <c r="F923" s="8">
+        <v>6600000</v>
+      </c>
+      <c r="G923" s="8">
+        <v>6500000</v>
+      </c>
+      <c r="H923" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="I923" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J923" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K923" s="6">
+        <v>1</v>
+      </c>
+      <c r="L923" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M923" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="924" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A924" s="6"/>
+      <c r="B924" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C924" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D924" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E924" s="6">
+        <v>69</v>
+      </c>
+      <c r="F924" s="8">
+        <v>4860000</v>
+      </c>
+      <c r="G924" s="8">
+        <v>4870000</v>
+      </c>
+      <c r="H924" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="I924" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J924" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K924" s="6">
+        <v>0</v>
+      </c>
+      <c r="L924" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M924" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="925" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A925" s="6"/>
+      <c r="B925" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C925" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D925" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E925" s="6">
+        <v>68</v>
+      </c>
+      <c r="F925" s="8">
+        <v>4250000</v>
+      </c>
+      <c r="G925" s="8">
+        <v>4270000</v>
+      </c>
+      <c r="H925" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I925" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J925" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K925" s="6">
+        <v>0</v>
+      </c>
+      <c r="L925" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M925" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="926" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A926" s="6"/>
+      <c r="B926" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="C926" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D926" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E926" s="6">
+        <v>81</v>
+      </c>
+      <c r="F926" s="8">
+        <v>1530000</v>
+      </c>
+      <c r="G926" s="8">
+        <v>1520000</v>
+      </c>
+      <c r="H926" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="I926" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J926" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K926" s="6">
+        <v>0</v>
+      </c>
+      <c r="L926" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M926" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="927" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A927" s="6"/>
+      <c r="B927" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C927" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D927" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E927" s="6">
+        <v>123</v>
+      </c>
+      <c r="F927" s="8">
+        <v>5600000</v>
+      </c>
+      <c r="G927" s="8">
+        <v>5560000</v>
+      </c>
+      <c r="H927" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="I927" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J927" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K927" s="6">
+        <v>0</v>
+      </c>
+      <c r="L927" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M927" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="928" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A928" s="6"/>
+      <c r="B928" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C928" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D928" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E928" s="6">
+        <v>109</v>
+      </c>
+      <c r="F928" s="8">
+        <v>3810000</v>
+      </c>
+      <c r="G928" s="8">
+        <v>3730000</v>
+      </c>
+      <c r="H928" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="I928" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J928" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K928" s="6">
+        <v>0</v>
+      </c>
+      <c r="L928" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M928" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="929" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A929" s="6"/>
+      <c r="B929" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C929" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D929" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E929" s="6">
+        <v>59</v>
+      </c>
+      <c r="F929" s="8">
+        <v>1300000</v>
+      </c>
+      <c r="G929" s="8">
+        <v>1310000</v>
+      </c>
+      <c r="H929" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="I929" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J929" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K929" s="6">
+        <v>0</v>
+      </c>
+      <c r="L929" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M929" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="930" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A930" s="6"/>
+      <c r="B930" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="C930" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D930" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E930" s="6">
+        <v>36</v>
+      </c>
+      <c r="F930" s="8">
+        <v>470000</v>
+      </c>
+      <c r="G930" s="8">
+        <v>470000</v>
+      </c>
+      <c r="H930" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="I930" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J930" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K930" s="6">
+        <v>0</v>
+      </c>
+      <c r="L930" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M930" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="931" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A931" s="6"/>
+      <c r="B931" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C931" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D931" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E931" s="6">
+        <v>16</v>
+      </c>
+      <c r="F931" s="8">
+        <v>510000</v>
+      </c>
+      <c r="G931" s="8">
+        <v>510000</v>
+      </c>
+      <c r="H931" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I931" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J931" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K931" s="6">
+        <v>0</v>
+      </c>
+      <c r="L931" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M931" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="932" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A932" s="6"/>
+      <c r="B932" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C932" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D932" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E932" s="6">
+        <v>0</v>
+      </c>
+      <c r="F932" s="8">
+        <v>2000000</v>
+      </c>
+      <c r="G932" s="8">
+        <v>2040000</v>
+      </c>
+      <c r="H932" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="I932" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J932" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K932" s="6">
+        <v>0</v>
+      </c>
+      <c r="L932" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M932" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="933" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A933" s="6"/>
+      <c r="B933" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C933" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D933" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E933" s="6">
+        <v>12</v>
+      </c>
+      <c r="F933" s="8">
+        <v>610000</v>
+      </c>
+      <c r="G933" s="8">
+        <v>610000</v>
+      </c>
+      <c r="H933" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="I933" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J933" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K933" s="6">
+        <v>0</v>
+      </c>
+      <c r="L933" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M933" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="934" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A934" s="6"/>
+      <c r="B934" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C934" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D934" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E934" s="6">
+        <v>0</v>
+      </c>
+      <c r="F934" s="8">
+        <v>10420000</v>
+      </c>
+      <c r="G934" s="8">
+        <v>10350000</v>
+      </c>
+      <c r="H934" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I934" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J934" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K934" s="6">
+        <v>0</v>
+      </c>
+      <c r="L934" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M934" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="935" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A935" s="6"/>
+      <c r="B935" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C935" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D935" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E935" s="6">
+        <v>66</v>
+      </c>
+      <c r="F935" s="8">
+        <v>1330000</v>
+      </c>
+      <c r="G935" s="8">
+        <v>1330000</v>
+      </c>
+      <c r="H935" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="I935" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J935" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K935" s="6">
+        <v>0</v>
+      </c>
+      <c r="L935" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M935" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="936" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A936" s="6"/>
+      <c r="B936" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="C936" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D936" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E936" s="6">
+        <v>0</v>
+      </c>
+      <c r="F936" s="8">
+        <v>300000</v>
+      </c>
+      <c r="G936" s="8">
+        <v>300000</v>
+      </c>
+      <c r="H936" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="I936" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J936" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K936" s="6">
+        <v>0</v>
+      </c>
+      <c r="L936" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M936" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="937" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A937" s="6"/>
+      <c r="B937" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C937" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D937" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E937" s="6">
+        <v>54</v>
+      </c>
+      <c r="F937" s="8">
+        <v>2260000</v>
+      </c>
+      <c r="G937" s="8">
+        <v>2300000</v>
+      </c>
+      <c r="H937" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I937" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J937" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K937" s="6">
+        <v>0</v>
+      </c>
+      <c r="L937" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M937" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="938" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A938" s="6"/>
+      <c r="B938" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C938" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D938" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E938" s="6">
+        <v>89</v>
+      </c>
+      <c r="F938" s="8">
+        <v>8310000</v>
+      </c>
+      <c r="G938" s="8">
+        <v>8250000</v>
+      </c>
+      <c r="H938" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I938" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J938" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K938" s="6">
+        <v>0</v>
+      </c>
+      <c r="L938" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M938" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="939" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A939" s="6"/>
+      <c r="B939" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C939" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D939" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E939" s="6">
+        <v>130</v>
+      </c>
+      <c r="F939" s="8">
+        <v>12260000</v>
+      </c>
+      <c r="G939" s="8">
+        <v>12300000</v>
+      </c>
+      <c r="H939" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="I939" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J939" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K939" s="6">
+        <v>0</v>
+      </c>
+      <c r="L939" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M939" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="940" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A940" s="6"/>
+      <c r="B940" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C940" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D940" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E940" s="6">
+        <v>0</v>
+      </c>
+      <c r="F940" s="8">
+        <v>1940000</v>
+      </c>
+      <c r="G940" s="8">
+        <v>1930000</v>
+      </c>
+      <c r="H940" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="I940" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J940" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K940" s="6">
+        <v>0</v>
+      </c>
+      <c r="L940" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M940" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="941" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A941" s="6"/>
+      <c r="B941" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C941" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D941" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E941" s="6">
+        <v>91</v>
+      </c>
+      <c r="F941" s="8">
+        <v>9290000</v>
+      </c>
+      <c r="G941" s="8">
+        <v>9230000</v>
+      </c>
+      <c r="H941" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="I941" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J941" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K941" s="6">
+        <v>0</v>
+      </c>
+      <c r="L941" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M941" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="942" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A942" s="6"/>
+      <c r="B942" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C942" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D942" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E942" s="6">
+        <v>9</v>
+      </c>
+      <c r="F942" s="8">
+        <v>400000</v>
+      </c>
+      <c r="G942" s="8">
+        <v>400000</v>
+      </c>
+      <c r="H942" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="I942" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J942" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K942" s="6">
+        <v>0</v>
+      </c>
+      <c r="L942" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M942" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="943" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A943" s="6"/>
+      <c r="B943" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C943" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D943" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E943" s="6">
+        <v>0</v>
+      </c>
+      <c r="F943" s="8">
+        <v>160000</v>
+      </c>
+      <c r="G943" s="8">
+        <v>160000</v>
+      </c>
+      <c r="H943" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I943" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J943" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K943" s="6">
+        <v>0</v>
+      </c>
+      <c r="L943" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M943" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="944" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A944" s="6"/>
+      <c r="B944" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C944" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D944" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E944" s="6">
+        <v>1</v>
+      </c>
+      <c r="F944" s="8">
+        <v>290000</v>
+      </c>
+      <c r="G944" s="8">
+        <v>290000</v>
+      </c>
+      <c r="H944" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="I944" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J944" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K944" s="6">
+        <v>0</v>
+      </c>
+      <c r="L944" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M944" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="945" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A945" s="6"/>
+      <c r="B945" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C945" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D945" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E945" s="6">
+        <v>108</v>
+      </c>
+      <c r="F945" s="8">
+        <v>3100000</v>
+      </c>
+      <c r="G945" s="8">
+        <v>3080000</v>
+      </c>
+      <c r="H945" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="I945" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J945" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K945" s="6">
+        <v>0</v>
+      </c>
+      <c r="L945" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M945" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="946" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A946" s="6"/>
+      <c r="B946" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C946" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D946" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E946" s="6">
+        <v>71</v>
+      </c>
+      <c r="F946" s="8">
+        <v>2270000</v>
+      </c>
+      <c r="G946" s="8">
+        <v>2290000</v>
+      </c>
+      <c r="H946" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="I946" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J946" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K946" s="6">
+        <v>0</v>
+      </c>
+      <c r="L946" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M946" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="947" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A947" s="6"/>
+      <c r="B947" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C947" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D947" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E947" s="6">
+        <v>0</v>
+      </c>
+      <c r="F947" s="8">
+        <v>2180000</v>
+      </c>
+      <c r="G947" s="8">
+        <v>2230000</v>
+      </c>
+      <c r="H947" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I947" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J947" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K947" s="6">
+        <v>0</v>
+      </c>
+      <c r="L947" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M947" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="948" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A948" s="6"/>
+      <c r="B948" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C948" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D948" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E948" s="6">
+        <v>8</v>
+      </c>
+      <c r="F948" s="8">
+        <v>280000</v>
+      </c>
+      <c r="G948" s="8">
+        <v>280000</v>
+      </c>
+      <c r="H948" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="I948" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J948" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K948" s="6">
+        <v>0</v>
+      </c>
+      <c r="L948" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M948" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="949" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A949" s="6"/>
+      <c r="B949" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C949" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D949" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E949" s="6">
+        <v>90</v>
+      </c>
+      <c r="F949" s="8">
+        <v>3990000</v>
+      </c>
+      <c r="G949" s="8">
+        <v>3910000</v>
+      </c>
+      <c r="H949" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="I949" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J949" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K949" s="6">
+        <v>0</v>
+      </c>
+      <c r="L949" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M949" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="950" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A950" s="6"/>
+      <c r="B950" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C950" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D950" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E950" s="6">
+        <v>15</v>
+      </c>
+      <c r="F950" s="8">
+        <v>410000</v>
+      </c>
+      <c r="G950" s="8">
+        <v>410000</v>
+      </c>
+      <c r="H950" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="I950" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J950" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K950" s="6">
+        <v>0</v>
+      </c>
+      <c r="L950" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M950" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="951" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A951" s="6"/>
+      <c r="B951" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C951" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D951" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E951" s="6">
+        <v>58</v>
+      </c>
+      <c r="F951" s="8">
+        <v>1390000</v>
+      </c>
+      <c r="G951" s="8">
+        <v>1380000</v>
+      </c>
+      <c r="H951" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I951" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J951" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K951" s="6">
+        <v>0</v>
+      </c>
+      <c r="L951" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M951" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="952" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A952" s="6"/>
+      <c r="B952" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C952" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D952" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E952" s="6">
+        <v>4</v>
+      </c>
+      <c r="F952" s="8">
+        <v>460000</v>
+      </c>
+      <c r="G952" s="8">
+        <v>460000</v>
+      </c>
+      <c r="H952" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="I952" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J952" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K952" s="6">
+        <v>0</v>
+      </c>
+      <c r="L952" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M952" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="953" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A953" s="6"/>
+      <c r="B953" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C953" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D953" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E953" s="6">
+        <v>47</v>
+      </c>
+      <c r="F953" s="8">
+        <v>1580000</v>
+      </c>
+      <c r="G953" s="8">
+        <v>1590000</v>
+      </c>
+      <c r="H953" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="I953" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J953" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K953" s="6">
+        <v>0</v>
+      </c>
+      <c r="L953" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M953" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="954" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A954" s="6"/>
+      <c r="B954" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C954" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D954" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E954" s="6">
+        <v>4</v>
+      </c>
+      <c r="F954" s="8">
+        <v>450000</v>
+      </c>
+      <c r="G954" s="8">
+        <v>450000</v>
+      </c>
+      <c r="H954" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="I954" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J954" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K954" s="6">
+        <v>0</v>
+      </c>
+      <c r="L954" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M954" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="955" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A955" s="6"/>
+      <c r="B955" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C955" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D955" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E955" s="6">
+        <v>156</v>
+      </c>
+      <c r="F955" s="8">
+        <v>7130000</v>
+      </c>
+      <c r="G955" s="8">
+        <v>7050000</v>
+      </c>
+      <c r="H955" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="I955" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J955" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K955" s="6">
+        <v>0</v>
+      </c>
+      <c r="L955" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M955" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="956" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A956" s="6"/>
+      <c r="B956" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C956" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D956" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E956" s="6">
+        <v>0</v>
+      </c>
+      <c r="F956" s="8">
+        <v>170000</v>
+      </c>
+      <c r="G956" s="8">
+        <v>170000</v>
+      </c>
+      <c r="H956" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I956" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J956" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K956" s="6">
+        <v>0</v>
+      </c>
+      <c r="L956" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M956" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="957" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A957" s="6"/>
+      <c r="B957" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C957" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D957" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E957" s="6">
+        <v>29</v>
+      </c>
+      <c r="F957" s="8">
+        <v>890000</v>
+      </c>
+      <c r="G957" s="8">
+        <v>880000</v>
+      </c>
+      <c r="H957" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="I957" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J957" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K957" s="6">
+        <v>0</v>
+      </c>
+      <c r="L957" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M957" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="958" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A958" s="6"/>
+      <c r="B958" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C958" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D958" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E958" s="6">
+        <v>19</v>
+      </c>
+      <c r="F958" s="8">
+        <v>960000</v>
+      </c>
+      <c r="G958" s="8">
+        <v>960000</v>
+      </c>
+      <c r="H958" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="I958" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J958" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K958" s="6">
+        <v>0</v>
+      </c>
+      <c r="L958" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M958" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="959" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A959" s="6"/>
+      <c r="B959" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C959" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D959" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E959" s="6">
+        <v>0</v>
+      </c>
+      <c r="F959" s="8">
+        <v>170000</v>
+      </c>
+      <c r="G959" s="8">
+        <v>170000</v>
+      </c>
+      <c r="H959" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I959" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J959" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K959" s="6">
+        <v>0</v>
+      </c>
+      <c r="L959" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M959" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="960" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A960" s="6"/>
+      <c r="B960" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C960" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D960" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E960" s="6">
+        <v>11</v>
+      </c>
+      <c r="F960" s="8">
+        <v>3210000</v>
+      </c>
+      <c r="G960" s="8">
+        <v>3170000</v>
+      </c>
+      <c r="H960" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="I960" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J960" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K960" s="6">
+        <v>0</v>
+      </c>
+      <c r="L960" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M960" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="961" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A961" s="6"/>
+      <c r="B961" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C961" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D961" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E961" s="6">
+        <v>40</v>
+      </c>
+      <c r="F961" s="8">
+        <v>2510000</v>
+      </c>
+      <c r="G961" s="8">
+        <v>2530000</v>
+      </c>
+      <c r="H961" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="I961" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J961" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K961" s="6">
+        <v>0</v>
+      </c>
+      <c r="L961" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M961" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="962" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A962" s="6"/>
+      <c r="B962" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C962" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D962" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E962" s="6">
+        <v>23</v>
+      </c>
+      <c r="F962" s="8">
+        <v>770000</v>
+      </c>
+      <c r="G962" s="8">
+        <v>780000</v>
+      </c>
+      <c r="H962" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="I962" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J962" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K962" s="6">
+        <v>0</v>
+      </c>
+      <c r="L962" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M962" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="963" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A963" s="6"/>
+      <c r="B963" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C963" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D963" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E963" s="6">
+        <v>0</v>
+      </c>
+      <c r="F963" s="8">
+        <v>160000</v>
+      </c>
+      <c r="G963" s="8">
+        <v>160000</v>
+      </c>
+      <c r="H963" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I963" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J963" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K963" s="6">
+        <v>0</v>
+      </c>
+      <c r="L963" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M963" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="964" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A964" s="6"/>
+      <c r="B964" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C964" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D964" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E964" s="6">
+        <v>0</v>
+      </c>
+      <c r="F964" s="8">
+        <v>3480000</v>
+      </c>
+      <c r="G964" s="8">
+        <v>3500000</v>
+      </c>
+      <c r="H964" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I964" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J964" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K964" s="6">
+        <v>0</v>
+      </c>
+      <c r="L964" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M964" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="965" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A965" s="6"/>
+      <c r="B965" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C965" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D965" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E965" s="6">
+        <v>0</v>
+      </c>
+      <c r="F965" s="8">
+        <v>3540000</v>
+      </c>
+      <c r="G965" s="8">
+        <v>3510000</v>
+      </c>
+      <c r="H965" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I965" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J965" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K965" s="6">
+        <v>0</v>
+      </c>
+      <c r="L965" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M965" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="966" spans="1:13" ht="21" x14ac:dyDescent="0.25">
+      <c r="A966" s="6"/>
+      <c r="B966" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C966" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D966" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E966" s="6">
+        <v>0</v>
+      </c>
+      <c r="F966" s="8">
+        <v>3880000</v>
+      </c>
+      <c r="G966" s="8">
+        <v>3830000</v>
+      </c>
+      <c r="H966" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I966" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J966" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K966" s="6">
+        <v>0</v>
+      </c>
+      <c r="L966" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M966" s="9" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -34461,8 +37881,92 @@
     <hyperlink ref="B880" r:id="rId343" display="https://www.com-analytics.de/player/34129" xr:uid="{8584134F-E06C-4BA0-B916-C8BBD455C2EA}"/>
     <hyperlink ref="B881" r:id="rId344" display="https://www.com-analytics.de/player/34146" xr:uid="{502811BF-0F96-4DAD-85AC-403867CC506C}"/>
     <hyperlink ref="B882" r:id="rId345" display="https://www.com-analytics.de/player/34148" xr:uid="{2072C76C-DDFF-491D-AEAC-54DC9D3A0DC8}"/>
+    <hyperlink ref="B883" r:id="rId346" display="https://www.com-analytics.de/player/30755" xr:uid="{ADDA4528-6E12-4D66-8CDC-35F6AE248EB5}"/>
+    <hyperlink ref="B884" r:id="rId347" display="https://www.com-analytics.de/player/31419" xr:uid="{2A581C5B-FC7F-444D-B54B-E293855DE735}"/>
+    <hyperlink ref="B885" r:id="rId348" display="https://www.com-analytics.de/player/31710" xr:uid="{429DC880-5540-4D5C-A43E-94281285E873}"/>
+    <hyperlink ref="B886" r:id="rId349" display="https://www.com-analytics.de/player/31910" xr:uid="{1A959FFA-61F7-473B-8E43-FD64FED434CC}"/>
+    <hyperlink ref="B887" r:id="rId350" display="https://www.com-analytics.de/player/31958" xr:uid="{E108A13D-0F2D-41F9-8EC4-A2AD05D15EF2}"/>
+    <hyperlink ref="B888" r:id="rId351" display="https://www.com-analytics.de/player/32080" xr:uid="{C66F57AB-0785-4EE2-B308-15743A3C2AB9}"/>
+    <hyperlink ref="B889" r:id="rId352" display="https://www.com-analytics.de/player/32122" xr:uid="{BDB1CB88-E8A1-4903-922A-2375D69DDC45}"/>
+    <hyperlink ref="B890" r:id="rId353" display="https://www.com-analytics.de/player/32310" xr:uid="{D1CDE69A-6873-4634-B3C9-42B7D2E0E704}"/>
+    <hyperlink ref="B891" r:id="rId354" display="https://www.com-analytics.de/player/32364" xr:uid="{A69D1F50-3FA2-45B0-8B3E-7888C27EA3ED}"/>
+    <hyperlink ref="B892" r:id="rId355" display="https://www.com-analytics.de/player/32395" xr:uid="{0DA37B1E-A927-48B8-90FB-9A2F8ECD0F3B}"/>
+    <hyperlink ref="B893" r:id="rId356" display="https://www.com-analytics.de/player/32398" xr:uid="{57BCBA87-A90A-43C5-8FB5-466BB7552184}"/>
+    <hyperlink ref="B894" r:id="rId357" display="https://www.com-analytics.de/player/32408" xr:uid="{00CD55C2-D178-43A6-A666-052F0E75BB9A}"/>
+    <hyperlink ref="B895" r:id="rId358" display="https://www.com-analytics.de/player/32509" xr:uid="{A5BAD9A2-4A4F-4F38-A628-697B45480369}"/>
+    <hyperlink ref="B896" r:id="rId359" display="https://www.com-analytics.de/player/32575" xr:uid="{68268168-DA1F-4756-8BBC-2726D4A5F99A}"/>
+    <hyperlink ref="B897" r:id="rId360" display="https://www.com-analytics.de/player/32579" xr:uid="{436A0DC5-EE75-4CBD-AFAA-2DA553693F4E}"/>
+    <hyperlink ref="B898" r:id="rId361" display="https://www.com-analytics.de/player/32603" xr:uid="{7A9E26A4-1E99-401F-AEC2-26DE8F525CB2}"/>
+    <hyperlink ref="B899" r:id="rId362" display="https://www.com-analytics.de/player/32629" xr:uid="{79EDFEC6-D679-4637-9D0A-2E1AE4610A5C}"/>
+    <hyperlink ref="B900" r:id="rId363" display="https://www.com-analytics.de/player/32630" xr:uid="{9F7B5D8A-61F9-4DFD-A4FF-9CFF3832D1BE}"/>
+    <hyperlink ref="B901" r:id="rId364" display="https://www.com-analytics.de/player/32633" xr:uid="{A50FEFD1-A85B-482D-8CF8-277AA097E318}"/>
+    <hyperlink ref="B902" r:id="rId365" display="https://www.com-analytics.de/player/32731" xr:uid="{15E70C3B-4A94-41D9-A5DF-22F80F60BEBF}"/>
+    <hyperlink ref="B903" r:id="rId366" display="https://www.com-analytics.de/player/32744" xr:uid="{EC94C8A2-B355-4BE9-8C5D-0ECC4301C604}"/>
+    <hyperlink ref="B904" r:id="rId367" display="https://www.com-analytics.de/player/32756" xr:uid="{6A66C316-C6AC-4B8B-8531-4426D4D428BF}"/>
+    <hyperlink ref="B905" r:id="rId368" display="https://www.com-analytics.de/player/32787" xr:uid="{1E278CE8-4143-473A-8054-797FCA2EE351}"/>
+    <hyperlink ref="B906" r:id="rId369" display="https://www.com-analytics.de/player/32841" xr:uid="{AC0584BD-016E-48C8-BBCD-B9EC86D8CE2E}"/>
+    <hyperlink ref="B907" r:id="rId370" display="https://www.com-analytics.de/player/32877" xr:uid="{2CC95699-46B6-415A-B95D-AF431C5AD040}"/>
+    <hyperlink ref="B908" r:id="rId371" display="https://www.com-analytics.de/player/32880" xr:uid="{1187830F-EF3E-49C7-AAFF-240EE4359355}"/>
+    <hyperlink ref="B909" r:id="rId372" display="https://www.com-analytics.de/player/32961" xr:uid="{C4BD534D-303E-48AA-B7DD-EDE3E9243EC0}"/>
+    <hyperlink ref="B910" r:id="rId373" display="https://www.com-analytics.de/player/32977" xr:uid="{C06EB21A-54A7-4ED2-8AA2-580C4FE8BF30}"/>
+    <hyperlink ref="B911" r:id="rId374" display="https://www.com-analytics.de/player/33070" xr:uid="{5EDB3B41-B36C-4D42-8433-F0AC8EA1BA64}"/>
+    <hyperlink ref="B912" r:id="rId375" display="https://www.com-analytics.de/player/33105" xr:uid="{EEC82119-A336-4AC6-8246-65A8B8E3947C}"/>
+    <hyperlink ref="B913" r:id="rId376" display="https://www.com-analytics.de/player/33133" xr:uid="{B91FD19B-77EB-4A89-927B-9F041A0C729D}"/>
+    <hyperlink ref="B914" r:id="rId377" display="https://www.com-analytics.de/player/33156" xr:uid="{6C6533A8-A5C2-4389-8307-C77F4E0205B2}"/>
+    <hyperlink ref="B915" r:id="rId378" display="https://www.com-analytics.de/player/33236" xr:uid="{D652FA49-AA62-4734-B92F-BB106BAA818E}"/>
+    <hyperlink ref="B916" r:id="rId379" display="https://www.com-analytics.de/player/33296" xr:uid="{AAA8ECE2-6861-4ED0-BDDC-5CF40A79C27C}"/>
+    <hyperlink ref="B917" r:id="rId380" display="https://www.com-analytics.de/player/33335" xr:uid="{D129E6D4-3C83-44C5-ACA4-37A9FEB3D19A}"/>
+    <hyperlink ref="B918" r:id="rId381" display="https://www.com-analytics.de/player/33356" xr:uid="{D19328E9-08C6-411F-8397-38FC28528D1B}"/>
+    <hyperlink ref="B919" r:id="rId382" display="https://www.com-analytics.de/player/33364" xr:uid="{EB5043AE-0B43-401B-B0EF-D787B229C08A}"/>
+    <hyperlink ref="B920" r:id="rId383" display="https://www.com-analytics.de/player/33383" xr:uid="{1006350F-A126-47E4-A906-C9CE92507EEE}"/>
+    <hyperlink ref="B921" r:id="rId384" display="https://www.com-analytics.de/player/33397" xr:uid="{9C0CF659-AD63-420F-8092-B7EC1DCF83C8}"/>
+    <hyperlink ref="B922" r:id="rId385" display="https://www.com-analytics.de/player/33409" xr:uid="{80BDBDE3-9997-4F2B-A3BC-0829534FD396}"/>
+    <hyperlink ref="B923" r:id="rId386" display="https://www.com-analytics.de/player/33510" xr:uid="{2B1C9044-32B3-4766-96A3-5BDA6C544FFC}"/>
+    <hyperlink ref="B924" r:id="rId387" display="https://www.com-analytics.de/player/33514" xr:uid="{F948F9A9-488D-46E3-B24B-408CD31EE6B2}"/>
+    <hyperlink ref="B925" r:id="rId388" display="https://www.com-analytics.de/player/33547" xr:uid="{199D8306-7AB6-4845-8F9B-F9CC72AB74C2}"/>
+    <hyperlink ref="B926" r:id="rId389" display="https://www.com-analytics.de/player/33550" xr:uid="{E44DC184-93D6-45CB-A435-DE1FAD52866A}"/>
+    <hyperlink ref="B927" r:id="rId390" display="https://www.com-analytics.de/player/33552" xr:uid="{D39567BF-1ECF-4099-9750-6722711E05F1}"/>
+    <hyperlink ref="B928" r:id="rId391" display="https://www.com-analytics.de/player/33609" xr:uid="{90D22884-5900-4B4E-BEA5-717100090F84}"/>
+    <hyperlink ref="B929" r:id="rId392" display="https://www.com-analytics.de/player/33616" xr:uid="{6FE628C3-6E28-438B-87BC-286E506F907A}"/>
+    <hyperlink ref="B930" r:id="rId393" display="https://www.com-analytics.de/player/33669" xr:uid="{CA4160AD-42CE-4824-9586-EAC75E65DE1A}"/>
+    <hyperlink ref="B931" r:id="rId394" display="https://www.com-analytics.de/player/33678" xr:uid="{365F19F9-2F2C-4F0E-87EC-5A82FE835957}"/>
+    <hyperlink ref="B932" r:id="rId395" display="https://www.com-analytics.de/player/33696" xr:uid="{10450FDF-BABF-4EF2-8D70-BD6DCA426F10}"/>
+    <hyperlink ref="B933" r:id="rId396" display="https://www.com-analytics.de/player/33718" xr:uid="{816947F2-92CA-48A5-8CE8-E1D019603516}"/>
+    <hyperlink ref="B934" r:id="rId397" display="https://www.com-analytics.de/player/33744" xr:uid="{E0ADA115-2ED5-407F-B221-893B3F6BDB2B}"/>
+    <hyperlink ref="B935" r:id="rId398" display="https://www.com-analytics.de/player/33807" xr:uid="{3D00E0E9-0103-4E72-8259-C48605D669B6}"/>
+    <hyperlink ref="B936" r:id="rId399" display="https://www.com-analytics.de/player/33812" xr:uid="{81FCF58D-9860-4D63-8C65-1B4FFEE06555}"/>
+    <hyperlink ref="B937" r:id="rId400" display="https://www.com-analytics.de/player/33815" xr:uid="{0685735A-0F14-41C0-B748-E37A34E821ED}"/>
+    <hyperlink ref="B938" r:id="rId401" display="https://www.com-analytics.de/player/33827" xr:uid="{8ABD7C6D-618C-4A0C-B6DE-019C04BC8269}"/>
+    <hyperlink ref="B939" r:id="rId402" display="https://www.com-analytics.de/player/33832" xr:uid="{C516FDA7-CAC4-43AD-B523-F9855E240110}"/>
+    <hyperlink ref="B940" r:id="rId403" display="https://www.com-analytics.de/player/33848" xr:uid="{B8825473-D6A8-4421-AE8E-C0E650427764}"/>
+    <hyperlink ref="B941" r:id="rId404" display="https://www.com-analytics.de/player/33854" xr:uid="{5D6C4DD4-61CF-462F-96FE-5520A9541070}"/>
+    <hyperlink ref="B942" r:id="rId405" display="https://www.com-analytics.de/player/33883" xr:uid="{FBF795B4-055C-4F91-BDEC-188F8AA271A8}"/>
+    <hyperlink ref="B943" r:id="rId406" display="https://www.com-analytics.de/player/33889" xr:uid="{A6B57E56-7FD7-4FF0-B992-9D34FC835176}"/>
+    <hyperlink ref="B944" r:id="rId407" display="https://www.com-analytics.de/player/33905" xr:uid="{8CF5FBDD-8EDB-48C8-B9F2-D572D3F47C91}"/>
+    <hyperlink ref="B945" r:id="rId408" display="https://www.com-analytics.de/player/33948" xr:uid="{6C67ED74-4858-46B2-94F4-02EF8ED36B74}"/>
+    <hyperlink ref="B946" r:id="rId409" display="https://www.com-analytics.de/player/33978" xr:uid="{D8F88D84-0F05-41B0-ACCC-5B109BABB0E7}"/>
+    <hyperlink ref="B947" r:id="rId410" display="https://www.com-analytics.de/player/33991" xr:uid="{5D30C96D-69D4-42BF-910E-1CA8517364AE}"/>
+    <hyperlink ref="B948" r:id="rId411" display="https://www.com-analytics.de/player/33993" xr:uid="{7920D25F-62CA-435F-A0CF-0BADD3AF3DB4}"/>
+    <hyperlink ref="B949" r:id="rId412" display="https://www.com-analytics.de/player/33995" xr:uid="{3664309B-DBA6-4BCB-BBB0-AE62D786F0AC}"/>
+    <hyperlink ref="B950" r:id="rId413" display="https://www.com-analytics.de/player/33999" xr:uid="{B91D3531-2580-4551-9A53-F208822BA3BC}"/>
+    <hyperlink ref="B951" r:id="rId414" display="https://www.com-analytics.de/player/34001" xr:uid="{7AEF6AF1-B581-48AE-9380-DBC8E69C77EB}"/>
+    <hyperlink ref="B952" r:id="rId415" display="https://www.com-analytics.de/player/34011" xr:uid="{64036D8B-8E9A-42BD-9535-8FF19DC95768}"/>
+    <hyperlink ref="B953" r:id="rId416" display="https://www.com-analytics.de/player/34019" xr:uid="{8C15E7EC-E299-41F7-854A-D3753DDCFB67}"/>
+    <hyperlink ref="B954" r:id="rId417" display="https://www.com-analytics.de/player/34021" xr:uid="{46DF6871-BE63-4EA2-8F6E-12BDB112CEB1}"/>
+    <hyperlink ref="B955" r:id="rId418" display="https://www.com-analytics.de/player/34025" xr:uid="{48AF0257-65CB-493B-90B9-F4328B470845}"/>
+    <hyperlink ref="B956" r:id="rId419" display="https://www.com-analytics.de/player/34032" xr:uid="{12B41AA1-A5D3-4CC9-823E-A7991F4030E0}"/>
+    <hyperlink ref="B957" r:id="rId420" display="https://www.com-analytics.de/player/34035" xr:uid="{0D4C9D7A-F964-414F-AB09-1D5124659A01}"/>
+    <hyperlink ref="B958" r:id="rId421" display="https://www.com-analytics.de/player/34050" xr:uid="{4B1F2269-8A0B-4ABB-AD9F-26BEA8F57CAB}"/>
+    <hyperlink ref="B959" r:id="rId422" display="https://www.com-analytics.de/player/34088" xr:uid="{6CBAA109-B480-443A-ACB1-758E8EA9BD99}"/>
+    <hyperlink ref="B960" r:id="rId423" display="https://www.com-analytics.de/player/34096" xr:uid="{BC62CADE-39BE-40F1-A28A-14EF69977A2E}"/>
+    <hyperlink ref="B961" r:id="rId424" display="https://www.com-analytics.de/player/34109" xr:uid="{DC81D97C-A165-4478-BA12-F4CCDB38603E}"/>
+    <hyperlink ref="B962" r:id="rId425" display="https://www.com-analytics.de/player/34111" xr:uid="{9CF60884-1847-4604-B254-96BB68BC68EC}"/>
+    <hyperlink ref="B963" r:id="rId426" display="https://www.com-analytics.de/player/34120" xr:uid="{48C9BEC3-0441-4B20-B69B-383FAFDD427B}"/>
+    <hyperlink ref="B964" r:id="rId427" display="https://www.com-analytics.de/player/34146" xr:uid="{6D366095-4485-4799-820E-0163C666B073}"/>
+    <hyperlink ref="B965" r:id="rId428" display="https://www.com-analytics.de/player/34148" xr:uid="{41264995-04B2-4496-A841-8876A9A7B88E}"/>
+    <hyperlink ref="B966" r:id="rId429" display="https://www.com-analytics.de/player/34187" xr:uid="{6B55E76B-D339-42F6-AC79-CB79A92F7E6E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId346"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId430"/>
 </worksheet>
 </file>
--- a/TM_all.xlsx
+++ b/TM_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aecf56309e6168f4/Documents/comunio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="214" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45D9059B-905C-4C1F-88CF-0CDFBF289F64}"/>
+  <xr:revisionPtr revIDLastSave="218" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87486627-A459-446D-A33B-5F6E3A2DD1D1}"/>
   <bookViews>
     <workbookView xWindow="2110" yWindow="2130" windowWidth="28800" windowHeight="15370" xr2:uid="{607DE709-F91E-4262-9941-1066BBEC319E}"/>
   </bookViews>
@@ -860,7 +860,7 @@
     <t>Diks</t>
   </si>
   <si>
-    <t>11.06.2026</t>
+    <t>11.06.2025</t>
   </si>
 </sst>
 </file>

--- a/TM_all.xlsx
+++ b/TM_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aecf56309e6168f4/Documents/comunio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="225" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B04FA23-EC55-4F77-88BC-456F87E4EAD1}"/>
+  <xr:revisionPtr revIDLastSave="234" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51C20D1E-0DF0-489C-83F1-A6D45CB1609D}"/>
   <bookViews>
-    <workbookView xWindow="2110" yWindow="2130" windowWidth="28800" windowHeight="15370" xr2:uid="{607DE709-F91E-4262-9941-1066BBEC319E}"/>
+    <workbookView xWindow="6660" yWindow="2700" windowWidth="28800" windowHeight="15370" xr2:uid="{607DE709-F91E-4262-9941-1066BBEC319E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7275" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7987" uniqueCount="295">
   <si>
     <t>Spieler</t>
   </si>
@@ -883,6 +883,48 @@
   <si>
     <t>12.06.2025</t>
   </si>
+  <si>
+    <t>W. Orbán</t>
+  </si>
+  <si>
+    <t>5,7</t>
+  </si>
+  <si>
+    <t>Kramarić</t>
+  </si>
+  <si>
+    <t>Kainz</t>
+  </si>
+  <si>
+    <t>3,7</t>
+  </si>
+  <si>
+    <t>Burkardt</t>
+  </si>
+  <si>
+    <t>6,6</t>
+  </si>
+  <si>
+    <t>Jäkel</t>
+  </si>
+  <si>
+    <t>Caci</t>
+  </si>
+  <si>
+    <t>Dietz</t>
+  </si>
+  <si>
+    <t>0,7</t>
+  </si>
+  <si>
+    <t>Malatini</t>
+  </si>
+  <si>
+    <t>Sieb</t>
+  </si>
+  <si>
+    <t>13.06.2025</t>
+  </si>
 </sst>
 </file>
 
@@ -1306,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93EB6F54-7766-4759-97DF-03549A275A7C}">
-  <dimension ref="A1:M1045"/>
+  <dimension ref="A1:M1135"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="2"/>
@@ -40345,7 +40387,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="1041" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1041" s="2" t="s">
         <v>206</v>
       </c>
@@ -40383,7 +40425,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="1042" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1042" s="2" t="s">
         <v>118</v>
       </c>
@@ -40421,7 +40463,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="1043" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1043" s="2" t="s">
         <v>121</v>
       </c>
@@ -40459,7 +40501,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="1044" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1044" s="2" t="s">
         <v>200</v>
       </c>
@@ -40497,7 +40539,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="1045" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1045" s="2" t="s">
         <v>272</v>
       </c>
@@ -40534,6 +40576,3480 @@
       <c r="M1045" s="7" t="s">
         <v>280</v>
       </c>
+    </row>
+    <row r="1046" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1046" s="6"/>
+      <c r="B1046" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1046" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1046" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1046" s="2">
+        <v>70</v>
+      </c>
+      <c r="F1046" s="2">
+        <v>1890000</v>
+      </c>
+      <c r="G1046" s="2">
+        <v>1890000</v>
+      </c>
+      <c r="H1046" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I1046" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1046" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1046" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1046" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1046" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1047" s="6"/>
+      <c r="B1047" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1047" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1047" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1047" s="2">
+        <v>124</v>
+      </c>
+      <c r="F1047" s="2">
+        <v>5870000</v>
+      </c>
+      <c r="G1047" s="2">
+        <v>5640000</v>
+      </c>
+      <c r="H1047" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I1047" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="J1047" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1047" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1047" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1047" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1048" s="6"/>
+      <c r="B1048" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1048" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1048" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1048" s="2">
+        <v>143</v>
+      </c>
+      <c r="F1048" s="2">
+        <v>6270000</v>
+      </c>
+      <c r="G1048" s="2">
+        <v>6170000</v>
+      </c>
+      <c r="H1048" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I1048" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1048" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1048" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1048" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1048" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1049" s="6"/>
+      <c r="B1049" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1049" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1049" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1049" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1049" s="2">
+        <v>4790000</v>
+      </c>
+      <c r="G1049" s="2">
+        <v>4680000</v>
+      </c>
+      <c r="H1049" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1049" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1049" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1049" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1049" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1049" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1050" s="6"/>
+      <c r="B1050" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1050" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1050" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1050" s="2">
+        <v>83</v>
+      </c>
+      <c r="F1050" s="2">
+        <v>1040000</v>
+      </c>
+      <c r="G1050" s="2">
+        <v>1050000</v>
+      </c>
+      <c r="H1050" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1050" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1050" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1050" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1050" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1050" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1051" s="6"/>
+      <c r="B1051" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1051" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1051" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1051" s="2">
+        <v>43</v>
+      </c>
+      <c r="F1051" s="2">
+        <v>2460000</v>
+      </c>
+      <c r="G1051" s="2">
+        <v>2460000</v>
+      </c>
+      <c r="H1051" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1051" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1051" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1051" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1051" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1051" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1052" s="6"/>
+      <c r="B1052" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1052" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1052" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1052" s="2">
+        <v>42</v>
+      </c>
+      <c r="F1052" s="2">
+        <v>5020000</v>
+      </c>
+      <c r="G1052" s="2">
+        <v>4970000</v>
+      </c>
+      <c r="H1052" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1052" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1052" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1052" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1052" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1052" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1053" s="6"/>
+      <c r="B1053" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1053" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1053" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1053" s="2">
+        <v>43</v>
+      </c>
+      <c r="F1053" s="2">
+        <v>4330000</v>
+      </c>
+      <c r="G1053" s="2">
+        <v>4350000</v>
+      </c>
+      <c r="H1053" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1053" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1053" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1053" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1053" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1053" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1054" s="6"/>
+      <c r="B1054" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1054" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1054" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1054" s="2">
+        <v>60</v>
+      </c>
+      <c r="F1054" s="2">
+        <v>1360000</v>
+      </c>
+      <c r="G1054" s="2">
+        <v>1350000</v>
+      </c>
+      <c r="H1054" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1054" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1054" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1054" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1054" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1054" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1055" s="6"/>
+      <c r="B1055" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1055" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1055" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1055" s="2">
+        <v>124</v>
+      </c>
+      <c r="F1055" s="2">
+        <v>3370000</v>
+      </c>
+      <c r="G1055" s="2">
+        <v>3260000</v>
+      </c>
+      <c r="H1055" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1055" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1055" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1055" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1055" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1055" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1056" s="6"/>
+      <c r="B1056" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1056" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1056" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1056" s="2">
+        <v>112</v>
+      </c>
+      <c r="F1056" s="2">
+        <v>4560000</v>
+      </c>
+      <c r="G1056" s="2">
+        <v>4530000</v>
+      </c>
+      <c r="H1056" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I1056" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1056" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1056" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1056" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1056" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1057" s="6"/>
+      <c r="B1057" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1057" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1057" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1057" s="2">
+        <v>108</v>
+      </c>
+      <c r="F1057" s="2">
+        <v>3620000</v>
+      </c>
+      <c r="G1057" s="2">
+        <v>3560000</v>
+      </c>
+      <c r="H1057" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="I1057" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1057" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1057" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1057" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1057" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1058" s="6"/>
+      <c r="B1058" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1058" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1058" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1058" s="2">
+        <v>183</v>
+      </c>
+      <c r="F1058" s="2">
+        <v>10130000</v>
+      </c>
+      <c r="G1058" s="2">
+        <v>10020000</v>
+      </c>
+      <c r="H1058" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I1058" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1058" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1058" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1058" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1058" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1059" s="6"/>
+      <c r="B1059" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1059" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1059" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1059" s="2">
+        <v>167</v>
+      </c>
+      <c r="F1059" s="2">
+        <v>9680000</v>
+      </c>
+      <c r="G1059" s="2">
+        <v>9530000</v>
+      </c>
+      <c r="H1059" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I1059" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1059" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1059" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1059" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1059" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1060" s="6"/>
+      <c r="B1060" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1060" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1060" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1060" s="2">
+        <v>127</v>
+      </c>
+      <c r="F1060" s="2">
+        <v>3230000</v>
+      </c>
+      <c r="G1060" s="2">
+        <v>3210000</v>
+      </c>
+      <c r="H1060" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I1060" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1060" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1060" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1060" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1060" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1061" s="6"/>
+      <c r="B1061" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1061" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1061" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1061" s="2">
+        <v>69</v>
+      </c>
+      <c r="F1061" s="2">
+        <v>1730000</v>
+      </c>
+      <c r="G1061" s="2">
+        <v>1740000</v>
+      </c>
+      <c r="H1061" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1061" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1061" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1061" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1061" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1061" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1062" s="6"/>
+      <c r="B1062" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1062" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1062" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1062" s="2">
+        <v>72</v>
+      </c>
+      <c r="F1062" s="2">
+        <v>1840000</v>
+      </c>
+      <c r="G1062" s="2">
+        <v>1840000</v>
+      </c>
+      <c r="H1062" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1062" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1062" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1062" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1062" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1062" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1063" s="6"/>
+      <c r="B1063" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1063" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1063" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1063" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1063" s="2">
+        <v>2430000</v>
+      </c>
+      <c r="G1063" s="2">
+        <v>2410000</v>
+      </c>
+      <c r="H1063" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I1063" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1063" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1063" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1063" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1063" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1064" s="6"/>
+      <c r="B1064" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1064" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1064" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1064" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1064" s="2">
+        <v>2340000</v>
+      </c>
+      <c r="G1064" s="2">
+        <v>2340000</v>
+      </c>
+      <c r="H1064" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1064" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1064" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1064" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1064" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1064" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1065" s="6"/>
+      <c r="B1065" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1065" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1065" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1065" s="2">
+        <v>110</v>
+      </c>
+      <c r="F1065" s="2">
+        <v>3490000</v>
+      </c>
+      <c r="G1065" s="2">
+        <v>3410000</v>
+      </c>
+      <c r="H1065" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I1065" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1065" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1065" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1065" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1065" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1066" s="6"/>
+      <c r="B1066" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1066" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1066" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1066" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1066" s="2">
+        <v>3740000</v>
+      </c>
+      <c r="G1066" s="2">
+        <v>3750000</v>
+      </c>
+      <c r="H1066" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I1066" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1066" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1066" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1066" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1066" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1067" s="6"/>
+      <c r="B1067" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1067" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1067" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1067" s="2">
+        <v>59</v>
+      </c>
+      <c r="F1067" s="2">
+        <v>900000</v>
+      </c>
+      <c r="G1067" s="2">
+        <v>910000</v>
+      </c>
+      <c r="H1067" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1067" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1067" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1067" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1067" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1067" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1068" s="6"/>
+      <c r="B1068" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1068" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1068" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1068" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1068" s="2">
+        <v>3160000</v>
+      </c>
+      <c r="G1068" s="2">
+        <v>3080000</v>
+      </c>
+      <c r="H1068" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I1068" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1068" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1068" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1068" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1068" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1069" s="6"/>
+      <c r="B1069" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1069" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1069" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1069" s="2">
+        <v>95</v>
+      </c>
+      <c r="F1069" s="2">
+        <v>3670000</v>
+      </c>
+      <c r="G1069" s="2">
+        <v>3630000</v>
+      </c>
+      <c r="H1069" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I1069" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1069" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1069" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1069" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1069" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1070" s="6"/>
+      <c r="B1070" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1070" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1070" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1070" s="2">
+        <v>71</v>
+      </c>
+      <c r="F1070" s="2">
+        <v>1570000</v>
+      </c>
+      <c r="G1070" s="2">
+        <v>1600000</v>
+      </c>
+      <c r="H1070" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I1070" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1070" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1070" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1070" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1070" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1071" s="6"/>
+      <c r="B1071" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1071" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1071" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1071" s="2">
+        <v>127</v>
+      </c>
+      <c r="F1071" s="2">
+        <v>5700000</v>
+      </c>
+      <c r="G1071" s="2">
+        <v>5620000</v>
+      </c>
+      <c r="H1071" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1071" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1071" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1071" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1071" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1071" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1072" s="6"/>
+      <c r="B1072" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1072" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1072" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1072" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1072" s="2">
+        <v>230000</v>
+      </c>
+      <c r="G1072" s="2">
+        <v>230000</v>
+      </c>
+      <c r="H1072" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1072" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1072" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1072" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1072" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1072" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1073" s="6"/>
+      <c r="B1073" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1073" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1073" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1073" s="2">
+        <v>72</v>
+      </c>
+      <c r="F1073" s="2">
+        <v>3330000</v>
+      </c>
+      <c r="G1073" s="2">
+        <v>3260000</v>
+      </c>
+      <c r="H1073" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1073" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1073" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1073" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1073" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1073" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1074" s="6"/>
+      <c r="B1074" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1074" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1074" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1074" s="2">
+        <v>36</v>
+      </c>
+      <c r="F1074" s="2">
+        <v>3150000</v>
+      </c>
+      <c r="G1074" s="2">
+        <v>3160000</v>
+      </c>
+      <c r="H1074" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1074" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1074" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1074" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1074" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1074" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1075" s="6"/>
+      <c r="B1075" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1075" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1075" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1075" s="2">
+        <v>184</v>
+      </c>
+      <c r="F1075" s="2">
+        <v>15530000</v>
+      </c>
+      <c r="G1075" s="2">
+        <v>15550000</v>
+      </c>
+      <c r="H1075" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I1075" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1075" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1075" s="2">
+        <v>2</v>
+      </c>
+      <c r="L1075" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1075" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1076" s="6"/>
+      <c r="B1076" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1076" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1076" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1076" s="2">
+        <v>87</v>
+      </c>
+      <c r="F1076" s="2">
+        <v>2590000</v>
+      </c>
+      <c r="G1076" s="2">
+        <v>2570000</v>
+      </c>
+      <c r="H1076" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I1076" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1076" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1076" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1076" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1076" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1077" s="6"/>
+      <c r="B1077" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1077" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1077" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1077" s="2">
+        <v>123</v>
+      </c>
+      <c r="F1077" s="2">
+        <v>3760000</v>
+      </c>
+      <c r="G1077" s="2">
+        <v>3840000</v>
+      </c>
+      <c r="H1077" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1077" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1077" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1077" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1077" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1077" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1078" s="6"/>
+      <c r="B1078" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1078" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1078" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1078" s="2">
+        <v>89</v>
+      </c>
+      <c r="F1078" s="2">
+        <v>1850000</v>
+      </c>
+      <c r="G1078" s="2">
+        <v>1860000</v>
+      </c>
+      <c r="H1078" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I1078" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1078" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1078" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1078" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1078" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1079" s="6"/>
+      <c r="B1079" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C1079" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1079" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1079" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1079" s="2">
+        <v>290000</v>
+      </c>
+      <c r="G1079" s="2">
+        <v>290000</v>
+      </c>
+      <c r="H1079" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I1079" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1079" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1079" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1079" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1079" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1080" s="6"/>
+      <c r="B1080" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1080" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1080" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1080" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1080" s="2">
+        <v>220000</v>
+      </c>
+      <c r="G1080" s="2">
+        <v>220000</v>
+      </c>
+      <c r="H1080" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1080" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1080" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1080" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1080" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1080" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1081" s="6"/>
+      <c r="B1081" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1081" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1081" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1081" s="2">
+        <v>6</v>
+      </c>
+      <c r="F1081" s="2">
+        <v>3650000</v>
+      </c>
+      <c r="G1081" s="2">
+        <v>3720000</v>
+      </c>
+      <c r="H1081" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="I1081" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1081" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1081" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1081" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1081" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1082" s="6"/>
+      <c r="B1082" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1082" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1082" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1082" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1082" s="2">
+        <v>2320000</v>
+      </c>
+      <c r="G1082" s="2">
+        <v>2270000</v>
+      </c>
+      <c r="H1082" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I1082" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1082" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1082" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1082" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1082" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1083" s="6"/>
+      <c r="B1083" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1083" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1083" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1083" s="2">
+        <v>100</v>
+      </c>
+      <c r="F1083" s="2">
+        <v>4810000</v>
+      </c>
+      <c r="G1083" s="2">
+        <v>4870000</v>
+      </c>
+      <c r="H1083" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I1083" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1083" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1083" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1083" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1083" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1084" s="6"/>
+      <c r="B1084" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1084" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1084" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1084" s="2">
+        <v>199</v>
+      </c>
+      <c r="F1084" s="2">
+        <v>19070000</v>
+      </c>
+      <c r="G1084" s="2">
+        <v>19290000</v>
+      </c>
+      <c r="H1084" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I1084" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1084" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1084" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1084" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1084" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1085" s="6"/>
+      <c r="B1085" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1085" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1085" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1085" s="2">
+        <v>179</v>
+      </c>
+      <c r="F1085" s="2">
+        <v>11850000</v>
+      </c>
+      <c r="G1085" s="2">
+        <v>11790000</v>
+      </c>
+      <c r="H1085" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1085" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1085" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1085" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1085" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1085" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1086" s="6"/>
+      <c r="B1086" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C1086" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1086" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1086" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1086" s="2">
+        <v>350000</v>
+      </c>
+      <c r="G1086" s="2">
+        <v>350000</v>
+      </c>
+      <c r="H1086" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I1086" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1086" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1086" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1086" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1086" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1087" s="6"/>
+      <c r="B1087" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1087" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1087" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1087" s="2">
+        <v>185</v>
+      </c>
+      <c r="F1087" s="2">
+        <v>12210000</v>
+      </c>
+      <c r="G1087" s="2">
+        <v>12130000</v>
+      </c>
+      <c r="H1087" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I1087" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1087" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1087" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1087" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1087" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1088" s="6"/>
+      <c r="B1088" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1088" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1088" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1088" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1088" s="2">
+        <v>4430000</v>
+      </c>
+      <c r="G1088" s="2">
+        <v>4470000</v>
+      </c>
+      <c r="H1088" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1088" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1088" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1088" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1088" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1088" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1089" s="6"/>
+      <c r="B1089" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1089" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1089" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1089" s="2">
+        <v>51</v>
+      </c>
+      <c r="F1089" s="2">
+        <v>2630000</v>
+      </c>
+      <c r="G1089" s="2">
+        <v>2730000</v>
+      </c>
+      <c r="H1089" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I1089" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1089" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1089" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1089" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1089" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1090" s="6"/>
+      <c r="B1090" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1090" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1090" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1090" s="2">
+        <v>119</v>
+      </c>
+      <c r="F1090" s="2">
+        <v>6180000</v>
+      </c>
+      <c r="G1090" s="2">
+        <v>6110000</v>
+      </c>
+      <c r="H1090" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1090" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1090" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1090" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1090" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1090" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1091" s="6"/>
+      <c r="B1091" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1091" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1091" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1091" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1091" s="2">
+        <v>170000</v>
+      </c>
+      <c r="G1091" s="2">
+        <v>170000</v>
+      </c>
+      <c r="H1091" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1091" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1091" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1091" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1091" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1091" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1092" s="6"/>
+      <c r="B1092" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1092" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1092" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1092" s="2">
+        <v>127</v>
+      </c>
+      <c r="F1092" s="2">
+        <v>6530000</v>
+      </c>
+      <c r="G1092" s="2">
+        <v>6400000</v>
+      </c>
+      <c r="H1092" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I1092" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1092" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1092" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1092" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1092" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1093" s="6"/>
+      <c r="B1093" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1093" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1093" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1093" s="2">
+        <v>69</v>
+      </c>
+      <c r="F1093" s="2">
+        <v>4770000</v>
+      </c>
+      <c r="G1093" s="2">
+        <v>4810000</v>
+      </c>
+      <c r="H1093" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I1093" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1093" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1093" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1093" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1093" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1094" s="6"/>
+      <c r="B1094" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1094" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1094" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1094" s="2">
+        <v>68</v>
+      </c>
+      <c r="F1094" s="2">
+        <v>4360000</v>
+      </c>
+      <c r="G1094" s="2">
+        <v>4400000</v>
+      </c>
+      <c r="H1094" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1094" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1094" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1094" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1094" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1094" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1095" s="6"/>
+      <c r="B1095" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1095" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1095" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1095" s="2">
+        <v>81</v>
+      </c>
+      <c r="F1095" s="2">
+        <v>1550000</v>
+      </c>
+      <c r="G1095" s="2">
+        <v>1560000</v>
+      </c>
+      <c r="H1095" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1095" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1095" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1095" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1095" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1095" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1096" s="6"/>
+      <c r="B1096" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1096" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1096" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1096" s="2">
+        <v>123</v>
+      </c>
+      <c r="F1096" s="2">
+        <v>5340000</v>
+      </c>
+      <c r="G1096" s="2">
+        <v>5350000</v>
+      </c>
+      <c r="H1096" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1096" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1096" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1096" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1096" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1096" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1097" s="6"/>
+      <c r="B1097" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1097" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1097" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1097" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1097" s="2">
+        <v>4690000</v>
+      </c>
+      <c r="G1097" s="2">
+        <v>4680000</v>
+      </c>
+      <c r="H1097" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1097" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1097" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1097" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1097" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1097" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1098" s="6"/>
+      <c r="B1098" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1098" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1098" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1098" s="2">
+        <v>109</v>
+      </c>
+      <c r="F1098" s="2">
+        <v>3900000</v>
+      </c>
+      <c r="G1098" s="2">
+        <v>3820000</v>
+      </c>
+      <c r="H1098" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I1098" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1098" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1098" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1098" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1098" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1099" s="6"/>
+      <c r="B1099" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1099" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1099" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1099" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1099" s="2">
+        <v>160000</v>
+      </c>
+      <c r="G1099" s="2">
+        <v>160000</v>
+      </c>
+      <c r="H1099" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I1099" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1099" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1099" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1099" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1099" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1100" s="6"/>
+      <c r="B1100" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1100" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1100" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1100" s="2">
+        <v>16</v>
+      </c>
+      <c r="F1100" s="2">
+        <v>460000</v>
+      </c>
+      <c r="G1100" s="2">
+        <v>460000</v>
+      </c>
+      <c r="H1100" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1100" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1100" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1100" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1100" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1100" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1101" s="6"/>
+      <c r="B1101" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1101" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1101" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1101" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1101" s="2">
+        <v>1970000</v>
+      </c>
+      <c r="G1101" s="2">
+        <v>1960000</v>
+      </c>
+      <c r="H1101" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I1101" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1101" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1101" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1101" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1101" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1102" s="6"/>
+      <c r="B1102" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1102" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1102" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1102" s="2">
+        <v>12</v>
+      </c>
+      <c r="F1102" s="2">
+        <v>640000</v>
+      </c>
+      <c r="G1102" s="2">
+        <v>640000</v>
+      </c>
+      <c r="H1102" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1102" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1102" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1102" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1102" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1103" s="6"/>
+      <c r="B1103" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1103" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1103" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1103" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1103" s="2">
+        <v>10640000</v>
+      </c>
+      <c r="G1103" s="2">
+        <v>11300000</v>
+      </c>
+      <c r="H1103" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1103" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1103" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1103" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1103" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1103" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1104" s="6"/>
+      <c r="B1104" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1104" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1104" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1104" s="2">
+        <v>118</v>
+      </c>
+      <c r="F1104" s="2">
+        <v>6680000</v>
+      </c>
+      <c r="G1104" s="2">
+        <v>6530000</v>
+      </c>
+      <c r="H1104" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1104" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1104" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1104" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1104" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1104" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1105" s="6"/>
+      <c r="B1105" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1105" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1105" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1105" s="2">
+        <v>30</v>
+      </c>
+      <c r="F1105" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="G1105" s="2">
+        <v>2630000</v>
+      </c>
+      <c r="H1105" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1105" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1105" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1105" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1105" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1105" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1106" s="6"/>
+      <c r="B1106" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1106" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1106" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1106" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1106" s="2">
+        <v>260000</v>
+      </c>
+      <c r="G1106" s="2">
+        <v>260000</v>
+      </c>
+      <c r="H1106" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="I1106" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1106" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1106" s="2">
+        <v>4</v>
+      </c>
+      <c r="L1106" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1106" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1107" s="6"/>
+      <c r="B1107" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1107" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1107" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1107" s="2">
+        <v>54</v>
+      </c>
+      <c r="F1107" s="2">
+        <v>2300000</v>
+      </c>
+      <c r="G1107" s="2">
+        <v>2300000</v>
+      </c>
+      <c r="H1107" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1107" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1107" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1107" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1107" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1107" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1108" s="6"/>
+      <c r="B1108" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1108" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1108" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1108" s="2">
+        <v>89</v>
+      </c>
+      <c r="F1108" s="2">
+        <v>8520000</v>
+      </c>
+      <c r="G1108" s="2">
+        <v>8460000</v>
+      </c>
+      <c r="H1108" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I1108" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1108" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1108" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1108" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1108" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1109" s="6"/>
+      <c r="B1109" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1109" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1109" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1109" s="2">
+        <v>130</v>
+      </c>
+      <c r="F1109" s="2">
+        <v>12090000</v>
+      </c>
+      <c r="G1109" s="2">
+        <v>12150000</v>
+      </c>
+      <c r="H1109" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I1109" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1109" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1109" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1109" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1109" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1110" s="6"/>
+      <c r="B1110" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1110" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1110" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1110" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1110" s="2">
+        <v>1920000</v>
+      </c>
+      <c r="G1110" s="2">
+        <v>1900000</v>
+      </c>
+      <c r="H1110" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1110" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1110" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1110" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1110" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1110" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1111" s="6"/>
+      <c r="B1111" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1111" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1111" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1111" s="2">
+        <v>91</v>
+      </c>
+      <c r="F1111" s="2">
+        <v>8730000</v>
+      </c>
+      <c r="G1111" s="2">
+        <v>8660000</v>
+      </c>
+      <c r="H1111" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="I1111" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1111" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1111" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1111" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1111" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1112" s="6"/>
+      <c r="B1112" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1112" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1112" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1112" s="2">
+        <v>30</v>
+      </c>
+      <c r="F1112" s="2">
+        <v>880000</v>
+      </c>
+      <c r="G1112" s="2">
+        <v>870000</v>
+      </c>
+      <c r="H1112" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1112" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1112" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1112" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1112" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1113" s="6"/>
+      <c r="B1113" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1113" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1113" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1113" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1113" s="2">
+        <v>290000</v>
+      </c>
+      <c r="G1113" s="2">
+        <v>290000</v>
+      </c>
+      <c r="H1113" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1113" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1113" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1113" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1113" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1113" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1114" s="6"/>
+      <c r="B1114" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1114" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1114" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1114" s="2">
+        <v>108</v>
+      </c>
+      <c r="F1114" s="2">
+        <v>3200000</v>
+      </c>
+      <c r="G1114" s="2">
+        <v>3170000</v>
+      </c>
+      <c r="H1114" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1114" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1114" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1114" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1114" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1114" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1115" s="6"/>
+      <c r="B1115" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1115" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1115" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1115" s="2">
+        <v>112</v>
+      </c>
+      <c r="F1115" s="2">
+        <v>4120000</v>
+      </c>
+      <c r="G1115" s="2">
+        <v>4110000</v>
+      </c>
+      <c r="H1115" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1115" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1115" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1115" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1115" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1115" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1116" s="6"/>
+      <c r="B1116" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1116" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1116" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1116" s="2">
+        <v>136</v>
+      </c>
+      <c r="F1116" s="2">
+        <v>7340000</v>
+      </c>
+      <c r="G1116" s="2">
+        <v>7330000</v>
+      </c>
+      <c r="H1116" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I1116" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1116" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1116" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1116" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1116" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1117" s="6"/>
+      <c r="B1117" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1117" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1117" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1117" s="2">
+        <v>90</v>
+      </c>
+      <c r="F1117" s="2">
+        <v>3610000</v>
+      </c>
+      <c r="G1117" s="2">
+        <v>3590000</v>
+      </c>
+      <c r="H1117" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I1117" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1117" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1117" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1117" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1117" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1118" s="6"/>
+      <c r="B1118" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1118" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1118" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1118" s="2">
+        <v>15</v>
+      </c>
+      <c r="F1118" s="2">
+        <v>390000</v>
+      </c>
+      <c r="G1118" s="2">
+        <v>390000</v>
+      </c>
+      <c r="H1118" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1118" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1118" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1118" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1118" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1118" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1119" s="6"/>
+      <c r="B1119" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1119" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1119" s="2">
+        <v>58</v>
+      </c>
+      <c r="F1119" s="2">
+        <v>1310000</v>
+      </c>
+      <c r="G1119" s="2">
+        <v>1300000</v>
+      </c>
+      <c r="H1119" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1119" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1119" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1119" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1119" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1119" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1120" s="6"/>
+      <c r="B1120" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1120" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1120" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1120" s="2">
+        <v>48</v>
+      </c>
+      <c r="F1120" s="2">
+        <v>1660000</v>
+      </c>
+      <c r="G1120" s="2">
+        <v>1650000</v>
+      </c>
+      <c r="H1120" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I1120" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1120" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1120" s="2">
+        <v>5</v>
+      </c>
+      <c r="L1120" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1120" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1121" s="6"/>
+      <c r="B1121" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1121" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1121" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1121" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1121" s="2">
+        <v>4640000</v>
+      </c>
+      <c r="G1121" s="2">
+        <v>4670000</v>
+      </c>
+      <c r="H1121" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1121" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1121" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1121" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1121" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1121" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1122" s="6"/>
+      <c r="B1122" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1122" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1122" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1122" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1122" s="2">
+        <v>420000</v>
+      </c>
+      <c r="G1122" s="2">
+        <v>420000</v>
+      </c>
+      <c r="H1122" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1122" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1122" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1122" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1122" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1122" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1123" s="6"/>
+      <c r="B1123" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1123" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1123" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1123" s="2">
+        <v>47</v>
+      </c>
+      <c r="F1123" s="2">
+        <v>1410000</v>
+      </c>
+      <c r="G1123" s="2">
+        <v>1380000</v>
+      </c>
+      <c r="H1123" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1123" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1123" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1123" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1123" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1123" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1124" s="6"/>
+      <c r="B1124" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1124" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1124" s="2">
+        <v>156</v>
+      </c>
+      <c r="F1124" s="2">
+        <v>6840000</v>
+      </c>
+      <c r="G1124" s="2">
+        <v>6760000</v>
+      </c>
+      <c r="H1124" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I1124" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1124" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1124" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1124" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1124" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1125" s="6"/>
+      <c r="B1125" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1125" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1125" s="2">
+        <v>29</v>
+      </c>
+      <c r="F1125" s="2">
+        <v>850000</v>
+      </c>
+      <c r="G1125" s="2">
+        <v>840000</v>
+      </c>
+      <c r="H1125" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1125" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1125" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1125" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1125" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1125" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1126" s="6"/>
+      <c r="B1126" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1126" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1126" s="2">
+        <v>102</v>
+      </c>
+      <c r="F1126" s="2">
+        <v>2750000</v>
+      </c>
+      <c r="G1126" s="2">
+        <v>2730000</v>
+      </c>
+      <c r="H1126" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I1126" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1126" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1126" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1126" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1126" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1127" s="6"/>
+      <c r="B1127" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1127" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1127" s="2">
+        <v>19</v>
+      </c>
+      <c r="F1127" s="2">
+        <v>910000</v>
+      </c>
+      <c r="G1127" s="2">
+        <v>900000</v>
+      </c>
+      <c r="H1127" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I1127" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1127" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1127" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1127" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1127" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1128" s="6"/>
+      <c r="B1128" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1128" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1128" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1128" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1128" s="2">
+        <v>2870000</v>
+      </c>
+      <c r="G1128" s="2">
+        <v>2940000</v>
+      </c>
+      <c r="H1128" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I1128" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1128" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1128" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1128" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1128" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1129" s="6"/>
+      <c r="B1129" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1129" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1129" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1129" s="2">
+        <v>40</v>
+      </c>
+      <c r="F1129" s="2">
+        <v>2390000</v>
+      </c>
+      <c r="G1129" s="2">
+        <v>2360000</v>
+      </c>
+      <c r="H1129" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1129" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1129" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1129" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1129" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1129" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1130" s="6"/>
+      <c r="B1130" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1130" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1130" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1130" s="2">
+        <v>17</v>
+      </c>
+      <c r="F1130" s="2">
+        <v>1400000</v>
+      </c>
+      <c r="G1130" s="2">
+        <v>1420000</v>
+      </c>
+      <c r="H1130" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1130" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1130" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1130" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1130" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1130" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1131" s="6"/>
+      <c r="B1131" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1131" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1131" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1131" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1131" s="2">
+        <v>160000</v>
+      </c>
+      <c r="G1131" s="2">
+        <v>160000</v>
+      </c>
+      <c r="H1131" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1131" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1131" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1131" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1131" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1131" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1132" s="6"/>
+      <c r="B1132" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1132" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1132" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1132" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1132" s="2">
+        <v>3650000</v>
+      </c>
+      <c r="G1132" s="2">
+        <v>3610000</v>
+      </c>
+      <c r="H1132" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1132" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1132" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1132" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1132" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1132" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1133" s="6"/>
+      <c r="B1133" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1133" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1133" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1133" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1133" s="2">
+        <v>190000</v>
+      </c>
+      <c r="G1133" s="2">
+        <v>190000</v>
+      </c>
+      <c r="H1133" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1133" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1133" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1133" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1133" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1133" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1134" s="6"/>
+      <c r="B1134" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C1134" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1134" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1134" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1134" s="2">
+        <v>3520000</v>
+      </c>
+      <c r="G1134" s="2">
+        <v>3400000</v>
+      </c>
+      <c r="H1134" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1134" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1134" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1134" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1134" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1134" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M1135" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:M1" xr:uid="{93EB6F54-7766-4759-97DF-03549A275A7C}">
@@ -40972,8 +44488,97 @@
     <hyperlink ref="B964" r:id="rId427" display="https://www.com-analytics.de/player/34146" xr:uid="{6D366095-4485-4799-820E-0163C666B073}"/>
     <hyperlink ref="B965" r:id="rId428" display="https://www.com-analytics.de/player/34148" xr:uid="{41264995-04B2-4496-A841-8876A9A7B88E}"/>
     <hyperlink ref="B966" r:id="rId429" display="https://www.com-analytics.de/player/34187" xr:uid="{6B55E76B-D339-42F6-AC79-CB79A92F7E6E}"/>
+    <hyperlink ref="B1046" r:id="rId430" display="https://www.com-analytics.de/player/30755" xr:uid="{B0FFC3B6-B77F-4227-944F-07B23F45EFA9}"/>
+    <hyperlink ref="B1047" r:id="rId431" display="https://www.com-analytics.de/player/31419" xr:uid="{8386018F-208B-472E-A6DD-53190B9BF445}"/>
+    <hyperlink ref="B1048" r:id="rId432" display="https://www.com-analytics.de/player/31846" xr:uid="{8CAF91C6-74F7-4630-A075-65300CC21E77}"/>
+    <hyperlink ref="B1049" r:id="rId433" display="https://www.com-analytics.de/player/31910" xr:uid="{58FA4847-C907-4DAF-810B-16DA9826BFB7}"/>
+    <hyperlink ref="B1050" r:id="rId434" display="https://www.com-analytics.de/player/31932" xr:uid="{4CE92407-DE5F-4E93-8B82-8A8F4BF37D8F}"/>
+    <hyperlink ref="B1051" r:id="rId435" display="https://www.com-analytics.de/player/31958" xr:uid="{E90F4231-2B27-45C1-9261-B5ADFA8B5FB1}"/>
+    <hyperlink ref="B1052" r:id="rId436" display="https://www.com-analytics.de/player/32080" xr:uid="{8ABBB07B-7425-47EC-97D9-4925AF302F4F}"/>
+    <hyperlink ref="B1053" r:id="rId437" display="https://www.com-analytics.de/player/32122" xr:uid="{073A333A-069F-4C44-BE6B-376A62E7BAF0}"/>
+    <hyperlink ref="B1054" r:id="rId438" display="https://www.com-analytics.de/player/32310" xr:uid="{77084502-ABE8-4536-A329-056A25448C0B}"/>
+    <hyperlink ref="B1055" r:id="rId439" display="https://www.com-analytics.de/player/32364" xr:uid="{BE70D4EF-EC97-47AE-8374-D2E5CDE13296}"/>
+    <hyperlink ref="B1056" r:id="rId440" display="https://www.com-analytics.de/player/32398" xr:uid="{5016B014-CA6F-4E0B-A9B4-7CC7EEC8FEE8}"/>
+    <hyperlink ref="B1057" r:id="rId441" display="https://www.com-analytics.de/player/32472" xr:uid="{32932586-0995-4BDD-A058-F4B06AB1A829}"/>
+    <hyperlink ref="B1058" r:id="rId442" display="https://www.com-analytics.de/player/32509" xr:uid="{CD183843-15D6-4661-935E-0DD05B639C42}"/>
+    <hyperlink ref="B1059" r:id="rId443" display="https://www.com-analytics.de/player/32553" xr:uid="{7D343D60-BE89-4528-ACE7-876B6C15D57D}"/>
+    <hyperlink ref="B1060" r:id="rId444" display="https://www.com-analytics.de/player/32575" xr:uid="{25C1DE99-9D80-4F2F-8E3E-D31BE62DD265}"/>
+    <hyperlink ref="B1061" r:id="rId445" display="https://www.com-analytics.de/player/32579" xr:uid="{73ABBBB9-78BF-442A-9A66-A2EA144FD3F8}"/>
+    <hyperlink ref="B1062" r:id="rId446" display="https://www.com-analytics.de/player/32603" xr:uid="{1C57847F-6CCE-4E77-828D-9DCDCFF814F2}"/>
+    <hyperlink ref="B1063" r:id="rId447" display="https://www.com-analytics.de/player/32629" xr:uid="{1565101F-76AF-47F7-9A37-655F9A28F485}"/>
+    <hyperlink ref="B1064" r:id="rId448" display="https://www.com-analytics.de/player/32630" xr:uid="{45E4510D-DB3B-4DBB-97C1-3918E12E4B20}"/>
+    <hyperlink ref="B1065" r:id="rId449" display="https://www.com-analytics.de/player/32633" xr:uid="{4A99EF4F-1E9F-4176-93AF-60AB42C13C27}"/>
+    <hyperlink ref="B1066" r:id="rId450" display="https://www.com-analytics.de/player/32636" xr:uid="{4D6CA489-C7DA-40ED-B1AF-1D8558576F66}"/>
+    <hyperlink ref="B1067" r:id="rId451" display="https://www.com-analytics.de/player/32738" xr:uid="{A63EB659-8B5E-4612-B7C7-4128F9182F01}"/>
+    <hyperlink ref="B1068" r:id="rId452" display="https://www.com-analytics.de/player/32744" xr:uid="{90DAC7E3-D4EF-4FAB-AE2C-4CAA9E083B7D}"/>
+    <hyperlink ref="B1069" r:id="rId453" display="https://www.com-analytics.de/player/32754" xr:uid="{F3DF93A7-B5CF-4AC5-84C7-E6A85FFEB67A}"/>
+    <hyperlink ref="B1070" r:id="rId454" display="https://www.com-analytics.de/player/32756" xr:uid="{2BF42AC4-572F-4742-92BB-4B439A7F7ED5}"/>
+    <hyperlink ref="B1071" r:id="rId455" display="https://www.com-analytics.de/player/32787" xr:uid="{4D651536-12A6-4C38-B65F-973AEF94C6F9}"/>
+    <hyperlink ref="B1072" r:id="rId456" display="https://www.com-analytics.de/player/32841" xr:uid="{4E88EBF8-7C05-44AE-9CC4-E1A2AA1C3635}"/>
+    <hyperlink ref="B1073" r:id="rId457" display="https://www.com-analytics.de/player/32877" xr:uid="{A8E4FC38-0313-43CB-AFE1-ED190819EF9C}"/>
+    <hyperlink ref="B1074" r:id="rId458" display="https://www.com-analytics.de/player/32931" xr:uid="{3BC17B98-FF4A-4FE4-A4E7-49DCA9C1A256}"/>
+    <hyperlink ref="B1075" r:id="rId459" display="https://www.com-analytics.de/player/32948" xr:uid="{D1F98622-F473-47C7-8F64-5780D321712F}"/>
+    <hyperlink ref="B1076" r:id="rId460" display="https://www.com-analytics.de/player/32977" xr:uid="{2FBAC77F-F4C1-4322-9E5E-8B0FFFAC0CF4}"/>
+    <hyperlink ref="B1077" r:id="rId461" display="https://www.com-analytics.de/player/33070" xr:uid="{FCD46820-C12A-4166-B999-D6B490807A25}"/>
+    <hyperlink ref="B1078" r:id="rId462" display="https://www.com-analytics.de/player/33096" xr:uid="{8046DE26-1F8B-41D0-9753-6B77620B64A8}"/>
+    <hyperlink ref="B1079" r:id="rId463" display="https://www.com-analytics.de/player/33105" xr:uid="{ADF94AB4-61B8-4780-AC12-64055D52B341}"/>
+    <hyperlink ref="B1080" r:id="rId464" display="https://www.com-analytics.de/player/33109" xr:uid="{6782FCF7-4CEB-4AF3-9F1F-4E5BF2C22544}"/>
+    <hyperlink ref="B1081" r:id="rId465" display="https://www.com-analytics.de/player/33133" xr:uid="{304A4B82-011D-43BD-B4C2-56772EB62FC1}"/>
+    <hyperlink ref="B1082" r:id="rId466" display="https://www.com-analytics.de/player/33156" xr:uid="{5C57AEED-309C-4375-AFFD-B86A082194A7}"/>
+    <hyperlink ref="B1083" r:id="rId467" display="https://www.com-analytics.de/player/33157" xr:uid="{1FDB6A19-39C8-4872-BFA5-0185458226B2}"/>
+    <hyperlink ref="B1084" r:id="rId468" display="https://www.com-analytics.de/player/33236" xr:uid="{1E2D8F80-9781-4EF3-B5E3-92211F928DA9}"/>
+    <hyperlink ref="B1085" r:id="rId469" display="https://www.com-analytics.de/player/33296" xr:uid="{EFDA8CB1-CA43-4636-8311-8B7961621E28}"/>
+    <hyperlink ref="B1086" r:id="rId470" display="https://www.com-analytics.de/player/33313" xr:uid="{18AD819C-16EF-4721-B6A7-022B610E0102}"/>
+    <hyperlink ref="B1087" r:id="rId471" display="https://www.com-analytics.de/player/33335" xr:uid="{0B96B4A1-08A8-4CFE-B7FB-9179F0F9F3F2}"/>
+    <hyperlink ref="B1088" r:id="rId472" display="https://www.com-analytics.de/player/33356" xr:uid="{8F8F55C3-73EE-418E-A180-EAF05A91AAE9}"/>
+    <hyperlink ref="B1089" r:id="rId473" display="https://www.com-analytics.de/player/33364" xr:uid="{F965E591-A7EF-4E67-8DE1-791F14A0C546}"/>
+    <hyperlink ref="B1090" r:id="rId474" display="https://www.com-analytics.de/player/33383" xr:uid="{E619F695-99E8-4A6A-ADCE-E9F58C89731D}"/>
+    <hyperlink ref="B1091" r:id="rId475" display="https://www.com-analytics.de/player/33397" xr:uid="{25071E93-9F0E-4F36-86EB-704A73EA4349}"/>
+    <hyperlink ref="B1092" r:id="rId476" display="https://www.com-analytics.de/player/33409" xr:uid="{F47981E6-231B-41C7-8DE9-E074662F69BC}"/>
+    <hyperlink ref="B1093" r:id="rId477" display="https://www.com-analytics.de/player/33514" xr:uid="{957FDB37-1D0D-4C8C-BEF4-68EC5ED3F4B7}"/>
+    <hyperlink ref="B1094" r:id="rId478" display="https://www.com-analytics.de/player/33547" xr:uid="{877AC8EF-5874-4DDD-BC6E-4624F5DB5985}"/>
+    <hyperlink ref="B1095" r:id="rId479" display="https://www.com-analytics.de/player/33550" xr:uid="{4DE94E2C-B767-409E-851D-E4BCAB9C6D05}"/>
+    <hyperlink ref="B1096" r:id="rId480" display="https://www.com-analytics.de/player/33552" xr:uid="{3243CC70-5696-418B-B480-5E47EE74FD0C}"/>
+    <hyperlink ref="B1097" r:id="rId481" display="https://www.com-analytics.de/player/33577" xr:uid="{9CB34097-A966-4286-858D-814A86DCCDD4}"/>
+    <hyperlink ref="B1098" r:id="rId482" display="https://www.com-analytics.de/player/33609" xr:uid="{EB514D1F-5885-40DC-8FA3-25299A01C4C4}"/>
+    <hyperlink ref="B1099" r:id="rId483" display="https://www.com-analytics.de/player/33615" xr:uid="{A1880EB6-6CF2-4CB4-8CB7-63509137F936}"/>
+    <hyperlink ref="B1100" r:id="rId484" display="https://www.com-analytics.de/player/33678" xr:uid="{5DEF044A-E702-498E-B7A8-634A776058C0}"/>
+    <hyperlink ref="B1101" r:id="rId485" display="https://www.com-analytics.de/player/33696" xr:uid="{98A598D2-2854-4CA3-B83A-FBA1A200542E}"/>
+    <hyperlink ref="B1102" r:id="rId486" display="https://www.com-analytics.de/player/33718" xr:uid="{BDB7D5B4-05AA-44CF-8AD2-81BA0F1D3285}"/>
+    <hyperlink ref="B1103" r:id="rId487" display="https://www.com-analytics.de/player/33744" xr:uid="{23885634-3738-48A2-AD11-97DF53052028}"/>
+    <hyperlink ref="B1104" r:id="rId488" display="https://www.com-analytics.de/player/33782" xr:uid="{4649082F-B540-4322-A373-40E0052EC182}"/>
+    <hyperlink ref="B1105" r:id="rId489" display="https://www.com-analytics.de/player/33783" xr:uid="{8F567C4F-8C1B-4732-BC8D-DC8663073113}"/>
+    <hyperlink ref="B1106" r:id="rId490" display="https://www.com-analytics.de/player/33812" xr:uid="{9B27461B-BB58-45F8-B3A5-9D73DA9357BA}"/>
+    <hyperlink ref="B1107" r:id="rId491" display="https://www.com-analytics.de/player/33815" xr:uid="{C0BAF3BD-1B1D-4F6B-8343-DF2AB55507B4}"/>
+    <hyperlink ref="B1108" r:id="rId492" display="https://www.com-analytics.de/player/33827" xr:uid="{FCB2F52A-3536-494E-A44E-BEB2A5D3C245}"/>
+    <hyperlink ref="B1109" r:id="rId493" display="https://www.com-analytics.de/player/33832" xr:uid="{BF353C95-EFA3-48E6-B92F-B6BD66E66228}"/>
+    <hyperlink ref="B1110" r:id="rId494" display="https://www.com-analytics.de/player/33848" xr:uid="{C53C71E8-8CB5-4D6F-B243-EDCDD6A0C81E}"/>
+    <hyperlink ref="B1111" r:id="rId495" display="https://www.com-analytics.de/player/33854" xr:uid="{296900CA-745A-4E27-81B7-3471D09EA7A4}"/>
+    <hyperlink ref="B1112" r:id="rId496" display="https://www.com-analytics.de/player/33882" xr:uid="{BC163EDD-250F-48CC-9809-3E540E8C88EC}"/>
+    <hyperlink ref="B1113" r:id="rId497" display="https://www.com-analytics.de/player/33905" xr:uid="{71A948AF-9004-46B6-A77E-A6E963632398}"/>
+    <hyperlink ref="B1114" r:id="rId498" display="https://www.com-analytics.de/player/33948" xr:uid="{A1217C8A-55F5-4B7E-B67B-8FE39221A118}"/>
+    <hyperlink ref="B1115" r:id="rId499" display="https://www.com-analytics.de/player/33950" xr:uid="{CCC992F9-B8F0-4177-9BD5-C5E6DCE037F3}"/>
+    <hyperlink ref="B1116" r:id="rId500" display="https://www.com-analytics.de/player/33992" xr:uid="{825CEF13-B07C-41A4-98E4-C3E3C10B8B76}"/>
+    <hyperlink ref="B1117" r:id="rId501" display="https://www.com-analytics.de/player/33995" xr:uid="{A5B6FDEA-2C88-4845-B8ED-B09FD6D72032}"/>
+    <hyperlink ref="B1118" r:id="rId502" display="https://www.com-analytics.de/player/33999" xr:uid="{0E27C336-2D91-40DE-9D62-9CD8EC0D7F16}"/>
+    <hyperlink ref="B1119" r:id="rId503" display="https://www.com-analytics.de/player/34001" xr:uid="{179B37F7-1D00-4A68-A80E-E97D2046A5E1}"/>
+    <hyperlink ref="B1120" r:id="rId504" display="https://www.com-analytics.de/player/34006" xr:uid="{036A1A8F-7C55-49F7-9D89-154A27150793}"/>
+    <hyperlink ref="B1121" r:id="rId505" display="https://www.com-analytics.de/player/34008" xr:uid="{8F276541-95AA-475E-8864-CEE5B8A5A255}"/>
+    <hyperlink ref="B1122" r:id="rId506" display="https://www.com-analytics.de/player/34011" xr:uid="{1E45224E-EA63-4149-960C-823E9DE65323}"/>
+    <hyperlink ref="B1123" r:id="rId507" display="https://www.com-analytics.de/player/34019" xr:uid="{C21D6BBB-1307-442A-B3C8-E1E35C5A405E}"/>
+    <hyperlink ref="B1124" r:id="rId508" display="https://www.com-analytics.de/player/34025" xr:uid="{0BF9F279-3094-43F5-B7EF-E79515D825A4}"/>
+    <hyperlink ref="B1125" r:id="rId509" display="https://www.com-analytics.de/player/34035" xr:uid="{E29984F5-0F89-4188-9B4B-C9EC42EA7A72}"/>
+    <hyperlink ref="B1126" r:id="rId510" display="https://www.com-analytics.de/player/34044" xr:uid="{5AA058BD-284F-4A20-8C47-DD924002D2FC}"/>
+    <hyperlink ref="B1127" r:id="rId511" display="https://www.com-analytics.de/player/34050" xr:uid="{DBD2C17E-BFE8-40EC-8FD0-09086C35A9F8}"/>
+    <hyperlink ref="B1128" r:id="rId512" display="https://www.com-analytics.de/player/34096" xr:uid="{B6CD9502-BD82-4B3A-B66B-031BF9D3F3D5}"/>
+    <hyperlink ref="B1129" r:id="rId513" display="https://www.com-analytics.de/player/34109" xr:uid="{91B389C9-525F-4264-B4F9-C356E18DCB87}"/>
+    <hyperlink ref="B1130" r:id="rId514" display="https://www.com-analytics.de/player/34116" xr:uid="{A80DCB19-FC15-4F57-9960-CF9B5BAAEB48}"/>
+    <hyperlink ref="B1131" r:id="rId515" display="https://www.com-analytics.de/player/34126" xr:uid="{86467537-CA43-41A4-937B-75925D7C7607}"/>
+    <hyperlink ref="B1132" r:id="rId516" display="https://www.com-analytics.de/player/34148" xr:uid="{F0E18F02-56BE-4BD4-A4AE-A50E27943A12}"/>
+    <hyperlink ref="B1133" r:id="rId517" display="https://www.com-analytics.de/player/34162" xr:uid="{500CBE5D-421A-4406-A639-70907E3EC3EC}"/>
+    <hyperlink ref="B1134" r:id="rId518" display="https://www.com-analytics.de/player/34187" xr:uid="{A98B63D0-4871-4962-94BB-899FCB9DFCA2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId430"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId519"/>
 </worksheet>
 </file>
--- a/TM_all.xlsx
+++ b/TM_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aecf56309e6168f4/Documents/comunio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="234" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51C20D1E-0DF0-489C-83F1-A6D45CB1609D}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2CB34A4-E516-4A1A-8BA5-8CA4166C45EF}"/>
   <bookViews>
     <workbookView xWindow="6660" yWindow="2700" windowWidth="28800" windowHeight="15370" xr2:uid="{607DE709-F91E-4262-9941-1066BBEC319E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7987" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8675" uniqueCount="302">
   <si>
     <t>Spieler</t>
   </si>
@@ -925,6 +925,27 @@
   <si>
     <t>13.06.2025</t>
   </si>
+  <si>
+    <t>Klostermann</t>
+  </si>
+  <si>
+    <t>N. Schlotterbeck</t>
+  </si>
+  <si>
+    <t>Netz</t>
+  </si>
+  <si>
+    <t>Tschernuth</t>
+  </si>
+  <si>
+    <t>Petersson</t>
+  </si>
+  <si>
+    <t>M. El Mala</t>
+  </si>
+  <si>
+    <t>14.06.2025</t>
+  </si>
 </sst>
 </file>
 
@@ -1348,7 +1369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93EB6F54-7766-4759-97DF-03549A275A7C}">
-  <dimension ref="A1:M1135"/>
+  <dimension ref="A1:M1220"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="2"/>
@@ -44049,7 +44070,3272 @@
       </c>
     </row>
     <row r="1135" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M1135" s="7"/>
+      <c r="B1135" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1135" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1135" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1135" s="2">
+        <v>70</v>
+      </c>
+      <c r="F1135" s="3">
+        <v>1770000</v>
+      </c>
+      <c r="G1135" s="3">
+        <v>1780000</v>
+      </c>
+      <c r="H1135" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I1135" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1135" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1135" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1135" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1135" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1136" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1136" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1136" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1136" s="2">
+        <v>124</v>
+      </c>
+      <c r="F1136" s="3">
+        <v>5570000</v>
+      </c>
+      <c r="G1136" s="3">
+        <v>5400000</v>
+      </c>
+      <c r="H1136" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I1136" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="J1136" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1136" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1136" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1136" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1137" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1137" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1137" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1137" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1137" s="2">
+        <v>143</v>
+      </c>
+      <c r="F1137" s="3">
+        <v>5690000</v>
+      </c>
+      <c r="G1137" s="3">
+        <v>5530000</v>
+      </c>
+      <c r="H1137" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I1137" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1137" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1137" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1137" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1137" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1138" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1138" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1138" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1138" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1138" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1138" s="3">
+        <v>4610000</v>
+      </c>
+      <c r="G1138" s="3">
+        <v>4540000</v>
+      </c>
+      <c r="H1138" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1138" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1138" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1138" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1138" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1138" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1139" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1139" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1139" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1139" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1139" s="2">
+        <v>83</v>
+      </c>
+      <c r="F1139" s="3">
+        <v>950000</v>
+      </c>
+      <c r="G1139" s="3">
+        <v>980000</v>
+      </c>
+      <c r="H1139" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1139" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1139" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1139" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1139" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1139" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1140" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1140" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1140" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1140" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1140" s="2">
+        <v>43</v>
+      </c>
+      <c r="F1140" s="3">
+        <v>2370000</v>
+      </c>
+      <c r="G1140" s="3">
+        <v>2400000</v>
+      </c>
+      <c r="H1140" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1140" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1140" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1140" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1140" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1140" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1141" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1141" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1141" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1141" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1141" s="2">
+        <v>42</v>
+      </c>
+      <c r="F1141" s="3">
+        <v>5230000</v>
+      </c>
+      <c r="G1141" s="3">
+        <v>5170000</v>
+      </c>
+      <c r="H1141" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1141" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1141" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1141" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1141" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1141" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1142" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1142" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1142" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1142" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1142" s="2">
+        <v>43</v>
+      </c>
+      <c r="F1142" s="3">
+        <v>4190000</v>
+      </c>
+      <c r="G1142" s="3">
+        <v>4170000</v>
+      </c>
+      <c r="H1142" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1142" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1142" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1142" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1142" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1142" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1143" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1143" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1143" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1143" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1143" s="2">
+        <v>60</v>
+      </c>
+      <c r="F1143" s="3">
+        <v>1250000</v>
+      </c>
+      <c r="G1143" s="3">
+        <v>1250000</v>
+      </c>
+      <c r="H1143" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1143" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1143" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1143" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1143" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1143" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1144" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1144" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1144" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1144" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1144" s="2">
+        <v>124</v>
+      </c>
+      <c r="F1144" s="3">
+        <v>3310000</v>
+      </c>
+      <c r="G1144" s="3">
+        <v>3290000</v>
+      </c>
+      <c r="H1144" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1144" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1144" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1144" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1144" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1144" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1145" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1145" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1145" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1145" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1145" s="2">
+        <v>112</v>
+      </c>
+      <c r="F1145" s="3">
+        <v>4390000</v>
+      </c>
+      <c r="G1145" s="3">
+        <v>4370000</v>
+      </c>
+      <c r="H1145" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I1145" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1145" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1145" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1145" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1146" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1146" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1146" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1146" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1146" s="2">
+        <v>108</v>
+      </c>
+      <c r="F1146" s="3">
+        <v>3850000</v>
+      </c>
+      <c r="G1146" s="3">
+        <v>3790000</v>
+      </c>
+      <c r="H1146" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="I1146" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1146" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1146" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1146" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1146" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1147" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1147" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1147" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1147" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1147" s="2">
+        <v>183</v>
+      </c>
+      <c r="F1147" s="3">
+        <v>9970000</v>
+      </c>
+      <c r="G1147" s="3">
+        <v>9880000</v>
+      </c>
+      <c r="H1147" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I1147" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1147" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1147" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1147" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1148" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1148" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1148" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1148" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1148" s="2">
+        <v>167</v>
+      </c>
+      <c r="F1148" s="3">
+        <v>9150000</v>
+      </c>
+      <c r="G1148" s="3">
+        <v>9100000</v>
+      </c>
+      <c r="H1148" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I1148" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1148" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1148" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1148" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1148" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1149" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1149" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1149" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1149" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1149" s="2">
+        <v>127</v>
+      </c>
+      <c r="F1149" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="G1149" s="3">
+        <v>3030000</v>
+      </c>
+      <c r="H1149" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I1149" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1149" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1149" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1149" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1149" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1150" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1150" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1150" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1150" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1150" s="2">
+        <v>69</v>
+      </c>
+      <c r="F1150" s="3">
+        <v>1750000</v>
+      </c>
+      <c r="G1150" s="3">
+        <v>1770000</v>
+      </c>
+      <c r="H1150" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1150" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1150" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1150" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1150" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1150" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1151" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1151" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1151" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1151" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1151" s="2">
+        <v>100</v>
+      </c>
+      <c r="F1151" s="3">
+        <v>2540000</v>
+      </c>
+      <c r="G1151" s="3">
+        <v>2480000</v>
+      </c>
+      <c r="H1151" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1151" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1151" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1151" s="2">
+        <v>2</v>
+      </c>
+      <c r="L1151" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1151" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1152" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1152" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1152" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1152" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1152" s="2">
+        <v>72</v>
+      </c>
+      <c r="F1152" s="3">
+        <v>1820000</v>
+      </c>
+      <c r="G1152" s="3">
+        <v>1810000</v>
+      </c>
+      <c r="H1152" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1152" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1152" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1152" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1152" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1152" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1153" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1153" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1153" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1153" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1153" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1153" s="3">
+        <v>2580000</v>
+      </c>
+      <c r="G1153" s="3">
+        <v>2590000</v>
+      </c>
+      <c r="H1153" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I1153" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1153" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1153" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1153" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1154" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1154" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1154" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1154" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1154" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1154" s="3">
+        <v>2150000</v>
+      </c>
+      <c r="G1154" s="3">
+        <v>2170000</v>
+      </c>
+      <c r="H1154" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1154" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1154" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1154" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1154" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1155" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1155" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1155" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1155" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1155" s="2">
+        <v>110</v>
+      </c>
+      <c r="F1155" s="3">
+        <v>3420000</v>
+      </c>
+      <c r="G1155" s="3">
+        <v>3410000</v>
+      </c>
+      <c r="H1155" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I1155" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1155" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1155" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1155" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1156" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1156" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1156" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1156" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1156" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1156" s="3">
+        <v>3610000</v>
+      </c>
+      <c r="G1156" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="H1156" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I1156" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1156" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1156" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1156" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1156" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1157" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1157" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1157" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1157" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1157" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1157" s="3">
+        <v>3110000</v>
+      </c>
+      <c r="G1157" s="3">
+        <v>3100000</v>
+      </c>
+      <c r="H1157" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I1157" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1157" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1157" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1157" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1157" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1158" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1158" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1158" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1158" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1158" s="2">
+        <v>95</v>
+      </c>
+      <c r="F1158" s="3">
+        <v>3560000</v>
+      </c>
+      <c r="G1158" s="3">
+        <v>3580000</v>
+      </c>
+      <c r="H1158" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I1158" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1158" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1158" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1158" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1158" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1159" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1159" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1159" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1159" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1159" s="2">
+        <v>71</v>
+      </c>
+      <c r="F1159" s="3">
+        <v>1440000</v>
+      </c>
+      <c r="G1159" s="3">
+        <v>1440000</v>
+      </c>
+      <c r="H1159" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I1159" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1159" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1159" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1159" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1159" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1160" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1160" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1160" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1160" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1160" s="2">
+        <v>127</v>
+      </c>
+      <c r="F1160" s="3">
+        <v>5380000</v>
+      </c>
+      <c r="G1160" s="3">
+        <v>5350000</v>
+      </c>
+      <c r="H1160" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1160" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1160" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1160" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1160" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1160" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1161" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1161" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1161" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1161" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1161" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1161" s="3">
+        <v>230000</v>
+      </c>
+      <c r="G1161" s="3">
+        <v>230000</v>
+      </c>
+      <c r="H1161" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1161" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1161" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1161" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1161" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1161" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1162" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1162" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1162" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1162" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1162" s="2">
+        <v>72</v>
+      </c>
+      <c r="F1162" s="3">
+        <v>3070000</v>
+      </c>
+      <c r="G1162" s="3">
+        <v>3070000</v>
+      </c>
+      <c r="H1162" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1162" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1162" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1162" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1162" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1162" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1163" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1163" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1163" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1163" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1163" s="2">
+        <v>36</v>
+      </c>
+      <c r="F1163" s="3">
+        <v>3020000</v>
+      </c>
+      <c r="G1163" s="3">
+        <v>3060000</v>
+      </c>
+      <c r="H1163" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1163" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1163" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1163" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1163" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1163" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1164" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1164" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1164" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1164" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1164" s="2">
+        <v>184</v>
+      </c>
+      <c r="F1164" s="3">
+        <v>15550000</v>
+      </c>
+      <c r="G1164" s="3">
+        <v>15660000</v>
+      </c>
+      <c r="H1164" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I1164" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1164" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1164" s="2">
+        <v>2</v>
+      </c>
+      <c r="L1164" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1164" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1165" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1165" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1165" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1165" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1165" s="2">
+        <v>87</v>
+      </c>
+      <c r="F1165" s="3">
+        <v>2550000</v>
+      </c>
+      <c r="G1165" s="3">
+        <v>2540000</v>
+      </c>
+      <c r="H1165" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I1165" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1165" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1165" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1165" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1165" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1166" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1166" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1166" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1166" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1166" s="2">
+        <v>95</v>
+      </c>
+      <c r="F1166" s="3">
+        <v>6890000</v>
+      </c>
+      <c r="G1166" s="3">
+        <v>6960000</v>
+      </c>
+      <c r="H1166" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I1166" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1166" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1166" s="2">
+        <v>2</v>
+      </c>
+      <c r="L1166" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1166" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1167" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1167" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1167" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1167" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1167" s="2">
+        <v>123</v>
+      </c>
+      <c r="F1167" s="3">
+        <v>3560000</v>
+      </c>
+      <c r="G1167" s="3">
+        <v>3630000</v>
+      </c>
+      <c r="H1167" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1167" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1167" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1167" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1167" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1167" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1168" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1168" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1168" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1168" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1168" s="2">
+        <v>89</v>
+      </c>
+      <c r="F1168" s="3">
+        <v>1750000</v>
+      </c>
+      <c r="G1168" s="3">
+        <v>1770000</v>
+      </c>
+      <c r="H1168" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I1168" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1168" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1168" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1168" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1168" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1169" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1169" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1169" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1169" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1169" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1169" s="3">
+        <v>210000</v>
+      </c>
+      <c r="G1169" s="3">
+        <v>210000</v>
+      </c>
+      <c r="H1169" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1169" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1169" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1169" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1169" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1169" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1170" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1170" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1170" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1170" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1170" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1170" s="3">
+        <v>2200000</v>
+      </c>
+      <c r="G1170" s="3">
+        <v>2210000</v>
+      </c>
+      <c r="H1170" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I1170" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1170" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1170" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1170" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1170" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1171" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1171" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1171" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1171" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1171" s="2">
+        <v>100</v>
+      </c>
+      <c r="F1171" s="3">
+        <v>4650000</v>
+      </c>
+      <c r="G1171" s="3">
+        <v>4690000</v>
+      </c>
+      <c r="H1171" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I1171" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1171" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1171" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1171" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1171" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1172" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1172" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1172" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1172" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1172" s="2">
+        <v>199</v>
+      </c>
+      <c r="F1172" s="3">
+        <v>18620000</v>
+      </c>
+      <c r="G1172" s="3">
+        <v>18700000</v>
+      </c>
+      <c r="H1172" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I1172" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1172" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1172" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1172" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1172" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1173" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1173" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1173" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1173" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1173" s="2">
+        <v>179</v>
+      </c>
+      <c r="F1173" s="3">
+        <v>11630000</v>
+      </c>
+      <c r="G1173" s="3">
+        <v>11600000</v>
+      </c>
+      <c r="H1173" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1173" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1173" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1173" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1173" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1173" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1174" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1174" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C1174" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1174" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1174" s="2">
+        <v>7</v>
+      </c>
+      <c r="F1174" s="3">
+        <v>320000</v>
+      </c>
+      <c r="G1174" s="3">
+        <v>320000</v>
+      </c>
+      <c r="H1174" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I1174" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1174" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1174" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1174" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1174" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1175" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1175" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1175" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1175" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1175" s="2">
+        <v>46</v>
+      </c>
+      <c r="F1175" s="3">
+        <v>1320000</v>
+      </c>
+      <c r="G1175" s="3">
+        <v>1330000</v>
+      </c>
+      <c r="H1175" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I1175" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1175" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1175" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1175" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1175" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1176" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1176" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1176" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1176" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1176" s="2">
+        <v>185</v>
+      </c>
+      <c r="F1176" s="3">
+        <v>12160000</v>
+      </c>
+      <c r="G1176" s="3">
+        <v>12220000</v>
+      </c>
+      <c r="H1176" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I1176" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1176" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1176" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1176" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1176" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1177" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1177" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1177" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1177" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1177" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1177" s="3">
+        <v>4060000</v>
+      </c>
+      <c r="G1177" s="3">
+        <v>4050000</v>
+      </c>
+      <c r="H1177" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1177" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1177" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1177" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1177" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1177" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1178" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1178" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1178" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1178" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1178" s="2">
+        <v>51</v>
+      </c>
+      <c r="F1178" s="3">
+        <v>2570000</v>
+      </c>
+      <c r="G1178" s="3">
+        <v>2630000</v>
+      </c>
+      <c r="H1178" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I1178" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1178" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1178" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1178" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1178" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1179" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1179" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1179" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1179" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1179" s="2">
+        <v>119</v>
+      </c>
+      <c r="F1179" s="3">
+        <v>5930000</v>
+      </c>
+      <c r="G1179" s="3">
+        <v>5940000</v>
+      </c>
+      <c r="H1179" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1179" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1179" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1179" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1179" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1179" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1180" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1180" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1180" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1180" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1180" s="2">
+        <v>127</v>
+      </c>
+      <c r="F1180" s="3">
+        <v>6290000</v>
+      </c>
+      <c r="G1180" s="3">
+        <v>6170000</v>
+      </c>
+      <c r="H1180" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I1180" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1180" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1180" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1180" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1180" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1181" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1181" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1181" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1181" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1181" s="2">
+        <v>69</v>
+      </c>
+      <c r="F1181" s="3">
+        <v>4700000</v>
+      </c>
+      <c r="G1181" s="3">
+        <v>4770000</v>
+      </c>
+      <c r="H1181" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I1181" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1181" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1181" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1181" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1181" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1182" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1182" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1182" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1182" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1182" s="2">
+        <v>68</v>
+      </c>
+      <c r="F1182" s="3">
+        <v>4220000</v>
+      </c>
+      <c r="G1182" s="3">
+        <v>4250000</v>
+      </c>
+      <c r="H1182" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1182" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1182" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1182" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1182" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1182" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1183" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1183" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1183" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1183" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1183" s="2">
+        <v>81</v>
+      </c>
+      <c r="F1183" s="3">
+        <v>1520000</v>
+      </c>
+      <c r="G1183" s="3">
+        <v>1510000</v>
+      </c>
+      <c r="H1183" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1183" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1183" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1183" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1183" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1183" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1184" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1184" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1184" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1184" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1184" s="2">
+        <v>123</v>
+      </c>
+      <c r="F1184" s="3">
+        <v>5020000</v>
+      </c>
+      <c r="G1184" s="3">
+        <v>4990000</v>
+      </c>
+      <c r="H1184" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1184" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1184" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1184" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1184" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1184" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1185" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1185" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1185" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1185" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1185" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1185" s="3">
+        <v>4720000</v>
+      </c>
+      <c r="G1185" s="3">
+        <v>4680000</v>
+      </c>
+      <c r="H1185" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1185" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1185" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1185" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1185" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1185" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1186" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1186" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1186" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1186" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1186" s="2">
+        <v>109</v>
+      </c>
+      <c r="F1186" s="3">
+        <v>3540000</v>
+      </c>
+      <c r="G1186" s="3">
+        <v>3580000</v>
+      </c>
+      <c r="H1186" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I1186" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1186" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1186" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1186" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1186" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1187" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1187" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1187" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1187" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1187" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1187" s="3">
+        <v>160000</v>
+      </c>
+      <c r="G1187" s="3">
+        <v>160000</v>
+      </c>
+      <c r="H1187" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I1187" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1187" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1187" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1187" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1187" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1188" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1188" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1188" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1188" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1188" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1188" s="3">
+        <v>1940000</v>
+      </c>
+      <c r="G1188" s="3">
+        <v>1940000</v>
+      </c>
+      <c r="H1188" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I1188" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1188" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1188" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1188" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1188" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1189" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1189" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1189" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1189" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1189" s="2">
+        <v>12</v>
+      </c>
+      <c r="F1189" s="3">
+        <v>710000</v>
+      </c>
+      <c r="G1189" s="3">
+        <v>690000</v>
+      </c>
+      <c r="H1189" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1189" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1189" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1189" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1189" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1189" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1190" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1190" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1190" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1190" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1190" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1190" s="3">
+        <v>9870000</v>
+      </c>
+      <c r="G1190" s="3">
+        <v>10270000</v>
+      </c>
+      <c r="H1190" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1190" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1190" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1190" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1190" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1190" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1191" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1191" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1191" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1191" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1191" s="2">
+        <v>118</v>
+      </c>
+      <c r="F1191" s="3">
+        <v>6350000</v>
+      </c>
+      <c r="G1191" s="3">
+        <v>6230000</v>
+      </c>
+      <c r="H1191" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1191" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1191" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1191" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1191" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1191" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1192" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1192" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1192" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1192" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1192" s="2">
+        <v>30</v>
+      </c>
+      <c r="F1192" s="3">
+        <v>2480000</v>
+      </c>
+      <c r="G1192" s="3">
+        <v>2620000</v>
+      </c>
+      <c r="H1192" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1192" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1192" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1192" s="2">
+        <v>5</v>
+      </c>
+      <c r="L1192" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1192" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1193" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1193" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1193" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1193" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1193" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1193" s="3">
+        <v>160000</v>
+      </c>
+      <c r="G1193" s="3">
+        <v>160000</v>
+      </c>
+      <c r="H1193" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1193" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1193" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1193" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1193" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1193" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1194" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1194" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1194" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1194" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1194" s="2">
+        <v>54</v>
+      </c>
+      <c r="F1194" s="3">
+        <v>2300000</v>
+      </c>
+      <c r="G1194" s="3">
+        <v>2290000</v>
+      </c>
+      <c r="H1194" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1194" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1194" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1194" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1194" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1194" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1195" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1195" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1195" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1195" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1195" s="2">
+        <v>89</v>
+      </c>
+      <c r="F1195" s="3">
+        <v>8240000</v>
+      </c>
+      <c r="G1195" s="3">
+        <v>8240000</v>
+      </c>
+      <c r="H1195" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I1195" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1195" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1195" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1195" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1195" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1196" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1196" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1196" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1196" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1196" s="2">
+        <v>130</v>
+      </c>
+      <c r="F1196" s="3">
+        <v>11820000</v>
+      </c>
+      <c r="G1196" s="3">
+        <v>11950000</v>
+      </c>
+      <c r="H1196" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I1196" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1196" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1196" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1196" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1196" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1197" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1197" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1197" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1197" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1197" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1197" s="3">
+        <v>1890000</v>
+      </c>
+      <c r="G1197" s="3">
+        <v>1880000</v>
+      </c>
+      <c r="H1197" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1197" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1197" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1197" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1197" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1197" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1198" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1198" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1198" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1198" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1198" s="2">
+        <v>41</v>
+      </c>
+      <c r="F1198" s="3">
+        <v>1110000</v>
+      </c>
+      <c r="G1198" s="3">
+        <v>1090000</v>
+      </c>
+      <c r="H1198" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I1198" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1198" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1198" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1198" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1198" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1199" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1199" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1199" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1199" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1199" s="2">
+        <v>91</v>
+      </c>
+      <c r="F1199" s="3">
+        <v>7920000</v>
+      </c>
+      <c r="G1199" s="3">
+        <v>7980000</v>
+      </c>
+      <c r="H1199" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="I1199" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1199" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1199" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1199" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1199" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1200" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1200" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1200" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1200" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1200" s="2">
+        <v>30</v>
+      </c>
+      <c r="F1200" s="3">
+        <v>870000</v>
+      </c>
+      <c r="G1200" s="3">
+        <v>860000</v>
+      </c>
+      <c r="H1200" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1200" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1200" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1200" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1200" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1200" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1201" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1201" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1201" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1201" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1201" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1201" s="3">
+        <v>270000</v>
+      </c>
+      <c r="G1201" s="3">
+        <v>270000</v>
+      </c>
+      <c r="H1201" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1201" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1201" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1201" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1201" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1201" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1202" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1202" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1202" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1202" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1202" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1202" s="3">
+        <v>160000</v>
+      </c>
+      <c r="G1202" s="3">
+        <v>160000</v>
+      </c>
+      <c r="H1202" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1202" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1202" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1202" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1202" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1202" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1203" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1203" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1203" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1203" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1203" s="2">
+        <v>108</v>
+      </c>
+      <c r="F1203" s="3">
+        <v>3210000</v>
+      </c>
+      <c r="G1203" s="3">
+        <v>3160000</v>
+      </c>
+      <c r="H1203" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1203" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1203" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1203" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1203" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1203" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1204" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1204" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1204" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1204" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1204" s="2">
+        <v>112</v>
+      </c>
+      <c r="F1204" s="3">
+        <v>4070000</v>
+      </c>
+      <c r="G1204" s="3">
+        <v>4030000</v>
+      </c>
+      <c r="H1204" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1204" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1204" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1204" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1204" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1204" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1205" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1205" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1205" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1205" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1205" s="2">
+        <v>90</v>
+      </c>
+      <c r="F1205" s="3">
+        <v>3580000</v>
+      </c>
+      <c r="G1205" s="3">
+        <v>3590000</v>
+      </c>
+      <c r="H1205" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I1205" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1205" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1205" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1205" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1205" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1206" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1206" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1206" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1206" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1206" s="2">
+        <v>15</v>
+      </c>
+      <c r="F1206" s="3">
+        <v>370000</v>
+      </c>
+      <c r="G1206" s="3">
+        <v>380000</v>
+      </c>
+      <c r="H1206" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1206" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1206" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1206" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1206" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1206" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1207" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1207" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1207" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1207" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1207" s="2">
+        <v>58</v>
+      </c>
+      <c r="F1207" s="3">
+        <v>1210000</v>
+      </c>
+      <c r="G1207" s="3">
+        <v>1220000</v>
+      </c>
+      <c r="H1207" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1207" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1207" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1207" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1207" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1207" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1208" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1208" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1208" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1208" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1208" s="2">
+        <v>48</v>
+      </c>
+      <c r="F1208" s="3">
+        <v>1530000</v>
+      </c>
+      <c r="G1208" s="3">
+        <v>1540000</v>
+      </c>
+      <c r="H1208" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I1208" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1208" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1208" s="2">
+        <v>5</v>
+      </c>
+      <c r="L1208" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1208" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1209" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1209" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1209" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1209" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1209" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1209" s="3">
+        <v>4310000</v>
+      </c>
+      <c r="G1209" s="3">
+        <v>4360000</v>
+      </c>
+      <c r="H1209" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1209" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1209" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1209" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1209" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1209" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1210" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1210" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1210" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1210" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1210" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1210" s="3">
+        <v>390000</v>
+      </c>
+      <c r="G1210" s="3">
+        <v>390000</v>
+      </c>
+      <c r="H1210" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1210" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1210" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1210" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1210" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1210" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1211" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1211" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1211" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1211" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1211" s="2">
+        <v>47</v>
+      </c>
+      <c r="F1211" s="3">
+        <v>1290000</v>
+      </c>
+      <c r="G1211" s="3">
+        <v>1290000</v>
+      </c>
+      <c r="H1211" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1211" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1211" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1211" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1211" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1211" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1212" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1212" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1212" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1212" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1212" s="2">
+        <v>156</v>
+      </c>
+      <c r="F1212" s="3">
+        <v>6470000</v>
+      </c>
+      <c r="G1212" s="3">
+        <v>6350000</v>
+      </c>
+      <c r="H1212" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I1212" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1212" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1212" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1212" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1212" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1213" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1213" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1213" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1213" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1213" s="2">
+        <v>29</v>
+      </c>
+      <c r="F1213" s="3">
+        <v>790000</v>
+      </c>
+      <c r="G1213" s="3">
+        <v>800000</v>
+      </c>
+      <c r="H1213" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1213" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1213" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1213" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1213" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1213" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1214" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1214" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1214" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1214" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1214" s="2">
+        <v>102</v>
+      </c>
+      <c r="F1214" s="3">
+        <v>2990000</v>
+      </c>
+      <c r="G1214" s="3">
+        <v>2940000</v>
+      </c>
+      <c r="H1214" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I1214" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1214" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1214" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1214" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1214" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1215" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1215" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1215" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1215" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1215" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1215" s="3">
+        <v>2870000</v>
+      </c>
+      <c r="G1215" s="3">
+        <v>2850000</v>
+      </c>
+      <c r="H1215" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I1215" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1215" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1215" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1215" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1215" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1216" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1216" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1216" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1216" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1216" s="2">
+        <v>17</v>
+      </c>
+      <c r="F1216" s="3">
+        <v>1350000</v>
+      </c>
+      <c r="G1216" s="3">
+        <v>1350000</v>
+      </c>
+      <c r="H1216" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1216" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1216" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1216" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1216" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1216" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1217" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1217" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1217" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1217" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1217" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1217" s="3">
+        <v>160000</v>
+      </c>
+      <c r="G1217" s="3">
+        <v>160000</v>
+      </c>
+      <c r="H1217" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1217" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1217" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1217" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1217" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1217" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1218" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1218" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1218" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1218" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1218" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1218" s="3">
+        <v>420000</v>
+      </c>
+      <c r="G1218" s="3">
+        <v>430000</v>
+      </c>
+      <c r="H1218" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1218" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1218" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1218" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1218" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1218" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1219" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1219" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1219" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1219" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1219" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1219" s="3">
+        <v>3450000</v>
+      </c>
+      <c r="G1219" s="3">
+        <v>3410000</v>
+      </c>
+      <c r="H1219" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1219" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1219" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1219" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1219" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1219" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="1220" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1220" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1220" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1220" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1220" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1220" s="3">
+        <v>180000</v>
+      </c>
+      <c r="G1220" s="3">
+        <v>180000</v>
+      </c>
+      <c r="H1220" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1220" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1220" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1220" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1220" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1220" s="7" t="s">
+        <v>301</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:M1" xr:uid="{93EB6F54-7766-4759-97DF-03549A275A7C}">

--- a/TM_all.xlsx
+++ b/TM_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aecf56309e6168f4/Documents/comunio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="239" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2CB34A4-E516-4A1A-8BA5-8CA4166C45EF}"/>
+  <xr:revisionPtr revIDLastSave="244" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E3F379B-9358-4168-BFDA-3998CC4AE001}"/>
   <bookViews>
-    <workbookView xWindow="6660" yWindow="2700" windowWidth="28800" windowHeight="15370" xr2:uid="{607DE709-F91E-4262-9941-1066BBEC319E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{607DE709-F91E-4262-9941-1066BBEC319E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8675" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9443" uniqueCount="309">
   <si>
     <t>Spieler</t>
   </si>
@@ -946,6 +946,27 @@
   <si>
     <t>14.06.2025</t>
   </si>
+  <si>
+    <t>Heintz</t>
+  </si>
+  <si>
+    <t>Ritzka</t>
+  </si>
+  <si>
+    <t>Kaufmann</t>
+  </si>
+  <si>
+    <t>Kim</t>
+  </si>
+  <si>
+    <t>Heitmann</t>
+  </si>
+  <si>
+    <t>Telle</t>
+  </si>
+  <si>
+    <t>15.06.2025</t>
+  </si>
 </sst>
 </file>
 
@@ -1369,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93EB6F54-7766-4759-97DF-03549A275A7C}">
-  <dimension ref="A1:M1220"/>
+  <dimension ref="A1:M1316"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="2"/>
@@ -47335,6 +47356,3654 @@
       </c>
       <c r="M1220" s="7" t="s">
         <v>301</v>
+      </c>
+    </row>
+    <row r="1221" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1221" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1221" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1221" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1221" s="2">
+        <v>70</v>
+      </c>
+      <c r="F1221" s="3">
+        <v>1980000</v>
+      </c>
+      <c r="G1221" s="3">
+        <v>1960000</v>
+      </c>
+      <c r="H1221" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I1221" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1221" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1221" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1221" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1221" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1222" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1222" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1222" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1222" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1222" s="2">
+        <v>124</v>
+      </c>
+      <c r="F1222" s="3">
+        <v>5600000</v>
+      </c>
+      <c r="G1222" s="3">
+        <v>5480000</v>
+      </c>
+      <c r="H1222" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I1222" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1222" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1222" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1222" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1222" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1223" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1223" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1223" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1223" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1223" s="2">
+        <v>95</v>
+      </c>
+      <c r="F1223" s="3">
+        <v>3780000</v>
+      </c>
+      <c r="G1223" s="3">
+        <v>3930000</v>
+      </c>
+      <c r="H1223" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1223" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1223" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1223" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1223" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1223" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1224" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1224" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1224" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1224" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1224" s="2">
+        <v>143</v>
+      </c>
+      <c r="F1224" s="3">
+        <v>5610000</v>
+      </c>
+      <c r="G1224" s="3">
+        <v>5430000</v>
+      </c>
+      <c r="H1224" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I1224" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="J1224" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1224" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1224" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1224" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1225" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1225" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1225" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1225" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1225" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1225" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="G1225" s="3">
+        <v>1660000</v>
+      </c>
+      <c r="H1225" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I1225" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1225" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1225" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1225" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1225" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1226" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1226" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1226" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1226" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1226" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1226" s="3">
+        <v>4670000</v>
+      </c>
+      <c r="G1226" s="3">
+        <v>4680000</v>
+      </c>
+      <c r="H1226" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1226" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1226" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1226" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1226" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1226" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1227" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1227" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1227" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1227" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1227" s="2">
+        <v>83</v>
+      </c>
+      <c r="F1227" s="3">
+        <v>980000</v>
+      </c>
+      <c r="G1227" s="3">
+        <v>980000</v>
+      </c>
+      <c r="H1227" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1227" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1227" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1227" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1227" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1227" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1228" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1228" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1228" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1228" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1228" s="2">
+        <v>43</v>
+      </c>
+      <c r="F1228" s="3">
+        <v>2460000</v>
+      </c>
+      <c r="G1228" s="3">
+        <v>2450000</v>
+      </c>
+      <c r="H1228" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1228" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1228" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1228" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1228" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1228" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1229" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1229" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1229" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1229" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1229" s="2">
+        <v>42</v>
+      </c>
+      <c r="F1229" s="3">
+        <v>5300000</v>
+      </c>
+      <c r="G1229" s="3">
+        <v>5240000</v>
+      </c>
+      <c r="H1229" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1229" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1229" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1229" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1229" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1229" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1230" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1230" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1230" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1230" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1230" s="2">
+        <v>43</v>
+      </c>
+      <c r="F1230" s="3">
+        <v>3930000</v>
+      </c>
+      <c r="G1230" s="3">
+        <v>3940000</v>
+      </c>
+      <c r="H1230" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1230" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1230" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1230" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1230" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1230" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1231" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1231" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1231" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1231" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1231" s="2">
+        <v>60</v>
+      </c>
+      <c r="F1231" s="3">
+        <v>1290000</v>
+      </c>
+      <c r="G1231" s="3">
+        <v>1280000</v>
+      </c>
+      <c r="H1231" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1231" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1231" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1231" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1231" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1231" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1232" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1232" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1232" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1232" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1232" s="2">
+        <v>124</v>
+      </c>
+      <c r="F1232" s="3">
+        <v>3360000</v>
+      </c>
+      <c r="G1232" s="3">
+        <v>3290000</v>
+      </c>
+      <c r="H1232" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1232" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1232" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1232" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1232" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1232" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1233" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1233" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1233" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1233" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1233" s="2">
+        <v>178</v>
+      </c>
+      <c r="F1233" s="3">
+        <v>13520000</v>
+      </c>
+      <c r="G1233" s="3">
+        <v>13650000</v>
+      </c>
+      <c r="H1233" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I1233" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1233" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1233" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1233" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1233" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1234" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1234" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1234" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1234" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1234" s="2">
+        <v>112</v>
+      </c>
+      <c r="F1234" s="3">
+        <v>4470000</v>
+      </c>
+      <c r="G1234" s="3">
+        <v>4440000</v>
+      </c>
+      <c r="H1234" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I1234" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1234" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1234" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1234" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1234" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1235" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1235" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1235" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1235" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1235" s="2">
+        <v>108</v>
+      </c>
+      <c r="F1235" s="3">
+        <v>3880000</v>
+      </c>
+      <c r="G1235" s="3">
+        <v>3830000</v>
+      </c>
+      <c r="H1235" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="I1235" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1235" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1235" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1235" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1235" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1236" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1236" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1236" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1236" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1236" s="2">
+        <v>183</v>
+      </c>
+      <c r="F1236" s="3">
+        <v>10010000</v>
+      </c>
+      <c r="G1236" s="3">
+        <v>9990000</v>
+      </c>
+      <c r="H1236" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I1236" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1236" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1236" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1236" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1236" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1237" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1237" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1237" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1237" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1237" s="2">
+        <v>167</v>
+      </c>
+      <c r="F1237" s="3">
+        <v>9300000</v>
+      </c>
+      <c r="G1237" s="3">
+        <v>9150000</v>
+      </c>
+      <c r="H1237" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I1237" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1237" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1237" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1237" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1237" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1238" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1238" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1238" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1238" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1238" s="2">
+        <v>127</v>
+      </c>
+      <c r="F1238" s="3">
+        <v>3070000</v>
+      </c>
+      <c r="G1238" s="3">
+        <v>2980000</v>
+      </c>
+      <c r="H1238" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I1238" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1238" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1238" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1238" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1238" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1239" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1239" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1239" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1239" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1239" s="2">
+        <v>69</v>
+      </c>
+      <c r="F1239" s="3">
+        <v>1770000</v>
+      </c>
+      <c r="G1239" s="3">
+        <v>1780000</v>
+      </c>
+      <c r="H1239" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1239" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1239" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1239" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1239" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1239" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1240" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1240" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1240" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1240" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1240" s="2">
+        <v>100</v>
+      </c>
+      <c r="F1240" s="3">
+        <v>2580000</v>
+      </c>
+      <c r="G1240" s="3">
+        <v>2560000</v>
+      </c>
+      <c r="H1240" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1240" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1240" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1240" s="2">
+        <v>2</v>
+      </c>
+      <c r="L1240" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1240" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1241" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1241" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1241" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1241" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1241" s="2">
+        <v>72</v>
+      </c>
+      <c r="F1241" s="3">
+        <v>1840000</v>
+      </c>
+      <c r="G1241" s="3">
+        <v>1840000</v>
+      </c>
+      <c r="H1241" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1241" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1241" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1241" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1241" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1241" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1242" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1242" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1242" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1242" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1242" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1242" s="3">
+        <v>2510000</v>
+      </c>
+      <c r="G1242" s="3">
+        <v>2570000</v>
+      </c>
+      <c r="H1242" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I1242" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1242" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1242" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1242" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1242" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1243" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1243" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1243" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1243" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1243" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1243" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="G1243" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="H1243" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1243" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1243" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1243" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1243" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1243" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1244" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1244" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1244" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1244" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1244" s="2">
+        <v>110</v>
+      </c>
+      <c r="F1244" s="3">
+        <v>3390000</v>
+      </c>
+      <c r="G1244" s="3">
+        <v>3340000</v>
+      </c>
+      <c r="H1244" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I1244" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1244" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1244" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1244" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1244" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1245" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1245" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1245" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1245" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1245" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1245" s="3">
+        <v>3510000</v>
+      </c>
+      <c r="G1245" s="3">
+        <v>3510000</v>
+      </c>
+      <c r="H1245" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I1245" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1245" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1245" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1245" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1245" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1246" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1246" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1246" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1246" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1246" s="2">
+        <v>59</v>
+      </c>
+      <c r="F1246" s="3">
+        <v>850000</v>
+      </c>
+      <c r="G1246" s="3">
+        <v>850000</v>
+      </c>
+      <c r="H1246" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1246" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1246" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1246" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1246" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1246" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1247" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1247" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1247" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1247" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1247" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1247" s="3">
+        <v>3030000</v>
+      </c>
+      <c r="G1247" s="3">
+        <v>2980000</v>
+      </c>
+      <c r="H1247" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I1247" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1247" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1247" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1247" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1247" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1248" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1248" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1248" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1248" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1248" s="2">
+        <v>95</v>
+      </c>
+      <c r="F1248" s="3">
+        <v>3490000</v>
+      </c>
+      <c r="G1248" s="3">
+        <v>3470000</v>
+      </c>
+      <c r="H1248" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I1248" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1248" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1248" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1248" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1248" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1249" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1249" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1249" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1249" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1249" s="2">
+        <v>71</v>
+      </c>
+      <c r="F1249" s="3">
+        <v>1540000</v>
+      </c>
+      <c r="G1249" s="3">
+        <v>1550000</v>
+      </c>
+      <c r="H1249" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I1249" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1249" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1249" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1249" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1249" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1250" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1250" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1250" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1250" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1250" s="2">
+        <v>127</v>
+      </c>
+      <c r="F1250" s="3">
+        <v>5460000</v>
+      </c>
+      <c r="G1250" s="3">
+        <v>5360000</v>
+      </c>
+      <c r="H1250" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1250" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1250" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1250" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1250" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1250" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1251" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1251" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1251" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1251" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1251" s="2">
+        <v>55</v>
+      </c>
+      <c r="F1251" s="3">
+        <v>630000</v>
+      </c>
+      <c r="G1251" s="3">
+        <v>640000</v>
+      </c>
+      <c r="H1251" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1251" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1251" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1251" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1251" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1251" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1252" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1252" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1252" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1252" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1252" s="2">
+        <v>8</v>
+      </c>
+      <c r="F1252" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G1252" s="3">
+        <v>220000</v>
+      </c>
+      <c r="H1252" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1252" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1252" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1252" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1252" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1252" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1253" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1253" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1253" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1253" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1253" s="2">
+        <v>72</v>
+      </c>
+      <c r="F1253" s="3">
+        <v>2900000</v>
+      </c>
+      <c r="G1253" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="H1253" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1253" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1253" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1253" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1253" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1253" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1254" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1254" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1254" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1254" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1254" s="2">
+        <v>36</v>
+      </c>
+      <c r="F1254" s="3">
+        <v>3190000</v>
+      </c>
+      <c r="G1254" s="3">
+        <v>3230000</v>
+      </c>
+      <c r="H1254" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1254" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1254" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1254" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1254" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1254" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1255" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1255" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1255" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1255" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1255" s="2">
+        <v>184</v>
+      </c>
+      <c r="F1255" s="3">
+        <v>15550000</v>
+      </c>
+      <c r="G1255" s="3">
+        <v>15560000</v>
+      </c>
+      <c r="H1255" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I1255" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1255" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1255" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1255" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1255" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1256" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1256" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1256" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1256" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1256" s="2">
+        <v>87</v>
+      </c>
+      <c r="F1256" s="3">
+        <v>2650000</v>
+      </c>
+      <c r="G1256" s="3">
+        <v>2650000</v>
+      </c>
+      <c r="H1256" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I1256" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1256" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1256" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1256" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1256" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1257" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1257" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1257" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1257" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1257" s="2">
+        <v>95</v>
+      </c>
+      <c r="F1257" s="3">
+        <v>7190000</v>
+      </c>
+      <c r="G1257" s="3">
+        <v>7200000</v>
+      </c>
+      <c r="H1257" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I1257" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1257" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1257" s="2">
+        <v>2</v>
+      </c>
+      <c r="L1257" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1257" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1258" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1258" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1258" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1258" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1258" s="2">
+        <v>123</v>
+      </c>
+      <c r="F1258" s="3">
+        <v>3840000</v>
+      </c>
+      <c r="G1258" s="3">
+        <v>3880000</v>
+      </c>
+      <c r="H1258" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1258" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1258" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1258" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1258" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1258" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1259" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1259" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1259" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1259" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1259" s="2">
+        <v>89</v>
+      </c>
+      <c r="F1259" s="3">
+        <v>1650000</v>
+      </c>
+      <c r="G1259" s="3">
+        <v>1660000</v>
+      </c>
+      <c r="H1259" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I1259" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1259" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1259" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1259" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1259" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1260" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1260" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1260" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1260" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1260" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1260" s="3">
+        <v>200000</v>
+      </c>
+      <c r="G1260" s="3">
+        <v>200000</v>
+      </c>
+      <c r="H1260" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1260" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1260" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1260" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1260" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1260" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1261" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1261" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1261" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1261" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1261" s="2">
+        <v>100</v>
+      </c>
+      <c r="F1261" s="3">
+        <v>4790000</v>
+      </c>
+      <c r="G1261" s="3">
+        <v>4850000</v>
+      </c>
+      <c r="H1261" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I1261" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1261" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1261" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1261" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1261" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1262" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1262" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1262" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1262" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1262" s="2">
+        <v>199</v>
+      </c>
+      <c r="F1262" s="3">
+        <v>18860000</v>
+      </c>
+      <c r="G1262" s="3">
+        <v>19090000</v>
+      </c>
+      <c r="H1262" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I1262" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1262" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1262" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1262" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1262" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1263" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1263" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1263" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1263" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1263" s="2">
+        <v>179</v>
+      </c>
+      <c r="F1263" s="3">
+        <v>11600000</v>
+      </c>
+      <c r="G1263" s="3">
+        <v>11650000</v>
+      </c>
+      <c r="H1263" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1263" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1263" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1263" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1263" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1263" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1264" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1264" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1264" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1264" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1264" s="2">
+        <v>46</v>
+      </c>
+      <c r="F1264" s="3">
+        <v>1330000</v>
+      </c>
+      <c r="G1264" s="3">
+        <v>1320000</v>
+      </c>
+      <c r="H1264" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I1264" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1264" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1264" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1264" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1264" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1265" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1265" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1265" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1265" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1265" s="2">
+        <v>185</v>
+      </c>
+      <c r="F1265" s="3">
+        <v>12120000</v>
+      </c>
+      <c r="G1265" s="3">
+        <v>12080000</v>
+      </c>
+      <c r="H1265" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I1265" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1265" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1265" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1265" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1265" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1266" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1266" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1266" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1266" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1266" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1266" s="3">
+        <v>4130000</v>
+      </c>
+      <c r="G1266" s="3">
+        <v>4180000</v>
+      </c>
+      <c r="H1266" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1266" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1266" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1266" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1266" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1266" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1267" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1267" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1267" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1267" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1267" s="2">
+        <v>51</v>
+      </c>
+      <c r="F1267" s="3">
+        <v>2540000</v>
+      </c>
+      <c r="G1267" s="3">
+        <v>2570000</v>
+      </c>
+      <c r="H1267" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I1267" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1267" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1267" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1267" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1267" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1268" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1268" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1268" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1268" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1268" s="2">
+        <v>119</v>
+      </c>
+      <c r="F1268" s="3">
+        <v>5810000</v>
+      </c>
+      <c r="G1268" s="3">
+        <v>5790000</v>
+      </c>
+      <c r="H1268" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1268" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1268" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1268" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1268" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1268" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1269" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1269" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1269" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1269" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1269" s="2">
+        <v>127</v>
+      </c>
+      <c r="F1269" s="3">
+        <v>6520000</v>
+      </c>
+      <c r="G1269" s="3">
+        <v>6400000</v>
+      </c>
+      <c r="H1269" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I1269" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1269" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1269" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1269" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1269" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1270" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1270" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1270" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1270" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1270" s="2">
+        <v>69</v>
+      </c>
+      <c r="F1270" s="3">
+        <v>4890000</v>
+      </c>
+      <c r="G1270" s="3">
+        <v>4880000</v>
+      </c>
+      <c r="H1270" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I1270" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1270" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1270" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1270" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1270" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1271" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1271" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1271" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1271" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1271" s="2">
+        <v>68</v>
+      </c>
+      <c r="F1271" s="3">
+        <v>4330000</v>
+      </c>
+      <c r="G1271" s="3">
+        <v>4360000</v>
+      </c>
+      <c r="H1271" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1271" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1271" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1271" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1271" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1271" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1272" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1272" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1272" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1272" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1272" s="2">
+        <v>81</v>
+      </c>
+      <c r="F1272" s="3">
+        <v>1600000</v>
+      </c>
+      <c r="G1272" s="3">
+        <v>1610000</v>
+      </c>
+      <c r="H1272" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1272" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1272" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1272" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1272" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1272" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1273" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1273" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1273" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1273" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1273" s="2">
+        <v>123</v>
+      </c>
+      <c r="F1273" s="3">
+        <v>5280000</v>
+      </c>
+      <c r="G1273" s="3">
+        <v>5220000</v>
+      </c>
+      <c r="H1273" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1273" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1273" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1273" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1273" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1273" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1274" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1274" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1274" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1274" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1274" s="2">
+        <v>128</v>
+      </c>
+      <c r="F1274" s="3">
+        <v>4760000</v>
+      </c>
+      <c r="G1274" s="3">
+        <v>4780000</v>
+      </c>
+      <c r="H1274" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1274" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1274" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1274" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1274" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1274" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1275" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1275" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1275" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1275" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1275" s="2">
+        <v>109</v>
+      </c>
+      <c r="F1275" s="3">
+        <v>3700000</v>
+      </c>
+      <c r="G1275" s="3">
+        <v>3650000</v>
+      </c>
+      <c r="H1275" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I1275" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1275" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1275" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1275" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1275" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1276" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1276" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1276" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1276" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1276" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1276" s="3">
+        <v>170000</v>
+      </c>
+      <c r="G1276" s="3">
+        <v>170000</v>
+      </c>
+      <c r="H1276" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I1276" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1276" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1276" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1276" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1276" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1277" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1277" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C1277" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1277" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1277" s="2">
+        <v>36</v>
+      </c>
+      <c r="F1277" s="3">
+        <v>450000</v>
+      </c>
+      <c r="G1277" s="3">
+        <v>450000</v>
+      </c>
+      <c r="H1277" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I1277" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1277" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1277" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1277" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1277" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1278" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1278" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1278" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1278" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1278" s="2">
+        <v>16</v>
+      </c>
+      <c r="F1278" s="3">
+        <v>430000</v>
+      </c>
+      <c r="G1278" s="3">
+        <v>430000</v>
+      </c>
+      <c r="H1278" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1278" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1278" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1278" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1278" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1278" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1279" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1279" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1279" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1279" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1279" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1279" s="3">
+        <v>2110000</v>
+      </c>
+      <c r="G1279" s="3">
+        <v>2110000</v>
+      </c>
+      <c r="H1279" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I1279" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1279" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1279" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1279" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1279" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1280" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1280" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1280" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1280" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1280" s="2">
+        <v>12</v>
+      </c>
+      <c r="F1280" s="3">
+        <v>790000</v>
+      </c>
+      <c r="G1280" s="3">
+        <v>780000</v>
+      </c>
+      <c r="H1280" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1280" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1280" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1280" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1280" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1280" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1281" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1281" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1281" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1281" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1281" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1281" s="3">
+        <v>9990000</v>
+      </c>
+      <c r="G1281" s="3">
+        <v>10060000</v>
+      </c>
+      <c r="H1281" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1281" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1281" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1281" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1281" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1281" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1282" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1282" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1282" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1282" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1282" s="2">
+        <v>118</v>
+      </c>
+      <c r="F1282" s="3">
+        <v>6510000</v>
+      </c>
+      <c r="G1282" s="3">
+        <v>6370000</v>
+      </c>
+      <c r="H1282" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1282" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1282" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1282" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1282" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1282" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1283" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1283" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1283" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1283" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1283" s="2">
+        <v>30</v>
+      </c>
+      <c r="F1283" s="3">
+        <v>2610000</v>
+      </c>
+      <c r="G1283" s="3">
+        <v>2740000</v>
+      </c>
+      <c r="H1283" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1283" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1283" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1283" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1283" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1283" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1284" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1284" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1284" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1284" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1284" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1284" s="3">
+        <v>160000</v>
+      </c>
+      <c r="G1284" s="3">
+        <v>160000</v>
+      </c>
+      <c r="H1284" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1284" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1284" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1284" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1284" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1284" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1285" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1285" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1285" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1285" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1285" s="2">
+        <v>26</v>
+      </c>
+      <c r="F1285" s="3">
+        <v>320000</v>
+      </c>
+      <c r="G1285" s="3">
+        <v>320000</v>
+      </c>
+      <c r="H1285" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1285" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1285" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1285" s="2">
+        <v>5</v>
+      </c>
+      <c r="L1285" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1285" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1286" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1286" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1286" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1286" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1286" s="2">
+        <v>54</v>
+      </c>
+      <c r="F1286" s="3">
+        <v>2350000</v>
+      </c>
+      <c r="G1286" s="3">
+        <v>2330000</v>
+      </c>
+      <c r="H1286" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1286" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1286" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1286" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1286" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1286" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1287" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1287" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1287" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1287" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1287" s="2">
+        <v>131</v>
+      </c>
+      <c r="F1287" s="3">
+        <v>5090000</v>
+      </c>
+      <c r="G1287" s="3">
+        <v>5040000</v>
+      </c>
+      <c r="H1287" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I1287" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1287" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1287" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1287" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1287" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1288" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1288" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1288" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1288" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1288" s="2">
+        <v>89</v>
+      </c>
+      <c r="F1288" s="3">
+        <v>8280000</v>
+      </c>
+      <c r="G1288" s="3">
+        <v>8280000</v>
+      </c>
+      <c r="H1288" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I1288" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1288" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1288" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1288" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1288" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1289" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1289" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1289" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1289" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1289" s="2">
+        <v>130</v>
+      </c>
+      <c r="F1289" s="3">
+        <v>11240000</v>
+      </c>
+      <c r="G1289" s="3">
+        <v>11300000</v>
+      </c>
+      <c r="H1289" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I1289" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1289" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1289" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1289" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1289" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1290" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1290" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1290" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1290" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1290" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1290" s="3">
+        <v>2020000</v>
+      </c>
+      <c r="G1290" s="3">
+        <v>1990000</v>
+      </c>
+      <c r="H1290" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1290" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1290" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1290" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1290" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1290" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1291" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1291" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1291" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1291" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1291" s="2">
+        <v>41</v>
+      </c>
+      <c r="F1291" s="3">
+        <v>1160000</v>
+      </c>
+      <c r="G1291" s="3">
+        <v>1130000</v>
+      </c>
+      <c r="H1291" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I1291" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1291" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1291" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1291" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1291" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1292" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1292" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1292" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1292" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1292" s="2">
+        <v>91</v>
+      </c>
+      <c r="F1292" s="3">
+        <v>8180000</v>
+      </c>
+      <c r="G1292" s="3">
+        <v>8120000</v>
+      </c>
+      <c r="H1292" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="I1292" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1292" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1292" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1292" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1292" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1293" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1293" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1293" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1293" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1293" s="2">
+        <v>30</v>
+      </c>
+      <c r="F1293" s="3">
+        <v>830000</v>
+      </c>
+      <c r="G1293" s="3">
+        <v>830000</v>
+      </c>
+      <c r="H1293" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1293" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1293" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1293" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1293" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1293" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1294" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1294" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1294" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1294" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1294" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1294" s="3">
+        <v>280000</v>
+      </c>
+      <c r="G1294" s="3">
+        <v>280000</v>
+      </c>
+      <c r="H1294" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1294" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1294" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1294" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1294" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1294" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1295" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1295" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1295" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1295" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1295" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1295" s="3">
+        <v>160000</v>
+      </c>
+      <c r="G1295" s="3">
+        <v>160000</v>
+      </c>
+      <c r="H1295" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1295" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1295" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1295" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1295" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1295" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1296" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1296" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1296" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1296" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1296" s="2">
+        <v>108</v>
+      </c>
+      <c r="F1296" s="3">
+        <v>3270000</v>
+      </c>
+      <c r="G1296" s="3">
+        <v>3210000</v>
+      </c>
+      <c r="H1296" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1296" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1296" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1296" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1296" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1296" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1297" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1297" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1297" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1297" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1297" s="2">
+        <v>112</v>
+      </c>
+      <c r="F1297" s="3">
+        <v>3890000</v>
+      </c>
+      <c r="G1297" s="3">
+        <v>3830000</v>
+      </c>
+      <c r="H1297" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1297" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1297" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1297" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1297" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1297" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1298" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1298" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1298" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1298" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1298" s="2">
+        <v>136</v>
+      </c>
+      <c r="F1298" s="3">
+        <v>7260000</v>
+      </c>
+      <c r="G1298" s="3">
+        <v>7260000</v>
+      </c>
+      <c r="H1298" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I1298" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1298" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1298" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1298" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1298" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1299" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1299" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1299" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1299" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1299" s="2">
+        <v>90</v>
+      </c>
+      <c r="F1299" s="3">
+        <v>3570000</v>
+      </c>
+      <c r="G1299" s="3">
+        <v>3550000</v>
+      </c>
+      <c r="H1299" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I1299" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1299" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1299" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1299" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1299" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1300" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1300" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1300" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1300" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1300" s="2">
+        <v>15</v>
+      </c>
+      <c r="F1300" s="3">
+        <v>360000</v>
+      </c>
+      <c r="G1300" s="3">
+        <v>360000</v>
+      </c>
+      <c r="H1300" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1300" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1300" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1300" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1300" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1300" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1301" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1301" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1301" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1301" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1301" s="2">
+        <v>58</v>
+      </c>
+      <c r="F1301" s="3">
+        <v>1150000</v>
+      </c>
+      <c r="G1301" s="3">
+        <v>1150000</v>
+      </c>
+      <c r="H1301" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1301" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1301" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1301" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1301" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1301" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1302" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1302" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1302" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1302" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1302" s="2">
+        <v>48</v>
+      </c>
+      <c r="F1302" s="3">
+        <v>1500000</v>
+      </c>
+      <c r="G1302" s="3">
+        <v>1480000</v>
+      </c>
+      <c r="H1302" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I1302" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1302" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1302" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1302" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1302" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1303" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1303" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1303" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1303" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1303" s="2">
+        <v>77</v>
+      </c>
+      <c r="F1303" s="3">
+        <v>4420000</v>
+      </c>
+      <c r="G1303" s="3">
+        <v>4440000</v>
+      </c>
+      <c r="H1303" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1303" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1303" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1303" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1303" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1303" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1304" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1304" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1304" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1304" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1304" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1304" s="3">
+        <v>370000</v>
+      </c>
+      <c r="G1304" s="3">
+        <v>370000</v>
+      </c>
+      <c r="H1304" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1304" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1304" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1304" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1304" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1304" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1305" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1305" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C1305" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1305" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1305" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1305" s="3">
+        <v>390000</v>
+      </c>
+      <c r="G1305" s="3">
+        <v>390000</v>
+      </c>
+      <c r="H1305" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1305" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1305" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1305" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1305" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1305" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1306" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1306" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1306" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1306" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1306" s="2">
+        <v>156</v>
+      </c>
+      <c r="F1306" s="3">
+        <v>6890000</v>
+      </c>
+      <c r="G1306" s="3">
+        <v>6830000</v>
+      </c>
+      <c r="H1306" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I1306" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1306" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1306" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1306" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1306" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1307" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1307" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1307" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1307" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1307" s="2">
+        <v>29</v>
+      </c>
+      <c r="F1307" s="3">
+        <v>760000</v>
+      </c>
+      <c r="G1307" s="3">
+        <v>750000</v>
+      </c>
+      <c r="H1307" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1307" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1307" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1307" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1307" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1307" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1308" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1308" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1308" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1308" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1308" s="2">
+        <v>102</v>
+      </c>
+      <c r="F1308" s="3">
+        <v>3010000</v>
+      </c>
+      <c r="G1308" s="3">
+        <v>2960000</v>
+      </c>
+      <c r="H1308" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I1308" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1308" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1308" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1308" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1308" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1309" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1309" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1309" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1309" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1309" s="2">
+        <v>19</v>
+      </c>
+      <c r="F1309" s="3">
+        <v>900000</v>
+      </c>
+      <c r="G1309" s="3">
+        <v>890000</v>
+      </c>
+      <c r="H1309" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I1309" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1309" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1309" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1309" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1309" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1310" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1310" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1310" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1310" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1310" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1310" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G1310" s="3">
+        <v>190000</v>
+      </c>
+      <c r="H1310" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1310" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1310" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1310" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1310" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1310" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1311" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1311" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1311" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1311" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1311" s="2">
+        <v>11</v>
+      </c>
+      <c r="F1311" s="3">
+        <v>2890000</v>
+      </c>
+      <c r="G1311" s="3">
+        <v>2850000</v>
+      </c>
+      <c r="H1311" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I1311" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1311" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1311" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1311" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1311" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1312" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1312" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1312" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1312" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1312" s="2">
+        <v>17</v>
+      </c>
+      <c r="F1312" s="3">
+        <v>1280000</v>
+      </c>
+      <c r="G1312" s="3">
+        <v>1260000</v>
+      </c>
+      <c r="H1312" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1312" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1312" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1312" s="2">
+        <v>1</v>
+      </c>
+      <c r="L1312" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1312" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1313" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1313" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1313" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1313" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1313" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1313" s="3">
+        <v>160000</v>
+      </c>
+      <c r="G1313" s="3">
+        <v>160000</v>
+      </c>
+      <c r="H1313" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1313" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1313" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1313" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1313" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1313" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1314" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1314" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1314" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1314" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1314" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1314" s="3">
+        <v>160000</v>
+      </c>
+      <c r="G1314" s="3">
+        <v>160000</v>
+      </c>
+      <c r="H1314" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1314" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1314" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1314" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1314" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1314" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1315" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1315" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1315" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1315" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1315" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1315" s="3">
+        <v>410000</v>
+      </c>
+      <c r="G1315" s="3">
+        <v>410000</v>
+      </c>
+      <c r="H1315" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1315" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1315" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1315" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1315" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1315" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1316" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1316" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1316" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1316" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1316" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1316" s="3">
+        <v>3380000</v>
+      </c>
+      <c r="G1316" s="3">
+        <v>3380000</v>
+      </c>
+      <c r="H1316" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1316" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1316" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1316" s="2">
+        <v>0</v>
+      </c>
+      <c r="L1316" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1316" s="7" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>

--- a/TM_all.xlsx
+++ b/TM_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aecf56309e6168f4/Documents/comunio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="244" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E3F379B-9358-4168-BFDA-3998CC4AE001}"/>
+  <xr:revisionPtr revIDLastSave="245" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39F085F2-4AE3-4074-A10F-597EEC87267F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{607DE709-F91E-4262-9941-1066BBEC319E}"/>
   </bookViews>
@@ -1439,7 +1439,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>87</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="3" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>195</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="4" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>114</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="5" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>196</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="6" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>135</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>197</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="8" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>97</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="9" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>198</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>134</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="11" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>72</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="12" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>70</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="13" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="14" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>199</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="15" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>146</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="16" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>200</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="17" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>201</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="18" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>182</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="19" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>133</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="20" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>46</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="21" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>137</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="22" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
         <v>151</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="23" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
         <v>108</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="24" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
         <v>125</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="25" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
         <v>177</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="26" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>132</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="27" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
         <v>178</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
         <v>87</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="29" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
         <v>195</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="30" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
         <v>114</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="31" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
         <v>196</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="32" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
         <v>135</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="s">
         <v>197</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="2" t="s">
         <v>97</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="s">
         <v>198</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
         <v>134</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
         <v>72</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="2" t="s">
         <v>70</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
         <v>28</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
         <v>199</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
         <v>146</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="42" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
         <v>200</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
         <v>201</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="44" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="2" t="s">
         <v>182</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="2" t="s">
         <v>133</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="2" t="s">
         <v>46</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="2" t="s">
         <v>137</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="48" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="2" t="s">
         <v>151</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="49" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="2" t="s">
         <v>108</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="50" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="2" t="s">
         <v>125</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="51" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="2" t="s">
         <v>177</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="52" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="2" t="s">
         <v>132</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="53" spans="2:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:13" ht="13" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="2" t="s">
         <v>178</v>
       </c>
